--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -905,7 +905,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>This workbook documents the top-50 names from a global cross-listing universe of 19,750 equities ranked by an entry-today asymmetry score that blends Yartseva inflection signals, Pew sub-book / net-cash floors, Berezin growth quality, and an intrinsic-discount overlay. Each candidate has been qualitatively reviewed and assigned a verdict of Green (high-conviction), Yellow (risk-flagged), Red (avoid) or — where due diligence remains incomplete — Unresearched. Sheets are sequenced as Cover · Methodology · Index · per-name pages · Coverage · References.</t>
+          <t>This workbook documents the top-50 names from a global cross-listing universe of 19,749 equities ranked by an entry-today asymmetry score that blends Yartseva inflection signals, Pew sub-book / net-cash floors, Berezin growth quality, and an intrinsic-discount overlay. Each candidate has been qualitatively reviewed and assigned a verdict of Green (high-conviction), Yellow (risk-flagged), Red (avoid) or — where due diligence remains incomplete — Unresearched. Sheets are sequenced as Cover · Methodology · Index · per-name pages · Coverage · References.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
     <row r="22" ht="36" customHeight="1">
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>19,750</t>
+          <t>19,749</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -26400,7 +26400,7 @@
         </is>
       </c>
       <c r="C5" s="50" t="n">
-        <v>19750</v>
+        <v>19749</v>
       </c>
       <c r="D5" s="34" t="n">
         <v>123</v>
@@ -26412,10 +26412,10 @@
         <v>130</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>19290</v>
+        <v>19289</v>
       </c>
       <c r="H5" s="51" t="n">
-        <v>2.329113924050633</v>
+        <v>2.329231859841005</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -58,8 +58,8 @@
     <sheet name="46_0538_HK" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="47_0887_HK" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="48_7219_T" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="49_OPHC" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="50_053980_KQ" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="49_053980_KQ" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="50_094840_KQ" sheetId="53" state="visible" r:id="rId53"/>
     <sheet name="Coverage" sheetId="54" state="visible" r:id="rId54"/>
     <sheet name="References" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
@@ -905,7 +905,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>This workbook documents the top-50 names from a global cross-listing universe of 19,749 equities ranked by an entry-today asymmetry score that blends Yartseva inflection signals, Pew sub-book / net-cash floors, Berezin growth quality, and an intrinsic-discount overlay. Each candidate has been qualitatively reviewed and assigned a verdict of Green (high-conviction), Yellow (risk-flagged), Red (avoid) or — where due diligence remains incomplete — Unresearched. Sheets are sequenced as Cover · Methodology · Index · per-name pages · Coverage · References.</t>
+          <t>This workbook documents the top-50 names from a global cross-listing universe of 19,851 equities ranked by an entry-today asymmetry score that blends Yartseva inflection signals, Pew sub-book / net-cash floors, Berezin growth quality, and an intrinsic-discount overlay. Each candidate has been qualitatively reviewed and assigned a verdict of Green (high-conviction), Yellow (risk-flagged), Red (avoid) or — where due diligence remains incomplete — Unresearched. Sheets are sequenced as Cover · Methodology · Index · per-name pages · Coverage · References.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
     <row r="22" ht="36" customHeight="1">
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>19,749</t>
+          <t>19,851</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>457</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -12966,31 +12966,31 @@
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
-          <t>OPHC</t>
+          <t>053980.KQ</t>
         </is>
       </c>
       <c r="D52" s="21" t="inlineStr">
         <is>
-          <t>OptimumBank Holdings, Inc.</t>
+          <t>Osangjaiel Co., Ltd.</t>
         </is>
       </c>
       <c r="E52" s="22" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="G52" s="26" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H52" s="25" t="n">
-        <v>0.7980118180319363</v>
+        <v>0.7970702896263708</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -12999,12 +12999,12 @@
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>053980.KQ</t>
+          <t>094840.KQ</t>
         </is>
       </c>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>Osangjaiel Co., Ltd.</t>
+          <t>Suprema HQ Inc.</t>
         </is>
       </c>
       <c r="E53" s="22" t="inlineStr">
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="H53" s="25" t="n">
-        <v>0.7970702896263708</v>
+        <v>0.7938711177464474</v>
       </c>
     </row>
   </sheetData>
@@ -25325,7 +25325,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  #49  ·  OPHC  ·  OptimumBank Holdings, Inc.</t>
+          <t xml:space="preserve">  #49  ·  053980.KQ  ·  Osangjaiel Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -25335,9 +25335,9 @@
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+      <c r="C3" s="45" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="29" t="inlineStr">
@@ -25346,7 +25346,7 @@
         </is>
       </c>
       <c r="E3" s="31" t="n">
-        <v>0.7980118180319363</v>
+        <v>0.7970702896263708</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -25368,7 +25368,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
@@ -25380,7 +25380,7 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -25390,10 +25390,8 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
+      <c r="B8" s="33" t="n">
+        <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -25415,7 +25413,7 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>66739896</v>
+        <v>53787598848</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -25425,7 +25423,7 @@
         </is>
       </c>
       <c r="B11" s="34" t="n">
-        <v>49361000</v>
+        <v>136175106840</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -25436,7 +25434,7 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
@@ -25454,7 +25452,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Profitable fast-growing FL community bank: Q1'26 NI $4.7M, loans/deposits +13.8%/+17.3% QoQ, NIM 4.28%, ROAE 21.6%, Tier 1 leverage 10.74%; dilution but earnings outpace</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -25479,7 +25477,7 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>0.5689168248036316</v>
+        <v>0.5390975515032371</v>
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
@@ -25487,7 +25485,7 @@
         </is>
       </c>
       <c r="E21" s="25" t="n">
-        <v>0.5251693349380993</v>
+        <v>0.7285270075959243</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -25497,7 +25495,7 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>0.4258767809797973</v>
+        <v>0.4151802429096934</v>
       </c>
       <c r="D22" s="36" t="inlineStr">
         <is>
@@ -25505,7 +25503,7 @@
         </is>
       </c>
       <c r="E22" s="25" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -25515,7 +25513,7 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="D23" s="36" t="inlineStr">
         <is>
@@ -25533,7 +25531,7 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>0.831281</v>
+        <v>0.859829</v>
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
@@ -25541,7 +25539,7 @@
         </is>
       </c>
       <c r="E24" s="37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -25551,7 +25549,7 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>0.5542332460803989</v>
+        <v>0.4347092214693205</v>
       </c>
       <c r="D25" s="38" t="n"/>
       <c r="E25" s="38" t="n"/>
@@ -25574,17 +25572,15 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>0.5475105703995997</v>
+        <v>0.4894186186926682</v>
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
           <t>NCAV / mcap (%)</t>
         </is>
       </c>
-      <c r="E28" s="40" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E28" s="39" t="n">
+        <v>77.19257936635677</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -25593,20 +25589,16 @@
           <t>EV / EBITDA</t>
         </is>
       </c>
-      <c r="C29" s="40" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C29" s="25" t="n">
+        <v>0.2910564783690633</v>
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
           <t>Net debt / EBITDA (x)</t>
         </is>
       </c>
-      <c r="E29" s="40" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E29" s="25" t="n">
+        <v>-3.665553649058154</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -25615,20 +25607,16 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="40" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="25" t="n">
+        <v>0.310565911742744</v>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
           <t>ROCE (%)</t>
         </is>
       </c>
-      <c r="E30" s="40" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E30" s="39" t="n">
+        <v>21.41385175140904</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -25637,18 +25625,18 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="25" t="n">
-        <v>9.22034</v>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D31" s="36" t="inlineStr">
         <is>
           <t>EBITDA margin (%)</t>
         </is>
       </c>
-      <c r="E31" s="40" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E31" s="39" t="n">
+        <v>10.03543081927351</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -25658,7 +25646,7 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>1.352077470067462</v>
+        <v>0.3949884828157187</v>
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
@@ -25666,7 +25654,7 @@
         </is>
       </c>
       <c r="E32" s="39" t="n">
-        <v>18.501</v>
+        <v>36.765</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -25676,15 +25664,17 @@
         </is>
       </c>
       <c r="C33" s="39" t="n">
-        <v>25.389611035654</v>
+        <v>17.73458665994102</v>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
           <t>Rev 3y CAGR (%)</t>
         </is>
       </c>
-      <c r="E33" s="39" t="n">
-        <v>37.96624288776253</v>
+      <c r="E33" s="40" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
@@ -25694,7 +25684,7 @@
         </is>
       </c>
       <c r="C34" s="39" t="n">
-        <v>92.61926329642468</v>
+        <v>93.13033584480712</v>
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
@@ -25714,7 +25704,7 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>23.25647963334995</v>
+        <v>12.59731763970912</v>
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
@@ -25722,7 +25712,7 @@
         </is>
       </c>
       <c r="E35" s="39" t="n">
-        <v>17.24138391712487</v>
+        <v>-12.76815609807693</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -25746,14 +25736,14 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="41" t="inlineStr">
         <is>
-          <t>·  Negative enterprise value</t>
+          <t>·  Sub-book  (P/B 0.49)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="41" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.55)</t>
+          <t>·  Insider-aligned  (37% insider)</t>
         </is>
       </c>
     </row>
@@ -25771,7 +25761,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="42" t="inlineStr">
         <is>
-          <t>cash 172% of mcap; cash &gt; EV (23.26x, net cash 93% mcap)</t>
+          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.3x); cash 93% of mcap; cash &gt; EV (12.60x, net cash 93% mcap)</t>
         </is>
       </c>
     </row>
@@ -25823,7 +25813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -25837,7 +25827,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  #50  ·  053980.KQ  ·  Osangjaiel Co., Ltd.</t>
+          <t xml:space="preserve">  #50  ·  094840.KQ  ·  Suprema HQ Inc.</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25848,7 @@
         </is>
       </c>
       <c r="E3" s="31" t="n">
-        <v>0.7970702896263708</v>
+        <v>0.7938711177464474</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -25925,7 +25915,7 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>53787598848</v>
+        <v>100120371200</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -25935,7 +25925,7 @@
         </is>
       </c>
       <c r="B11" s="34" t="n">
-        <v>136175106840</v>
+        <v>22685433020</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -25989,7 +25979,7 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>0.5390975515032371</v>
+        <v>0.5785184051619124</v>
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
@@ -25997,7 +25987,7 @@
         </is>
       </c>
       <c r="E21" s="25" t="n">
-        <v>0.7285270075959243</v>
+        <v>0.6774480246347664</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -26007,7 +25997,7 @@
         </is>
       </c>
       <c r="C22" s="25" t="n">
-        <v>0.4151802429096934</v>
+        <v>0.4781193501586895</v>
       </c>
       <c r="D22" s="36" t="inlineStr">
         <is>
@@ -26033,7 +26023,7 @@
         </is>
       </c>
       <c r="E23" s="25" t="n">
-        <v>1</v>
+        <v>0.961</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -26043,7 +26033,7 @@
         </is>
       </c>
       <c r="C24" s="25" t="n">
-        <v>0.859829</v>
+        <v>0.413999</v>
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
@@ -26051,7 +26041,7 @@
         </is>
       </c>
       <c r="E24" s="37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -26061,7 +26051,7 @@
         </is>
       </c>
       <c r="C25" s="25" t="n">
-        <v>0.4347092214693205</v>
+        <v>0.4134057504621787</v>
       </c>
       <c r="D25" s="38" t="n"/>
       <c r="E25" s="38" t="n"/>
@@ -26084,7 +26074,7 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>0.4894186186926682</v>
+        <v>0.4098378807812725</v>
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
@@ -26092,7 +26082,7 @@
         </is>
       </c>
       <c r="E28" s="39" t="n">
-        <v>77.19257936635677</v>
+        <v>74.91782625352472</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -26102,7 +26092,7 @@
         </is>
       </c>
       <c r="C29" s="25" t="n">
-        <v>0.2910564783690633</v>
+        <v>1.800253838557828</v>
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
@@ -26110,7 +26100,7 @@
         </is>
       </c>
       <c r="E29" s="25" t="n">
-        <v>-3.665553649058154</v>
+        <v>-6.676660242655721</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -26120,7 +26110,7 @@
         </is>
       </c>
       <c r="C30" s="25" t="n">
-        <v>0.310565911742744</v>
+        <v>1.8640727049828</v>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
@@ -26128,7 +26118,7 @@
         </is>
       </c>
       <c r="E30" s="39" t="n">
-        <v>21.41385175140904</v>
+        <v>6.763084361603521</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -26148,7 +26138,7 @@
         </is>
       </c>
       <c r="E31" s="39" t="n">
-        <v>10.03543081927351</v>
+        <v>51.38574392528832</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -26158,7 +26148,7 @@
         </is>
       </c>
       <c r="C32" s="25" t="n">
-        <v>0.3949884828157187</v>
+        <v>4.41342120786196</v>
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
@@ -26166,7 +26156,7 @@
         </is>
       </c>
       <c r="E32" s="39" t="n">
-        <v>36.765</v>
+        <v>51.20099999999999</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -26176,7 +26166,7 @@
         </is>
       </c>
       <c r="C33" s="39" t="n">
-        <v>17.73458665994102</v>
+        <v>6.20733543584784</v>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
@@ -26196,7 +26186,7 @@
         </is>
       </c>
       <c r="C34" s="39" t="n">
-        <v>93.13033584480712</v>
+        <v>77.73678000506654</v>
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
@@ -26216,7 +26206,7 @@
         </is>
       </c>
       <c r="C35" s="25" t="n">
-        <v>12.59731763970912</v>
+        <v>3.710462667145587</v>
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
@@ -26224,7 +26214,7 @@
         </is>
       </c>
       <c r="E35" s="39" t="n">
-        <v>-12.76815609807693</v>
+        <v>40.82758620689655</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -26248,68 +26238,76 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="41" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.49)</t>
+          <t>·  Sub-book  (P/B 0.41)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="41" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (37% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+          <t>·  Insider-aligned  (51% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="41" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n"/>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="42" t="inlineStr">
-        <is>
-          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.3x); cash 93% of mcap; cash &gt; EV (12.60x, net cash 93% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="42" t="inlineStr">
+        <is>
+          <t>growth-flip; first-positive: FCF/CFO; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.9x); cash 78% of mcap; cash &gt; EV (3.71x, net cash 78% mcap)</t>
+        </is>
+      </c>
+    </row>
     <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="43" t="n"/>
-      <c r="B48" s="43" t="n"/>
-      <c r="C48" s="43" t="n"/>
-      <c r="D48" s="43" t="n"/>
-      <c r="E48" s="43" t="n"/>
-      <c r="F48" s="43" t="n"/>
-    </row>
+    <row r="46" ht="18" customHeight="1"/>
     <row r="49">
-      <c r="B49" s="44" t="inlineStr">
+      <c r="A49" s="43" t="n"/>
+      <c r="B49" s="43" t="n"/>
+      <c r="C49" s="43" t="n"/>
+      <c r="D49" s="43" t="n"/>
+      <c r="E49" s="43" t="n"/>
+      <c r="F49" s="43" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="44" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 50 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B44:E46"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -26400,22 +26398,22 @@
         </is>
       </c>
       <c r="C5" s="50" t="n">
-        <v>19749</v>
+        <v>19851</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" s="34" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F5" s="34" t="n">
         <v>130</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>19289</v>
+        <v>19394</v>
       </c>
       <c r="H5" s="51" t="n">
-        <v>2.329231859841005</v>
+        <v>2.302151025137273</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -26475,7 +26473,7 @@
         <v>50</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="34" t="n">
         <v>5</v>
@@ -26484,10 +26482,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="51" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -26551,19 +26549,19 @@
         <v>10</v>
       </c>
       <c r="D13" s="37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="37" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13" s="37" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="37" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -26576,7 +26574,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="37" t="n">
         <v>5</v>
@@ -26585,10 +26583,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="39" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -887,7 +887,7 @@
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Compiled from the Yartseva–Pew–Berezin asymmetry framework  ·  As of 20 June 2026</t>
+          <t>Compiled from the asymmetry framework (Yartseva-aligned upside, Graham downside floor)  ·  As of 20 June 2026</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>This workbook documents the top-50 names from a global cross-listing universe of 19,851 equities ranked by an entry-today asymmetry score that blends Yartseva inflection signals, Pew sub-book / net-cash floors, Berezin growth quality, and an intrinsic-discount overlay. Each candidate has been qualitatively reviewed and assigned a verdict of Green (high-conviction), Yellow (risk-flagged), Red (avoid) or — where due diligence remains incomplete — Unresearched. Sheets are sequenced as Cover · Methodology · Index · per-name pages · Coverage · References.</t>
+          <t>This workbook documents the top-50 names from a global cross-listing universe of 19,851 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum — plus an internal microcap deep-value composite (P/S, P/B, gross-profit / mcap, insider, leverage, momentum). The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and Pew-style negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of Green (high-conviction), Yellow (risk-flagged), Red (avoid) or — where due diligence remains incomplete — Unresearched. Sheets are sequenced as Cover · Methodology · Index · per-name pages · Coverage · References.</t>
         </is>
       </c>
     </row>
@@ -26807,7 +26807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -26833,56 +26833,91 @@
     <row r="6" ht="30" customHeight="1">
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Alta Fox Capital (2020)  Makings of a Multibagger. Internal research note. altafoxcapital.com.</t>
+          <t>Yartseva, A. (2025)  The Alchemy of Multibagger Stocks: An empirical investigation of factors that drive outperformance in the stock market. CAFE Working Paper 33, Birmingham City University. https://www.open-access.bcu.ac.uk/16180/</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Berezin, M. (2023)  Growth-quality screens for emerging-market smid-caps. Working paper.</t>
+          <t>Alta Fox Capital (2020)  Makings of a Multibagger. Summer Intern Class Project. https://www.altafoxcapital.com/s/Makings-of-a-MultiBagger.pdf</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Graham, B. (1934)  Security Analysis. McGraw-Hill, New York.</t>
+          <t>Mayer, C. (2015)  100 Baggers: Stocks That Return 100-to-1 and How to Find Them. Laissez Faire Books.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Pew, A. (2022)  Cash-as-floor screening: negative-EV and Graham net-net heuristics. Pew Capital.</t>
+          <t>Phelps, T. W. (1972)  100 to 1 in the Stock Market. McGraw-Hill, New York.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Yartseva, K. (2024)  Inflection-driven small-cap selection: the first-positive print as entry signal. Yartseva Capital.</t>
+          <t>Graham, B. (1934)  Security Analysis. McGraw-Hill, New York.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Yellowbrick (2023)  Multibagger archetype taxonomy: clusters A through G. Yellowbrick Road Capital.</t>
+          <t>Greenblatt, J. (2006)  The Little Book That Beats the Market. Wiley.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>yfinance (2026)  Yahoo! Finance python wrapper. github.com/ranaroussi/yfinance, accessed 20 June 2026.</t>
+          <t>Mauboussin, M. J. (2017)  The Base Rate Book: Integrating the Past to Better Anticipate the Future. Credit Suisse.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>financedatabase (2026)  Open securities database. github.com/JerBouma/FinanceDatabase, accessed 20 June 2026.</t>
+          <t>Russo, T. (2014)  Global Value: How to Spot Bubbles, Avoid Market Crashes, and Earn Big Returns in the Stock Market. Graham &amp; Doddsville interview series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Cassel, I. (MicroCapClub)  Top 10 Things in Micro Cap Investing. https://microcapclub.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>SEC EDGAR (2026)  XBRL company-facts API. https://data.sec.gov/api/xbrl/companyfacts/, accessed 24 June 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>yfinance (2026)  Yahoo! Finance Python wrapper. https://github.com/ranaroussi/yfinance, accessed 20 June 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>financedatabase (2026)  Open securities database. https://github.com/JerBouma/FinanceDatabase, accessed 20 June 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Internal house frameworks  The Pew negative-EV screen (pew_archetype.py) and Berezin / Stockcoach microcap deep-value composite (yartseva_db.py) are internal naming conventions for hand-rolled archetypes adapted from public deep-value / MicroCapClub heritage — not citations to published frameworks. The 'archetype taxonomy' is internal; the joinyellowbrick.com platform's Multibagger Monitor inspired the cluster-A through G naming but is not the source of the specific tag definitions.</t>
         </is>
       </c>
     </row>

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -905,7 +905,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>This workbook documents the top-50 names from a global cross-listing universe of 23,240 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum — plus an internal microcap deep-value composite (P/S, P/B, gross-profit / mcap, insider, leverage, momentum). The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and Pew-style negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of Green (high-conviction), Yellow (risk-flagged), Red (avoid) or — where due diligence remains incomplete — Unresearched. Sheets are sequenced as Cover · Methodology · Index · per-name pages · Coverage · References.</t>
+          <t>This workbook documents the top-50 names from a global cross-listing universe of 23,190 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum — plus an internal microcap deep-value composite (P/S, P/B, gross-profit / mcap, insider, leverage, momentum). The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and Pew-style negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of Green (high-conviction), Yellow (risk-flagged), Red (avoid) or — where due diligence remains incomplete — Unresearched. Sheets are sequenced as Cover · Methodology · Index · per-name pages · Coverage · References.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
     <row r="22" ht="36" customHeight="1">
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>23,240</t>
+          <t>23,190</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -26396,7 +26396,7 @@
         </is>
       </c>
       <c r="C5" s="50" t="n">
-        <v>23240</v>
+        <v>23190</v>
       </c>
       <c r="D5" s="34" t="n">
         <v>131</v>
@@ -26408,10 +26408,10 @@
         <v>132</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>22766</v>
+        <v>22716</v>
       </c>
       <c r="H5" s="51" t="n">
-        <v>2.039586919104991</v>
+        <v>2.043984476067271</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -84,42 +84,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <i val="1"/>
       <color rgb="00707070"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <color rgb="00707070"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <b val="1"/>
       <color rgb="00404040"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <color rgb="00707070"/>
       <sz val="10"/>
     </font>

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -1,67 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Index" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="01_088910_KQ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="02_AWC_SI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="03_2230_HK" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="04_0057_HK" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="05_003650_KS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="06_ZENIFIB_BO" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="07_SHRIDINE_BO" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="08_TPP_BK" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="09_0882_HK" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="10_ALGEV_PA" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="11_6155_T" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="12_0100_KL" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="13_IRC_BK" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="14_LSIP_JK" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="15_JAMESWARREN_BO" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="16_4301_T" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="17_2348_HK" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="18_S23_SI" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="19_4629_T" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="20_1798_T" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="21_FPIP_ST" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="22_6907_T" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="23_014570_KQ" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="24_TCID_JK" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="25_NPK_BK" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="26_HTMEDIA_BO" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="27_052330_KQ" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="28_120240_KQ" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="29_6986_T" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="30_035610_KQ" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="31_0114_HK" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="32_BENGALT_BO" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="33_SIAM_BK" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="34_036190_KQ" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="35_PRIMEPRO_BO" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="36_7722_T" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="37_IGAR_JK" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="38_METCO_BK" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="39_0420_HK" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="40_2033_HK" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="41_031510_KQ" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="42_1795_T" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="43_047820_KQ" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="44_0212_HK" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="45_PBMPOLY_BO" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="46_054800_KQ" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="47_015230_KS" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="48_0538_HK" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="49_0887_HK" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="50_7219_T" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="Coverage" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="References" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_088910_KQ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_AWC_SI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_2230_HK" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_0057_HK" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_003650_KS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_ZENIFIB_BO" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_SHRIDINE_BO" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_TPP_BK" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_0882_HK" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_ALGEV_PA" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_6155_T" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_0100_KL" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_IRC_BK" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_LSIP_JK" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_JAMESWARREN_BO" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_4301_T" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_2348_HK" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_S23_SI" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_4629_T" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_1798_T" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_FPIP_ST" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_6907_T" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_014570_KQ" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_TCID_JK" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_NPK_BK" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_HTMEDIA_BO" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_052330_KQ" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_120240_KQ" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_6986_T" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_035610_KQ" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_0114_HK" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_BENGALT_BO" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_SIAM_BK" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_036190_KQ" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35_PRIMEPRO_BO" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_7722_T" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="37_IGAR_JK" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38_METCO_BK" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="39_0420_HK" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40_2033_HK" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41_031510_KQ" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42_1795_T" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43_047820_KQ" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44_0212_HK" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45_PBMPOLY_BO" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46_054800_KQ" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="47_015230_KS" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48_0538_HK" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49_0887_HK" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50_7219_T" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -1250,10 +1250,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>3.69136615408451</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -1744,10 +1742,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>12.07545677042703</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -2228,10 +2224,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-4.85849326192409</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -2730,10 +2724,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>13.16741950428538</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -3228,10 +3220,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-2.05160744500846</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -3718,10 +3708,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>23.99058833898137</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -4212,10 +4200,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-2.14910060299603</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -4694,10 +4680,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>14.03843460486491</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -5178,10 +5162,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-2.2457207058357</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -5666,10 +5648,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>24.39749694415558</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -6296,10 +6276,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>16.08568822862014</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -6802,10 +6780,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>24.03992556251057</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -7288,10 +7264,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>6.929317560577431</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -7782,10 +7756,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>15.96915285260003</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -8278,10 +8250,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>44.44050164399806</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -8764,10 +8734,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>14.66329044442543</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -9250,10 +9218,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-14.02875104746569</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -9740,10 +9706,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>15.69105868985647</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -10234,10 +10198,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>13.30859566835752</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -10726,10 +10688,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>8.700165361078579</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -12993,10 +12953,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>39.39906543686433</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -13489,10 +13447,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>23.42328269392889</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -14475,10 +14431,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>12.96488373879826</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -14969,10 +14923,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-1.07304976403589</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -15461,10 +15413,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>32.22922398597871</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -15955,10 +15905,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-29.29164765468225</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -16449,10 +16397,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>23.85416843924622</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -16941,10 +16887,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -17435,10 +17379,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>28.95813021275008</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -17929,10 +17871,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>8.95404636415233</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -18427,10 +18367,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>4.10990513790382</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -18921,10 +18859,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>7.00038199914789</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -19415,10 +19351,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-6.54779627873395</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -19905,10 +19839,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-10.25953389830508</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -20393,10 +20325,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>8.272729934564961</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -20887,10 +20817,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>19.00031673248309</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -21381,10 +21309,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-30.35739413704464</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -21879,10 +21805,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>26.77384147074138</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -22367,10 +22291,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-10.84555980465894</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -22861,10 +22783,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>21.56346844565357</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -23347,10 +23267,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-0.22712524334847</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -23843,10 +23761,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>10.91122469934276</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -24337,10 +24253,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>6.67598367194824</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -24831,10 +24745,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>10.22818632319828</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -25325,10 +25237,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-0.3077629745327</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -26416,10 +26326,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>32.52742891395208</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -26910,10 +26818,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>29.12052230728846</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -27406,10 +27312,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>-6.109694716853889</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -27896,10 +27800,8 @@
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="33" t="n">
+        <v>26.21823687104556</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -757,7 +757,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>23,190</t>
+          <t>23,688</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>22,716</t>
+          <t>23,214</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 23,190 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 23,688 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
         </is>
       </c>
       <c r="C5" s="42" t="n">
-        <v>23190</v>
+        <v>23688</v>
       </c>
       <c r="D5" s="28" t="n">
         <v>131</v>
@@ -25445,10 +25445,10 @@
         <v>132</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>22716</v>
+        <v>23214</v>
       </c>
       <c r="H5" s="43" t="n">
-        <v>2.043984476067271</v>
+        <v>2.001013171225937</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
@@ -25573,16 +25573,16 @@
         <v>2</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" s="33" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -754,7 +754,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>24,603</t>
+          <t>24,899</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>24,130</t>
+          <t>24,426</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 24,603 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 24,899 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -25412,7 +25412,7 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>24603</v>
+        <v>24899</v>
       </c>
       <c r="D5" s="28" t="n">
         <v>131</v>
@@ -25424,10 +25424,10 @@
         <v>131</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>24130</v>
+        <v>24426</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.922529772791936</v>
+        <v>1.899674685730351</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -1,67 +1,67 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_088910_KQ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_AWC_SI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_2230_HK" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_0057_HK" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_003650_KS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_ZENIFIB_BO" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_ALGEV_PA" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_0882_HK" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_TPP_BK" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_SHRIDINE_BO" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_6155_T" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_0100_KL" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_IRC_BK" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_LSIP_JK" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_JAMESWARREN_BO" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_2348_HK" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_4301_T" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_S23_SI" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_4629_T" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_1798_T" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_6907_T" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_FPIP_ST" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_014570_KQ" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_TCID_JK" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_NPK_BK" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_052330_KQ" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_HTMEDIA_BO" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_120240_KQ" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_6986_T" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_035610_KQ" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_0114_HK" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_7722_T" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_BENGALT_BO" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_SIAM_BK" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35_036190_KQ" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_PRIMEPRO_BO" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="37_IGAR_JK" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="38_METCO_BK" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="39_0420_HK" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="40_2033_HK" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41_031510_KQ" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42_0538_HK" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43_0212_HK" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44_1795_T" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45_047820_KQ" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46_PBMPOLY_BO" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="47_054800_KQ" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48_0887_HK" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49_015230_KS" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50_7219_T" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Index" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="01_088910_KQ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="02_AWC_SI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="03_2230_HK" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="04_0057_HK" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="05_003650_KS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="06_ZENIFIB_BO" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="07_ALGEV_PA" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="08_0882_HK" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="09_TPP_BK" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="10_SHRIDINE_BO" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="11_6155_T" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="12_0100_KL" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="13_IRC_BK" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="14_LSIP_JK" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="15_JAMESWARREN_BO" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="16_2348_HK" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="17_4301_T" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="18_S23_SI" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="19_4629_T" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="20_1798_T" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="21_6907_T" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="22_FPIP_ST" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="23_014570_KQ" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="24_TCID_JK" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="25_NPK_BK" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="26_052330_KQ" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="27_HTMEDIA_BO" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="28_120240_KQ" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="29_6986_T" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="30_035610_KQ" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="31_0114_HK" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="32_7722_T" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="33_BENGALT_BO" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="34_SIAM_BK" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="35_036190_KQ" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="36_PRIMEPRO_BO" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="37_IGAR_JK" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="38_METCO_BK" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="39_0420_HK" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="40_2033_HK" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="41_031510_KQ" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="42_0538_HK" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="43_0212_HK" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="44_1795_T" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="45_047820_KQ" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="46_PBMPOLY_BO" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="47_054800_KQ" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="48_0887_HK" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="49_015230_KS" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="50_7219_T" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="Coverage" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="References" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -754,7 +754,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>24,899</t>
+          <t>26,756</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -764,22 +764,22 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>480</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>214</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>24,426</t>
+          <t>26,276</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1.9% of universe</t>
+          <t>1.8% of universe</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 24,899 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 26,756 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -25412,22 +25412,22 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>24899</v>
+        <v>26756</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>24426</v>
+        <v>26276</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.899674685730351</v>
+        <v>1.793990133054268</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -754,7 +754,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>26,756</t>
+          <t>30,308</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>26,276</t>
+          <t>29,828</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1.8% of universe</t>
+          <t>1.6% of universe</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 26,756 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 30,308 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -12884,8 +12884,10 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n">
-        <v>2215</v>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -25412,7 +25414,7 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>26756</v>
+        <v>30308</v>
       </c>
       <c r="D5" s="28" t="n">
         <v>133</v>
@@ -25424,10 +25426,10 @@
         <v>133</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>26276</v>
+        <v>29828</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.793990133054268</v>
+        <v>1.583740266596278</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -754,7 +754,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>28,684</t>
+          <t>28,973</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>28,223</t>
+          <t>28,512</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 28,684 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 28,973 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -25258,7 +25258,7 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>28684</v>
+        <v>28973</v>
       </c>
       <c r="D5" s="28" t="n">
         <v>130</v>
@@ -25270,10 +25270,10 @@
         <v>130</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>28223</v>
+        <v>28512</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.607167759029424</v>
+        <v>1.591136575432299</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
@@ -25398,16 +25398,16 @@
         <v>0</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -37,29 +37,29 @@
     <sheet name="25_0882_HK" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="26_014570_KQ" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="27_4629_T" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="28_7871_T" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="29_9983_HK" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="30_NPK_BK" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="31_MDX_BK" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="32_DC-A_TO" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="33_120240_KQ" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="34_KROS" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="35_JAMESWARREN_BO" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="36_PRIMEPRO_BO" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="37_6986_T" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="38_035610_KQ" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="39_BMKS3_SA" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="40_6907_T" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="41_4301_T" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="42_0114_HK" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="43_7722_T" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="44_3798_HK" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="45_BENGALT_BO" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="46_0559_HK" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="47_036190_KQ" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="48_FPIP_ST" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="49_1V5_F" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="50_IGAR_JK" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="28_9983_HK" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="29_NPK_BK" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="30_MDX_BK" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="31_DC-A_TO" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="32_120240_KQ" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="33_KROS" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="34_JAMESWARREN_BO" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="35_PRIMEPRO_BO" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="36_035610_KQ" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="37_BMKS3_SA" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="38_6907_T" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="39_4301_T" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="40_0114_HK" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="41_7722_T" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="42_3798_HK" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="43_BENGALT_BO" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="44_7871_T" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="45_0559_HK" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="46_036190_KQ" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="47_FPIP_ST" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="48_1V5_F" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="49_IGAR_JK" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="50_6912_KL" sheetId="53" state="visible" r:id="rId53"/>
     <sheet name="Coverage" sheetId="54" state="visible" r:id="rId54"/>
     <sheet name="References" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
@@ -3634,10 +3634,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>7.146097792911459</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -6224,10 +6222,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>149.1439690522244</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -7202,10 +7198,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>2.431402565182107</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -9188,10 +9182,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>2.496306784721881</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -11829,22 +11821,22 @@
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>7871.T</t>
+          <t>9983.HK</t>
         </is>
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>Fukuvi Chemical Industry Co.,Ltd.</t>
+          <t>Central China New Life Limited</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -11853,7 +11845,7 @@
         </is>
       </c>
       <c r="H31" s="21" t="n">
-        <v>1.045323432299752</v>
+        <v>1.043289599422137</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -11862,31 +11854,31 @@
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>9983.HK</t>
+          <t>NPK.BK</t>
         </is>
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>Central China New Life Limited</t>
+          <t>New Plus Knitting Public Company Limited</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
         <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="G32" s="22" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="H32" s="21" t="n">
-        <v>1.043289599422137</v>
+        <v>1.041913042278164</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -11895,12 +11887,12 @@
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>NPK.BK</t>
+          <t>MDX.BK</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>New Plus Knitting Public Company Limited</t>
+          <t>MDX Public Company Limited</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
@@ -11910,16 +11902,16 @@
       </c>
       <c r="F33" s="19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H33" s="21" t="n">
-        <v>1.041913042278164</v>
+        <v>1.038413084209085</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -11928,22 +11920,22 @@
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>MDX.BK</t>
+          <t>DC-A.TO</t>
         </is>
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>MDX Public Company Limited</t>
+          <t>Dundee Corporation</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -11952,7 +11944,7 @@
         </is>
       </c>
       <c r="H34" s="21" t="n">
-        <v>1.038413084209085</v>
+        <v>1.037415316740448</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -11961,31 +11953,31 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>DC-A.TO</t>
+          <t>120240.KQ</t>
         </is>
       </c>
       <c r="D35" s="17" t="inlineStr">
         <is>
-          <t>Dundee Corporation</t>
+          <t>Daejung Chemicals &amp; Metals Co.,Ltd.</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F35" s="19" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H35" s="21" t="n">
-        <v>1.037415316740448</v>
+        <v>1.028314476927255</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -11994,31 +11986,31 @@
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>120240.KQ</t>
+          <t>KROS</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr">
         <is>
-          <t>Daejung Chemicals &amp; Metals Co.,Ltd.</t>
+          <t>Keros Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="G36" s="20" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H36" s="21" t="n">
-        <v>1.028314476927255</v>
+        <v>1.026379500408792</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -12027,31 +12019,31 @@
       </c>
       <c r="C37" s="16" t="inlineStr">
         <is>
-          <t>KROS</t>
+          <t>JAMESWARREN.BO</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr">
         <is>
-          <t>Keros Therapeutics, Inc.</t>
+          <t>James Warren Tea Limited</t>
         </is>
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F37" s="19" t="inlineStr">
         <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="G37" s="22" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H37" s="21" t="n">
-        <v>1.026379500408792</v>
+        <v>1.026371412960481</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -12060,12 +12052,12 @@
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>JAMESWARREN.BO</t>
+          <t>PRIMEPRO.BO</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr">
         <is>
-          <t>James Warren Tea Limited</t>
+          <t>Prime Property Development Corporation Limited</t>
         </is>
       </c>
       <c r="E38" s="18" t="inlineStr">
@@ -12075,16 +12067,16 @@
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H38" s="21" t="n">
-        <v>1.026371412960481</v>
+        <v>1.025704637199411</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -12093,22 +12085,22 @@
       </c>
       <c r="C39" s="16" t="inlineStr">
         <is>
-          <t>PRIMEPRO.BO</t>
+          <t>035610.KQ</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
         <is>
-          <t>Prime Property Development Corporation Limited</t>
+          <t>Solborn, Inc.</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G39" s="22" t="inlineStr">
@@ -12117,7 +12109,7 @@
         </is>
       </c>
       <c r="H39" s="21" t="n">
-        <v>1.025704637199411</v>
+        <v>1.022307753250712</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -12126,22 +12118,22 @@
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>6986.T</t>
+          <t>BMKS3.SA</t>
         </is>
       </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
-          <t>Futaba Corporation</t>
+          <t>Bicicletas Monark S.A.</t>
         </is>
       </c>
       <c r="E40" s="18" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G40" s="22" t="inlineStr">
@@ -12150,7 +12142,7 @@
         </is>
       </c>
       <c r="H40" s="21" t="n">
-        <v>1.024063963285166</v>
+        <v>1.021626419869399</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -12159,31 +12151,31 @@
       </c>
       <c r="C41" s="16" t="inlineStr">
         <is>
-          <t>035610.KQ</t>
+          <t>6907.T</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
         <is>
-          <t>Solborn, Inc.</t>
+          <t>GEOMATEC Co., Ltd.</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F41" s="19" t="inlineStr">
         <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="G41" s="22" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H41" s="21" t="n">
-        <v>1.022307753250712</v>
+        <v>1.020637828704802</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -12192,31 +12184,31 @@
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>BMKS3.SA</t>
+          <t>4301.T</t>
         </is>
       </c>
       <c r="D42" s="17" t="inlineStr">
         <is>
-          <t>Bicicletas Monark S.A.</t>
+          <t>Amuse Inc.</t>
         </is>
       </c>
       <c r="E42" s="18" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="G42" s="22" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H42" s="21" t="n">
-        <v>1.021626419869399</v>
+        <v>1.019706548899006</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -12225,31 +12217,31 @@
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>6907.T</t>
+          <t>0114.HK</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
         <is>
-          <t>GEOMATEC Co., Ltd.</t>
+          <t>Herald Holdings Limited</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="G43" s="20" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="H43" s="21" t="n">
-        <v>1.020637828704802</v>
+        <v>1.012616484378791</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -12258,12 +12250,12 @@
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>4301.T</t>
+          <t>7722.T</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>Amuse Inc.</t>
+          <t>Kokusai Co., Ltd.</t>
         </is>
       </c>
       <c r="E44" s="18" t="inlineStr">
@@ -12273,7 +12265,7 @@
       </c>
       <c r="F44" s="19" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G44" s="20" t="inlineStr">
@@ -12282,7 +12274,7 @@
         </is>
       </c>
       <c r="H44" s="21" t="n">
-        <v>1.019706548899006</v>
+        <v>1.01125503470177</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -12291,31 +12283,31 @@
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>0114.HK</t>
+          <t>3798.HK</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>Herald Holdings Limited</t>
+          <t>Homeland Interactive Technology Ltd.</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F45" s="19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="G45" s="18" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H45" s="21" t="n">
-        <v>1.012616484378791</v>
+        <v>1.010269682038608</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -12324,31 +12316,31 @@
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>7722.T</t>
+          <t>BENGALT.BO</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>Kokusai Co., Ltd.</t>
+          <t>Bengal Tea &amp; Fabrics Limited</t>
         </is>
       </c>
       <c r="E46" s="18" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="G46" s="20" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="H46" s="21" t="n">
-        <v>1.01125503470177</v>
+        <v>1.008569295693687</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -12357,22 +12349,22 @@
       </c>
       <c r="C47" s="16" t="inlineStr">
         <is>
-          <t>3798.HK</t>
+          <t>7871.T</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>Homeland Interactive Technology Ltd.</t>
+          <t>Fukuvi Chemical Industry Co.,Ltd.</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F47" s="19" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G47" s="22" t="inlineStr">
@@ -12381,7 +12373,7 @@
         </is>
       </c>
       <c r="H47" s="21" t="n">
-        <v>1.010269682038608</v>
+        <v>1.003220044875006</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -12390,31 +12382,31 @@
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>BENGALT.BO</t>
+          <t>0559.HK</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t>Bengal Tea &amp; Fabrics Limited</t>
+          <t>DeTai New Energy Group Limited</t>
         </is>
       </c>
       <c r="E48" s="18" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F48" s="19" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="G48" s="18" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H48" s="21" t="n">
-        <v>1.008569295693687</v>
+        <v>1.002930655934327</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -12423,31 +12415,31 @@
       </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
-          <t>0559.HK</t>
+          <t>036190.KQ</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
         <is>
-          <t>DeTai New Energy Group Limited</t>
+          <t>Geumhwa Plant Service &amp; Construction Co., Ltd.</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F49" s="19" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="G49" s="22" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="G49" s="20" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H49" s="21" t="n">
-        <v>1.002930655934327</v>
+        <v>1.002562672083327</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -12456,22 +12448,22 @@
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>036190.KQ</t>
+          <t>FPIP.ST</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t>Geumhwa Plant Service &amp; Construction Co., Ltd.</t>
+          <t>Formpipe Software AB (publ)</t>
         </is>
       </c>
       <c r="E50" s="18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G50" s="20" t="inlineStr">
@@ -12480,7 +12472,7 @@
         </is>
       </c>
       <c r="H50" s="21" t="n">
-        <v>1.002562672083327</v>
+        <v>0.9979808062005222</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -12489,31 +12481,31 @@
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>FPIP.ST</t>
+          <t>1V5.F</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
         <is>
-          <t>Formpipe Software AB (publ)</t>
+          <t>Zaklady Azotowe Pulawy S.A.</t>
         </is>
       </c>
       <c r="E51" s="18" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F51" s="19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="G51" s="20" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="G51" s="22" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H51" s="21" t="n">
-        <v>0.9979808062005222</v>
+        <v>0.9966682445966406</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -12522,23 +12514,21 @@
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>1V5.F</t>
+          <t>IGAR.JK</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t>Zaklady Azotowe Pulawy S.A.</t>
+          <t>PT Champion Pacific Indonesia Tbk</t>
         </is>
       </c>
       <c r="E52" s="18" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="n">
+        <v/>
       </c>
       <c r="G52" s="22" t="inlineStr">
         <is>
@@ -12546,7 +12536,7 @@
         </is>
       </c>
       <c r="H52" s="21" t="n">
-        <v>0.9966682445966406</v>
+        <v>0.9964378654420601</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -12555,21 +12545,23 @@
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
-          <t>IGAR.JK</t>
+          <t>6912.KL</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
         <is>
-          <t>PT Champion Pacific Indonesia Tbk</t>
+          <t>Pasdec Holdings Bhd</t>
         </is>
       </c>
       <c r="E53" s="18" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="F53" s="19" t="n">
-        <v/>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
       </c>
       <c r="G53" s="22" t="inlineStr">
         <is>
@@ -12577,7 +12569,7 @@
         </is>
       </c>
       <c r="H53" s="21" t="n">
-        <v>0.9964378654420601</v>
+        <v>0.9943177685727069</v>
       </c>
     </row>
   </sheetData>
@@ -13145,504 +13137,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>#28    7871.T    Fukuvi Chemical Industry Co.,Ltd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="36" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="D3" s="23" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="25" t="n">
-        <v>1.045323432299752</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Building Products</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>Micro Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="28" t="n">
-        <v>113765049.2331648</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="n">
-        <v>253081380.5738926</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="30" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="n">
-        <v>0.5841441591112785</v>
-      </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="n">
-        <v>0.7412463758519754</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="30" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="n">
-        <v>0.4874634266054609</v>
-      </c>
-      <c r="D22" s="30" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="30" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D23" s="30" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="30" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="n">
-        <v>0.6827490000000001</v>
-      </c>
-      <c r="D24" s="30" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="30" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="n">
-        <v>0.6262906567788207</v>
-      </c>
-      <c r="D25" s="30" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="30" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="n">
-        <v>0.45730183</v>
-      </c>
-      <c r="D28" s="30" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="32" t="n">
-        <v>104.0366695431652</v>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="n">
-        <v>2.052</v>
-      </c>
-      <c r="D29" s="30" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D30" s="30" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="n">
-        <v>10.857278</v>
-      </c>
-      <c r="D31" s="30" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="n">
-        <v>7.743</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="n">
-        <v>0.44951963</v>
-      </c>
-      <c r="D32" s="30" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="32" t="n">
-        <v>46.144</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="n">
-        <v>19.0416985247412</v>
-      </c>
-      <c r="D33" s="30" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="30" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="32" t="n">
-        <v>68.56641286184274</v>
-      </c>
-      <c r="D34" s="30" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="30" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="n">
-        <v>2.026766710219295</v>
-      </c>
-      <c r="D35" s="30" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="n">
-        <v>18.83017191050615</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="34" t="inlineStr">
-        <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="34" t="inlineStr">
-        <is>
-          <t>·  Sub-book  (P/B 0.46)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="34" t="inlineStr">
-        <is>
-          <t>·  Insider-aligned  (46% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; first-positive: FCF; under-priced vs fundamentals; cash 74% of mcap; cash &gt; EV (2.03x, net cash 69% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="35" t="n"/>
-      <c r="B48" s="35" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="35" t="n"/>
-      <c r="F48" s="35" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 28 of 50</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00707070"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13657,7 +13151,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#29    9983.HK    Central China New Life Limited</t>
+          <t>#28    9983.HK    Central China New Life Limited</t>
         </is>
       </c>
     </row>
@@ -14093,7 +13587,7 @@
     <row r="44">
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 29 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 28 of 50</t>
         </is>
       </c>
     </row>
@@ -14120,7 +13614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -14141,7 +13635,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#30    NPK.BK    New Plus Knitting Public Company Limited</t>
+          <t>#29    NPK.BK    New Plus Knitting Public Company Limited</t>
         </is>
       </c>
     </row>
@@ -14589,7 +14083,7 @@
     <row r="50">
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 30 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 29 of 50</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -14639,7 +14133,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#31    MDX.BK    MDX Public Company Limited</t>
+          <t>#30    MDX.BK    MDX Public Company Limited</t>
         </is>
       </c>
     </row>
@@ -15080,7 +14574,7 @@
     <row r="45">
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 31 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 30 of 50</t>
         </is>
       </c>
     </row>
@@ -15108,7 +14602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -15129,7 +14623,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#32    DC-A.TO    Dundee Corporation</t>
+          <t>#31    DC-A.TO    Dundee Corporation</t>
         </is>
       </c>
     </row>
@@ -15411,10 +14905,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>5.040549715944025</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -15556,7 +15048,7 @@
     <row r="43">
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 32 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 31 of 50</t>
         </is>
       </c>
     </row>
@@ -15570,6 +15062,498 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00707070"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#32    120240.KQ    Daejung Chemicals &amp; Metals Co.,Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="n">
+        <v>1.028314476927255</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Micro Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="n">
+        <v>61744015.19890881</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="n">
+        <v>74515427.36626884</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Daejung Chemicals reagent/battery materials, 3.4 pct yield, P/S 0.88, Value-Up beneficiary candidate (low PBR Korean materials)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>0.5492740281577365</v>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>0.6682831864399906</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>0.5028365966810432</v>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D23" s="30" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="n">
+        <v>0.81486</v>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>0.4016712189628891</v>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="n">
+        <v>0.5449940720767228</v>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="n">
+        <v>85.9174931594461</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="n">
+        <v>1.059317467710319</v>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="n">
+        <v>-3.38968499547607</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="n">
+        <v>2.36836202849494</v>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="n">
+        <v>17.61454268888295</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="n">
+        <v>19.77090424445142</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>0.8796080168298662</v>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n">
+        <v>12.00585788907265</v>
+      </c>
+      <c r="D33" s="30" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="n">
+        <v>76.18977565250363</v>
+      </c>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="32" t="n">
+        <v>23.42328269392889</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>3.50046292725338</v>
+      </c>
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="32" t="n">
+        <v>4.056025198740929</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>growth-flip; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.3x); cash 83% of mcap; cash &gt; EV (3.50x, net cash 76% mcap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1"/>
+    <row r="45" ht="18" customHeight="1"/>
+    <row r="48">
+      <c r="A48" s="35" t="n"/>
+      <c r="B48" s="35" t="n"/>
+      <c r="C48" s="35" t="n"/>
+      <c r="D48" s="35" t="n"/>
+      <c r="E48" s="35" t="n"/>
+      <c r="F48" s="35" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 32 of 50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
@@ -15603,7 +15587,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#33    120240.KQ    Daejung Chemicals &amp; Metals Co.,Ltd.</t>
+          <t>#33    KROS    Keros Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -15621,9 +15605,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -15632,7 +15616,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.028314476927255</v>
+        <v>1.026379500408792</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -15650,7 +15634,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
     </row>
@@ -15662,7 +15646,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
     </row>
@@ -15672,8 +15656,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v/>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Biotechnology</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -15684,7 +15670,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15681,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>61744015.19890881</v>
+        <v>217512272</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -15705,7 +15691,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>74515427.36626884</v>
+        <v>244061000</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -15716,7 +15702,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
     </row>
@@ -15730,7 +15716,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Daejung Chemicals reagent/battery materials, 3.4 pct yield, P/S 0.88, Value-Up beneficiary candidate (low PBR Korean materials)</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15737,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.5492740281577365</v>
+        <v>0.5451932503585999</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -15759,7 +15745,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.6682831864399906</v>
+        <v>0.6981519940000001</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -15769,7 +15755,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.5028365966810432</v>
+        <v>0.5716070773780287</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -15777,7 +15763,7 @@
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -15787,7 +15773,7 @@
         </is>
       </c>
       <c r="C23" s="21" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
@@ -15805,7 +15791,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.81486</v>
+        <v>0.837901</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -15813,7 +15799,7 @@
         </is>
       </c>
       <c r="E24" s="21" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -15823,7 +15809,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.4016712189628891</v>
+        <v>0.4395225067843441</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -15831,7 +15817,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -15848,7 +15834,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.5449940720767228</v>
+        <v>0.75924003</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -15856,7 +15842,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>85.9174931594461</v>
+        <v>127.0432475398032</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -15866,7 +15852,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>1.059317467710319</v>
+        <v>0.451</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -15874,7 +15860,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>-3.38968499547607</v>
+        <v>-3.916326471524943</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -15894,7 +15880,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>17.61454268888295</v>
+        <v>207.2668711656441</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -15914,7 +15900,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>19.77090424445142</v>
+        <v>28.30357984274423</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -15924,17 +15910,15 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>0.8796080168298662</v>
+        <v>6.5551286</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
           <t>Insider ownership (%)</t>
         </is>
       </c>
-      <c r="E32" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E32" s="32" t="n">
+        <v>3.641</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -15944,7 +15928,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>12.00585788907265</v>
+        <v>36.66783771232035</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -15964,7 +15948,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>76.18977565250363</v>
+        <v>135.4560479850007</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -15972,7 +15956,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>23.42328269392889</v>
+        <v>6774.957746478873</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -15981,8 +15965,10 @@
           <t>Cash / EV (x)</t>
         </is>
       </c>
-      <c r="C35" s="21" t="n">
-        <v>3.50046292725338</v>
+      <c r="C35" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -15990,7 +15976,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>4.056025198740929</v>
+        <v>-25.16036920995456</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -16003,21 +15989,21 @@
     <row r="38" ht="16" customHeight="1">
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
+          <t>·  Negative enterprise value</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.54)</t>
+          <t>·  Sub-book  (P/B 0.76)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -16031,7 +16017,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.3x); cash 83% of mcap; cash &gt; EV (3.50x, net cash 76% mcap)</t>
+          <t>growth-flip; first-positive: FCF/EBITDA/CFO/NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cash 138% of mcap</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16083,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#34    KROS    Keros Therapeutics, Inc.</t>
+          <t>#34    JAMESWARREN.BO    James Warren Tea Limited</t>
         </is>
       </c>
     </row>
@@ -16115,9 +16101,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -16126,7 +16112,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.026379500408792</v>
+        <v>1.026371412960481</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -16144,7 +16130,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -16156,7 +16142,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
     </row>
@@ -16166,10 +16152,8 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
+      <c r="B8" s="27" t="n">
+        <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -16180,7 +16164,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -16191,7 +16175,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>217512272</v>
+        <v>9864006.841266451</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -16201,7 +16185,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>244061000</v>
+        <v>11593267.25481078</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -16212,7 +16196,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
     </row>
@@ -16226,7 +16210,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>James Warren Tea Assam estates, debt-free, Goenka-family but clean; illiquid but no pledging/RPT red flags</t>
         </is>
       </c>
     </row>
@@ -16247,7 +16231,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.5451932503585999</v>
+        <v>0.5443150862636589</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -16255,7 +16239,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.6981519940000001</v>
+        <v>0.765272814</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -16265,7 +16249,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.5716070773780287</v>
+        <v>0.5697671406427199</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -16273,7 +16257,7 @@
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -16301,7 +16285,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.837901</v>
+        <v>0.951447</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -16309,7 +16293,7 @@
         </is>
       </c>
       <c r="E24" s="21" t="n">
-        <v>1.3</v>
+        <v>1.1428</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -16319,7 +16303,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.4395225067843441</v>
+        <v>0.4740175575093411</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -16327,7 +16311,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -16344,7 +16328,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.75924003</v>
+        <v>0.42363593</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -16352,7 +16336,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>127.0432475398032</v>
+        <v>148.7221286953815</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -16362,7 +16346,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>0.451</v>
+        <v>-0.4212200061235884</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -16370,7 +16354,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>-3.916326471524943</v>
+        <v>-1.697357851701097</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -16390,7 +16374,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>207.2668711656441</v>
+        <v>100.1085295110647</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -16399,10 +16383,8 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C31" s="21" t="n">
+        <v>7.5967836</v>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -16410,7 +16392,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>28.30357984274423</v>
+        <v>75.07572069879387</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -16420,7 +16402,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>6.5551286</v>
+        <v>0.84739184</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -16428,7 +16410,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>3.641</v>
+        <v>70.70600400000001</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -16438,7 +16420,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>36.66783771232035</v>
+        <v>21.04993719079012</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -16458,7 +16440,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>135.4560479850007</v>
+        <v>133.0074064947872</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -16466,7 +16448,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>6774.957746478873</v>
+        <v>-2.2457207058357</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -16486,7 +16468,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>-25.16036920995456</v>
+        <v>-17.42370430824755</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -16499,21 +16481,21 @@
     <row r="38" ht="16" customHeight="1">
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>·  Negative enterprise value</t>
+          <t>·  Sub-book  (P/B 0.42)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.76)</t>
+          <t>·  Insider-aligned  (71% insider)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -16527,7 +16509,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; first-positive: FCF/EBITDA/CFO/NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cash 138% of mcap</t>
+          <t>growth-flip; first-positive: FCF/CFO; accelerating sales; under-priced vs fundamentals; cash 133% of mcap</t>
         </is>
       </c>
     </row>
@@ -16579,7 +16561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -16593,7 +16575,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#35    JAMESWARREN.BO    James Warren Tea Limited</t>
+          <t>#35    PRIMEPRO.BO    Prime Property Development Corporation Limited</t>
         </is>
       </c>
     </row>
@@ -16611,9 +16593,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -16622,7 +16604,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.026371412960481</v>
+        <v>1.025704637199411</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -16652,7 +16634,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
     </row>
@@ -16685,7 +16667,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>9864006.841266451</v>
+        <v>5849265.35102427</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -16695,7 +16677,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>11593267.25481078</v>
+        <v>7881841.602735221</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -16720,7 +16702,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>James Warren Tea Assam estates, debt-free, Goenka-family but clean; illiquid but no pledging/RPT red flags</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -16741,7 +16723,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.5443150862636589</v>
+        <v>0.598439906777297</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -16749,7 +16731,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.765272814</v>
+        <v>0.7497937540706353</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -16759,7 +16741,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.5697671406427199</v>
+        <v>0.4263456214566903</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -16767,7 +16749,7 @@
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -16777,7 +16759,7 @@
         </is>
       </c>
       <c r="C23" s="21" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
@@ -16795,7 +16777,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.951447</v>
+        <v>0.864779</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -16813,7 +16795,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.4740175575093411</v>
+        <v>0.342946360360744</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -16821,7 +16803,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -16838,7 +16820,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.42363593</v>
+        <v>0.519722</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -16846,7 +16828,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>148.7221286953815</v>
+        <v>161.6763154080468</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -16856,7 +16838,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>-0.4212200061235884</v>
+        <v>1.191</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -16864,7 +16846,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>-1.697357851701097</v>
+        <v>-20.46235521235521</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -16873,10 +16855,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>17.57269811659193</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -16884,7 +16864,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>100.1085295110647</v>
+        <v>6.37463410171972</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -16894,7 +16874,7 @@
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>7.5967836</v>
+        <v>2.2651098</v>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -16902,7 +16882,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>75.07572069879387</v>
+        <v>34.267</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -16912,7 +16892,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>0.84739184</v>
+        <v>0.74211913</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -16920,7 +16900,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>70.70600400000001</v>
+        <v>79.893</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -16930,7 +16910,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>21.04993719079012</v>
+        <v>10.16076330443342</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -16950,7 +16930,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>133.0074064947872</v>
+        <v>119.481517571293</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -16958,7 +16938,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>-2.2457207058357</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -16967,10 +16947,8 @@
           <t>Cash / EV (x)</t>
         </is>
       </c>
-      <c r="C35" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C35" s="21" t="n">
+        <v>1.190130936093773</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -16978,7 +16956,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>-17.42370430824755</v>
+        <v>-39.05670647300728</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -16991,71 +16969,79 @@
     <row r="38" ht="16" customHeight="1">
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.42)</t>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (71% insider)</t>
+          <t>·  Graham net-net  (mcap &lt; NCAV)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+          <t>·  Sub-book  (P/B 0.52)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (80% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; first-positive: FCF/CFO; accelerating sales; under-priced vs fundamentals; cash 133% of mcap</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>growth-flip; first-positive: FCF/CFO; under-priced vs fundamentals; Graham net-net (mcap 0.62x NCAV); cash 119% of mcap; cash &gt; EV (1.19x, net cash 119% mcap)</t>
+        </is>
+      </c>
+    </row>
     <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="35" t="n"/>
-      <c r="B48" s="35" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="35" t="n"/>
-      <c r="F48" s="35" t="n"/>
-    </row>
+    <row r="46" ht="18" customHeight="1"/>
     <row r="49">
-      <c r="B49" s="23" t="inlineStr">
+      <c r="A49" s="35" t="n"/>
+      <c r="B49" s="35" t="n"/>
+      <c r="C49" s="35" t="n"/>
+      <c r="D49" s="35" t="n"/>
+      <c r="E49" s="35" t="n"/>
+      <c r="F49" s="35" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="23" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 35 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B44:E46"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -17085,7 +17071,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#36    PRIMEPRO.BO    Prime Property Development Corporation Limited</t>
+          <t>#36    035610.KQ    Solborn, Inc.</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17100,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.025704637199411</v>
+        <v>1.022307753250712</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -17132,7 +17118,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
@@ -17144,7 +17130,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
     </row>
@@ -17166,7 +17152,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -17177,7 +17163,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>5849265.35102427</v>
+        <v>59203626.18787384</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -17187,7 +17173,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>7881841.602735221</v>
+        <v>85769277.6876678</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -17198,7 +17184,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
@@ -17233,7 +17219,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.598439906777297</v>
+        <v>0.5679487518059509</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -17241,7 +17227,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.7497937540706353</v>
+        <v>0.7860699573532647</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -17251,7 +17237,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.4263456214566903</v>
+        <v>0.3840068865213544</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -17287,7 +17273,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.864779</v>
+        <v>0.6907720000000001</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -17295,7 +17281,7 @@
         </is>
       </c>
       <c r="E24" s="21" t="n">
-        <v>1.1428</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -17305,7 +17291,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.342946360360744</v>
+        <v>0.4338510468179886</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -17330,7 +17316,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.519722</v>
+        <v>0.4404573070670534</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -17338,7 +17324,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>161.6763154080468</v>
+        <v>165.9658148252666</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -17348,7 +17334,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>1.191</v>
+        <v>0.073</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -17356,7 +17342,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>-20.46235521235521</v>
+        <v>-2.865374817272523</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -17365,8 +17351,10 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="21" t="n">
-        <v>17.57269811659193</v>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -17374,7 +17362,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>6.37463410171972</v>
+        <v>197.6613890777809</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -17383,8 +17371,10 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n">
-        <v>2.2651098</v>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -17392,7 +17382,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>34.267</v>
+        <v>49.30611257990332</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -17402,7 +17392,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>0.74211913</v>
+        <v>0.6902661</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -17410,7 +17400,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>79.893</v>
+        <v>60.76000000000001</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -17420,7 +17410,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>10.16076330443342</v>
+        <v>18.55545599223466</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -17440,7 +17430,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>119.481517571293</v>
+        <v>194.1190612753346</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -17448,7 +17438,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>-100</v>
+        <v>12.96488373879826</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -17458,7 +17448,7 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>1.190130936093773</v>
+        <v>26.15700278552129</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -17466,7 +17456,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>-39.05670647300728</v>
+        <v>-6.30872483221476</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -17493,14 +17483,14 @@
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.52)</t>
+          <t>·  Sub-book  (P/B 0.44)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (80% insider)</t>
+          <t>·  Insider-aligned  (61% insider)</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17504,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; first-positive: FCF/CFO; under-priced vs fundamentals; Graham net-net (mcap 0.62x NCAV); cash 119% of mcap; cash &gt; EV (1.19x, net cash 119% mcap)</t>
+          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.1x); Graham net-net (mcap 0.60x NCAV); cash 197% of mcap; cash &gt; EV (26.16x, net cash 194% mcap)</t>
         </is>
       </c>
     </row>
@@ -18075,6 +18065,480 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#37    BMKS3.SA    Bicicletas Monark S.A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="n">
+        <v>1.021626419869399</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Hotels, Restaurants &amp; Leisure</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Nano Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="n">
+        <v>32512732.66926241</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="n">
+        <v>2569429.631665349</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>0.5886747775668669</v>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>0.786003003434291</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>0.4950542767762861</v>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D23" s="30" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>0.988</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>1.1714</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>0.4686882351493481</v>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="n">
+        <v>0.8185883275185453</v>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="n">
+        <v>80.74801441188816</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="n">
+        <v>0.0673248387031531</v>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="n">
+        <v>-1.64357947535546</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="n">
+        <v>219.6850215273057</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="n">
+        <v>2.8401284</v>
+      </c>
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="n">
+        <v>739.6663924003291</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>12.65367701398758</v>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n">
+        <v>34.93411670436354</v>
+      </c>
+      <c r="D33" s="30" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="n">
+        <v>96.07488003807457</v>
+      </c>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="32" t="n">
+        <v>-11.25199150292087</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>24.74883905090872</v>
+      </c>
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="32" t="n">
+        <v>33.44708548785322</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.82)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (88% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="n"/>
+      <c r="B42" s="35" t="n"/>
+      <c r="C42" s="35" t="n"/>
+      <c r="D42" s="35" t="n"/>
+      <c r="E42" s="35" t="n"/>
+      <c r="F42" s="35" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 37 of 50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00707070"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -18089,7 +18553,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#37    6986.T    Futaba Corporation</t>
+          <t>#38    6907.T    GEOMATEC Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -18107,9 +18571,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -18118,7 +18582,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.024063963285166</v>
+        <v>1.020637828704802</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -18183,7 +18647,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>143323809.5378494</v>
+        <v>30526752.73633003</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -18193,7 +18657,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>267969232.6202774</v>
+        <v>32923308.73264465</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -18218,7 +18682,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>GEOMATEC - CEO Matsuzaki 23% insider, 3.1% yield, vacuum thin-film coatings, market re-rating in progress on TSE reform</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18703,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.5754534350025499</v>
+        <v>0.6160387089186</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -18247,7 +18711,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.9451284280000001</v>
+        <v>0.5597039380903739</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -18257,7 +18721,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.4599259109114359</v>
+        <v>0.5421481298372796</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -18265,7 +18729,7 @@
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -18275,7 +18739,7 @@
         </is>
       </c>
       <c r="C23" s="21" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
@@ -18283,7 +18747,7 @@
         </is>
       </c>
       <c r="E23" s="21" t="n">
-        <v>0.989</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -18293,7 +18757,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.737268</v>
+        <v>0.6261910000000001</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -18301,7 +18765,7 @@
         </is>
       </c>
       <c r="E24" s="21" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -18311,7 +18775,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.6653805736245242</v>
+        <v>0.3625493263241238</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -18319,7 +18783,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -18336,7 +18800,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.27435786</v>
+        <v>0.46522254</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -18344,7 +18808,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>168.4364948036254</v>
+        <v>72.64296941092827</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -18354,17 +18818,15 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>1.17</v>
+        <v>6.819</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
           <t>Net debt / EBITDA (x)</t>
         </is>
       </c>
-      <c r="E29" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E29" s="21" t="n">
+        <v>-2.717956539716084</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -18373,20 +18835,16 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>3.766985990111552</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
           <t>ROCE (%)</t>
         </is>
       </c>
-      <c r="E30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E30" s="32" t="n">
+        <v>4.96206817919293</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -18396,7 +18854,7 @@
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>9.115372000000001</v>
+        <v>7.662788</v>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -18404,7 +18862,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>-2.964</v>
+        <v>10.30465457748786</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -18414,7 +18872,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>0.53485173</v>
+        <v>0.7752471</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -18422,7 +18880,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>23.332001</v>
+        <v>25.320998</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -18432,7 +18890,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>12.66687543786093</v>
+        <v>2.16867827999933</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -18452,17 +18910,15 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>121.1150982979056</v>
+        <v>29.21524166792663</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
           <t>Rev YoY (TTM, %)</t>
         </is>
       </c>
-      <c r="E34" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E34" s="32" t="n">
+        <v>14.66329044442543</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -18472,7 +18928,7 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>17.8242691121048</v>
+        <v>2.238130271207507</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -18480,7 +18936,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>33.17683926494909</v>
+        <v>-16.44908616187989</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -18500,14 +18956,14 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Graham net-net  (mcap &lt; NCAV)</t>
+          <t>·  Sub-book  (P/B 0.47)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.27)</t>
+          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -18521,7 +18977,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>under-priced vs fundamentals; Graham net-net (mcap 0.59x NCAV); cash 121% of mcap; cash &gt; EV (17.82x, net cash 121% mcap)</t>
+          <t>growth-flip; first-positive: FCF/EBITDA/CFO/NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 3.8x); cash 66% of mcap; cash &gt; EV (2.24x, net cash 29% mcap)</t>
         </is>
       </c>
     </row>
@@ -18538,7 +18994,7 @@
     <row r="49">
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 37 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 38 of 50</t>
         </is>
       </c>
     </row>
@@ -18566,7 +19022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -18587,7 +19043,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#38    035610.KQ    Solborn, Inc.</t>
+          <t>#39    4301.T    Amuse Inc.</t>
         </is>
       </c>
     </row>
@@ -18605,9 +19061,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -18616,7 +19072,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.022307753250712</v>
+        <v>1.019706548899006</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -18634,7 +19090,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
@@ -18646,7 +19102,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
     </row>
@@ -18656,8 +19112,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v/>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -18668,7 +19126,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
     </row>
@@ -18679,7 +19137,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>59203626.18787384</v>
+        <v>182271112.0044422</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -18689,7 +19147,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>85769277.6876678</v>
+        <v>425102384.579368</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -18700,7 +19158,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
     </row>
@@ -18714,7 +19172,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>Amuse talent agency, net cash, Southern All Stars IP; conservative balance sheet, no parent overhang, standard JP small-cap</t>
         </is>
       </c>
     </row>
@@ -18735,7 +19193,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.5679487518059509</v>
+        <v>0.5695956646156826</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -18743,7 +19201,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.7860699573532647</v>
+        <v>0.674116822302693</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -18753,7 +19211,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.3840068865213544</v>
+        <v>0.4634846016414016</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -18761,7 +19219,7 @@
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -18771,7 +19229,7 @@
         </is>
       </c>
       <c r="C23" s="21" t="n">
-        <v>0.84</v>
+        <v>0.7</v>
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
@@ -18789,7 +19247,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.6907720000000001</v>
+        <v>0.552356</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -18797,7 +19255,7 @@
         </is>
       </c>
       <c r="E24" s="21" t="n">
-        <v>1.2</v>
+        <v>1.1428</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -18807,7 +19265,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.4338510468179886</v>
+        <v>0.4361122345294578</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -18815,7 +19273,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -18832,7 +19290,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.4404573070670534</v>
+        <v>0.8071404</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -18840,7 +19298,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>165.9658148252666</v>
+        <v>89.14948456657699</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -18850,7 +19308,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>0.073</v>
+        <v>0.063</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -18858,7 +19316,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>-2.865374817272523</v>
+        <v>-8.223498694516971</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -18878,7 +19336,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>197.6613890777809</v>
+        <v>55.73164289487585</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -18887,10 +19345,8 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C31" s="21" t="n">
+        <v>10.857522</v>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -18898,7 +19354,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>49.30611257990332</v>
+        <v>5.61698882468541</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -18908,7 +19364,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>0.6902661</v>
+        <v>0.4197273</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -18916,7 +19372,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>60.76000000000001</v>
+        <v>40.842</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -18926,7 +19382,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>18.55545599223466</v>
+        <v>-6.8706531998538</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -18946,7 +19402,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>194.1190612753346</v>
+        <v>108.6335809149576</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -18954,7 +19410,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>12.96488373879826</v>
+        <v>24.39749694415558</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -18964,7 +19420,7 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>26.15700278552129</v>
+        <v>55.44032493218933</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -18972,7 +19428,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>-6.30872483221476</v>
+        <v>12.26815412258082</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -18992,21 +19448,21 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Graham net-net  (mcap &lt; NCAV)</t>
+          <t>·  Sub-book  (P/B 0.81)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.44)</t>
+          <t>·  Insider-aligned  (41% insider)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (61% insider)</t>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -19020,7 +19476,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.1x); Graham net-net (mcap 0.60x NCAV); cash 197% of mcap; cash &gt; EV (26.16x, net cash 194% mcap)</t>
+          <t>growth-flip; first-positive: CFO; accelerating sales; cheap+grow (EV/EBIT 0.2x); cash 109% of mcap; cash &gt; EV (55.44x, net cash 109% mcap)</t>
         </is>
       </c>
     </row>
@@ -19037,7 +19493,7 @@
     <row r="50">
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 38 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 39 of 50</t>
         </is>
       </c>
     </row>
@@ -19066,14 +19522,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -19087,7 +19543,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#39    BMKS3.SA    Bicicletas Monark S.A.</t>
+          <t>#40    0114.HK    Herald Holdings Limited</t>
         </is>
       </c>
     </row>
@@ -19105,9 +19561,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -19116,7 +19572,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.021626419869399</v>
+        <v>1.012616484378791</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -19134,7 +19590,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19626,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -19181,7 +19637,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>32512732.66926241</v>
+        <v>49366965.57013273</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -19191,7 +19647,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>2569429.631665349</v>
+        <v>89795964.46359158</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -19202,7 +19658,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>2025-09-30</t>
         </is>
       </c>
     </row>
@@ -19216,7 +19672,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>Herald Holdings - Bloch family HK conglomerate (toys+magnetic+watches+investments+others); 48% insider; ~10% dividend yield on 3% payout ratio (cash hoard); cash &gt; EV 8.5x BUT Bloch family has held discount for decades without unlocking</t>
         </is>
       </c>
     </row>
@@ -19237,7 +19693,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.5886747775668669</v>
+        <v>0.7001045122967356</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -19245,7 +19701,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.786003003434291</v>
+        <v>0.7219072332546076</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -19255,7 +19711,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.4950542767762861</v>
+        <v>0.7002090401975003</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -19263,7 +19719,7 @@
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -19281,7 +19737,7 @@
         </is>
       </c>
       <c r="E23" s="21" t="n">
-        <v>0.988</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -19291,7 +19747,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.85</v>
+        <v>0.805323</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -19299,7 +19755,7 @@
         </is>
       </c>
       <c r="E24" s="21" t="n">
-        <v>1.1714</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -19309,7 +19765,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.4686882351493481</v>
+        <v>0.47635344463577</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -19317,7 +19773,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -19334,7 +19790,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.8185883275185453</v>
+        <v>0.63241106</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -19342,7 +19798,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>80.74801441188816</v>
+        <v>105.2860486658501</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -19352,7 +19808,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>0.0673248387031531</v>
+        <v>0.866</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -19360,7 +19816,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>-1.64357947535546</v>
+        <v>-6.185674661445587</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -19369,10 +19825,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>6.508696468667075</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -19380,7 +19834,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>219.6850215273057</v>
+        <v>11.43562016190982</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -19390,7 +19844,7 @@
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>2.8401284</v>
+        <v>8</v>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -19398,7 +19852,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>739.6663924003291</v>
+        <v>7.83866512056205</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -19408,7 +19862,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>12.65367701398758</v>
+        <v>0.5252302</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -19416,7 +19870,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>88</v>
+        <v>48.104998</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -19426,7 +19880,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>34.93411670436354</v>
+        <v>18.71889103961108</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -19446,7 +19900,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>96.07488003807457</v>
+        <v>89.59607465377444</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -19454,7 +19908,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>-11.25199150292087</v>
+        <v>-1.07304976403589</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -19464,7 +19918,7 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>24.74883905090872</v>
+        <v>8.499498359778899</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -19472,7 +19926,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>33.44708548785322</v>
+        <v>40.2511907320183</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -19492,38 +19946,63 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.82)</t>
+          <t>·  Sub-book  (P/B 0.63)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (88% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="35" t="n"/>
-      <c r="B42" s="35" t="n"/>
-      <c r="C42" s="35" t="n"/>
-      <c r="D42" s="35" t="n"/>
-      <c r="E42" s="35" t="n"/>
-      <c r="F42" s="35" t="n"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 39 of 50</t>
+          <t>·  Insider-aligned  (48% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>growth-flip; first-positive: NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.3x); cash 90% of mcap; cash &gt; EV (8.50x, net cash 90% mcap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1"/>
+    <row r="46" ht="18" customHeight="1"/>
+    <row r="49">
+      <c r="A49" s="35" t="n"/>
+      <c r="B49" s="35" t="n"/>
+      <c r="C49" s="35" t="n"/>
+      <c r="D49" s="35" t="n"/>
+      <c r="E49" s="35" t="n"/>
+      <c r="F49" s="35" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 40 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
@@ -19532,496 +20011,7 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00707070"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>#40    6907.T    GEOMATEC Co., Ltd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="D3" s="23" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="25" t="n">
-        <v>1.020637828704802</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Electronic Equipment, Instruments &amp; Components</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>Micro Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="28" t="n">
-        <v>30526752.73633003</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="n">
-        <v>32923308.73264465</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>GEOMATEC - CEO Matsuzaki 23% insider, 3.1% yield, vacuum thin-film coatings, market re-rating in progress on TSE reform</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="30" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="n">
-        <v>0.6160387089186</v>
-      </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="n">
-        <v>0.5597039380903739</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="30" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="n">
-        <v>0.5421481298372796</v>
-      </c>
-      <c r="D22" s="30" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="30" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D23" s="30" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="30" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="n">
-        <v>0.6261910000000001</v>
-      </c>
-      <c r="D24" s="30" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="30" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="n">
-        <v>0.3625493263241238</v>
-      </c>
-      <c r="D25" s="30" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="30" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="n">
-        <v>0.46522254</v>
-      </c>
-      <c r="D28" s="30" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="32" t="n">
-        <v>72.64296941092827</v>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="n">
-        <v>6.819</v>
-      </c>
-      <c r="D29" s="30" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="n">
-        <v>-2.717956539716084</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="n">
-        <v>3.766985990111552</v>
-      </c>
-      <c r="D30" s="30" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="32" t="n">
-        <v>4.96206817919293</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="n">
-        <v>7.662788</v>
-      </c>
-      <c r="D31" s="30" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="n">
-        <v>10.30465457748786</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="n">
-        <v>0.7752471</v>
-      </c>
-      <c r="D32" s="30" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="32" t="n">
-        <v>25.320998</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="n">
-        <v>2.16867827999933</v>
-      </c>
-      <c r="D33" s="30" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="30" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="32" t="n">
-        <v>29.21524166792663</v>
-      </c>
-      <c r="D34" s="30" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="32" t="n">
-        <v>14.66329044442543</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="30" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="n">
-        <v>2.238130271207507</v>
-      </c>
-      <c r="D35" s="30" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="n">
-        <v>-16.44908616187989</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="34" t="inlineStr">
-        <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="34" t="inlineStr">
-        <is>
-          <t>·  Sub-book  (P/B 0.47)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="34" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; first-positive: FCF/EBITDA/CFO/NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 3.8x); cash 66% of mcap; cash &gt; EV (2.24x, net cash 29% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="35" t="n"/>
-      <c r="B48" s="35" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="35" t="n"/>
-      <c r="F48" s="35" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 40 of 50</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B44:E46"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -20051,7 +20041,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#41    4301.T    Amuse Inc.</t>
+          <t>#41    7722.T    Kokusai Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -20080,7 +20070,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.019706548899006</v>
+        <v>1.01125503470177</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -20110,7 +20100,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -20122,7 +20112,7 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Machinery</t>
         </is>
       </c>
     </row>
@@ -20134,7 +20124,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -20145,7 +20135,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>182271112.0044422</v>
+        <v>62835027.53350496</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -20155,7 +20145,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>425102384.579368</v>
+        <v>82321438.99549031</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -20180,7 +20170,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Amuse talent agency, net cash, Southern All Stars IP; conservative balance sheet, no parent overhang, standard JP small-cap</t>
+          <t>Japan TSE PBR&lt;1 reform tailwind; 4.25% dividend yield; 47% insider founder/family; cash &gt; EV</t>
         </is>
       </c>
     </row>
@@ -20201,7 +20191,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.5695956646156826</v>
+        <v>0.6821766345080053</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -20209,7 +20199,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.674116822302693</v>
+        <v>0.5208537749715599</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -20219,7 +20209,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.4634846016414016</v>
+        <v>0.6648070866695266</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -20245,7 +20235,7 @@
         </is>
       </c>
       <c r="E23" s="21" t="n">
-        <v>1</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -20255,7 +20245,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.552356</v>
+        <v>0.667544</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -20263,7 +20253,7 @@
         </is>
       </c>
       <c r="E24" s="21" t="n">
-        <v>1.1428</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -20273,7 +20263,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.4361122345294578</v>
+        <v>0.4980159370211181</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -20281,7 +20271,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -20298,7 +20288,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.8071404</v>
+        <v>0.806884</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -20306,7 +20296,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>89.14948456657699</v>
+        <v>66.209923188082</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -20316,7 +20306,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>0.063</v>
+        <v>2.026</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -20324,7 +20314,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>-8.223498694516971</v>
+        <v>-3.312752560554978</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -20333,10 +20323,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>3.429747363924815</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -20344,7 +20332,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>55.73164289487585</v>
+        <v>22.72889919259904</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -20354,7 +20342,7 @@
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>10.857522</v>
+        <v>6.742991</v>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -20362,7 +20350,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>5.61698882468541</v>
+        <v>12.08064629362137</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -20372,7 +20360,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>0.4197273</v>
+        <v>0.6742491</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -20380,7 +20368,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>40.842</v>
+        <v>47.185</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -20390,7 +20378,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>-6.8706531998538</v>
+        <v>9.080813555616301</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -20410,7 +20398,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>108.6335809149576</v>
+        <v>50.15163900536568</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -20418,7 +20406,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>24.39749694415558</v>
+        <v>28.95813021275008</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -20428,7 +20416,7 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>55.44032493218933</v>
+        <v>1.658077487723985</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -20436,7 +20424,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>12.26815412258082</v>
+        <v>62.56998952112021</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -20463,14 +20451,14 @@
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (41% insider)</t>
+          <t>·  Insider-aligned  (47% insider)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -20484,7 +20472,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; first-positive: CFO; accelerating sales; cheap+grow (EV/EBIT 0.2x); cash 109% of mcap; cash &gt; EV (55.44x, net cash 109% mcap)</t>
+          <t>growth-flip; first-positive: NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 3.4x); cash 78% of mcap; cash &gt; EV (1.66x, net cash 50% mcap)</t>
         </is>
       </c>
     </row>
@@ -20537,7 +20525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -20551,7 +20539,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#42    0114.HK    Herald Holdings Limited</t>
+          <t>#42    3798.HK    Homeland Interactive Technology Ltd.</t>
         </is>
       </c>
     </row>
@@ -20569,9 +20557,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -20580,7 +20568,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.012616484378791</v>
+        <v>1.010269682038608</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -20598,7 +20586,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
     </row>
@@ -20610,7 +20598,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
     </row>
@@ -20622,7 +20610,7 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>Hotels, Restaurants &amp; Leisure</t>
+          <t>Interactive Media &amp; Services</t>
         </is>
       </c>
     </row>
@@ -20634,7 +20622,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
     </row>
@@ -20645,7 +20633,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>49366965.57013273</v>
+        <v>224171789.4849358</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -20655,7 +20643,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>89795964.46359158</v>
+        <v>172106635.0032687</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -20666,7 +20654,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>–</t>
         </is>
       </c>
     </row>
@@ -20680,7 +20668,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Herald Holdings - Bloch family HK conglomerate (toys+magnetic+watches+investments+others); 48% insider; ~10% dividend yield on 3% payout ratio (cash hoard); cash &gt; EV 8.5x BUT Bloch family has held discount for decades without unlocking</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -20701,7 +20689,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.7001045122967356</v>
+        <v>0.6569742743083447</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -20709,7 +20697,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.7219072332546076</v>
+        <v>0.531467836141946</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -20719,7 +20707,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.7002090401975003</v>
+        <v>0.6165931387185373</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -20727,7 +20715,7 @@
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -20745,7 +20733,7 @@
         </is>
       </c>
       <c r="E23" s="21" t="n">
-        <v>0.963</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -20755,7 +20743,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.805323</v>
+        <v>0.8495485218474618</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -20773,7 +20761,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.47635344463577</v>
+        <v>0.4128425191777984</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -20798,15 +20786,17 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.63241106</v>
+        <v>0.9352838172307776</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
           <t>NCAV / mcap (%)</t>
         </is>
       </c>
-      <c r="E28" s="32" t="n">
-        <v>105.2860486658501</v>
+      <c r="E28" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -20816,7 +20806,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>0.866</v>
+        <v>2.330035585822138</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -20824,7 +20814,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>-6.185674661445587</v>
+        <v>-7.225898256848096</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -20833,10 +20823,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>2.041767239331802</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -20844,7 +20832,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>11.43562016190982</v>
+        <v>33.75755216989689</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -20854,7 +20842,7 @@
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -20862,7 +20850,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>7.83866512056205</v>
+        <v>13.1301770234321</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -20872,7 +20860,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>0.5252302</v>
+        <v>1.302516834872044</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -20880,7 +20868,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>48.104998</v>
+        <v>74.694</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -20890,7 +20878,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>18.71889103961108</v>
+        <v>11.29592044426044</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -20910,7 +20898,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>89.59607465377444</v>
+        <v>72.84153319603385</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -20918,7 +20906,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>-1.07304976403589</v>
+        <v>-2.6933510331294</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -20928,7 +20916,7 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>8.499498359778899</v>
+        <v>3.142024571801568</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -20936,7 +20924,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>40.2511907320183</v>
+        <v>18.96552025350472</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -20956,14 +20944,14 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.63)</t>
+          <t>·  Sub-book  (P/B 0.94)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (48% insider)</t>
+          <t>·  Insider-aligned  (75% insider)</t>
         </is>
       </c>
     </row>
@@ -20974,45 +20962,28 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; first-positive: NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.3x); cash 90% of mcap; cash &gt; EV (8.50x, net cash 90% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="46" ht="18" customHeight="1"/>
-    <row r="49">
-      <c r="A49" s="35" t="n"/>
-      <c r="B49" s="35" t="n"/>
-      <c r="C49" s="35" t="n"/>
-      <c r="D49" s="35" t="n"/>
-      <c r="E49" s="35" t="n"/>
-      <c r="F49" s="35" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="23" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="35" t="n"/>
+      <c r="B43" s="35" t="n"/>
+      <c r="C43" s="35" t="n"/>
+      <c r="D43" s="35" t="n"/>
+      <c r="E43" s="35" t="n"/>
+      <c r="F43" s="35" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 42 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
@@ -21021,7 +20992,6 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B44:E46"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -21051,7 +21021,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#43    7722.T    Kokusai Co., Ltd.</t>
+          <t>#43    BENGALT.BO    Bengal Tea &amp; Fabrics Limited</t>
         </is>
       </c>
     </row>
@@ -21069,9 +21039,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -21080,7 +21050,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.01125503470177</v>
+        <v>1.008569295693687</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -21098,7 +21068,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -21110,7 +21080,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
     </row>
@@ -21120,10 +21090,8 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Machinery</t>
-        </is>
+      <c r="B8" s="27" t="n">
+        <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -21134,7 +21102,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -21145,7 +21113,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>62835027.53350496</v>
+        <v>13176510.8988905</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -21155,7 +21123,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>82321438.99549031</v>
+        <v>5534877.479667775</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -21180,7 +21148,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Japan TSE PBR&lt;1 reform tailwind; 4.25% dividend yield; 47% insider founder/family; cash &gt; EV</t>
+          <t>BK Birla group offshoot; tea+fabric conglomerate discount real but check promoter cross-holdings and segment EBIT honesty</t>
         </is>
       </c>
     </row>
@@ -21201,7 +21169,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.6821766345080053</v>
+        <v>0.6591956181004494</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -21209,7 +21177,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.5208537749715599</v>
+        <v>0.8043732309929412</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -21219,7 +21187,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.6648070866695266</v>
+        <v>0.6207698041754764</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -21227,7 +21195,7 @@
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -21245,7 +21213,7 @@
         </is>
       </c>
       <c r="E23" s="21" t="n">
-        <v>0.884</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -21255,7 +21223,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.667544</v>
+        <v>0.918984</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -21273,7 +21241,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.4980159370211181</v>
+        <v>0.4734316608513833</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -21281,7 +21249,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -21298,7 +21266,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.806884</v>
+        <v>0.6265579999999999</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -21306,7 +21274,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>66.209923188082</v>
+        <v>94.33666693235584</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -21316,7 +21284,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>2.026</v>
+        <v>0.5163259892042282</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -21324,7 +21292,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>-3.312752560554978</v>
+        <v>0.3903915671502885</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -21333,8 +21301,10 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="21" t="n">
-        <v>3.429747363924815</v>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -21342,7 +21312,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>22.72889919259904</v>
+        <v>23.06910778751934</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -21352,7 +21322,7 @@
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>6.742991</v>
+        <v>28.11245</v>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -21360,7 +21330,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>12.08064629362137</v>
+        <v>38.54704195248318</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -21370,7 +21340,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>0.6742491</v>
+        <v>2.3937035</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -21378,7 +21348,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>47.185</v>
+        <v>84.797996</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -21388,7 +21358,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>9.080813555616301</v>
+        <v>12.82322950167912</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -21408,7 +21378,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>50.15163900536568</v>
+        <v>92.80615316949594</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -21416,7 +21386,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>28.95813021275008</v>
+        <v>32.22922398597871</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -21426,7 +21396,7 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>1.658077487723985</v>
+        <v>12.54245137388083</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -21434,7 +21404,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>62.56998952112021</v>
+        <v>2.40659480742106</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -21454,21 +21424,21 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.81)</t>
+          <t>·  Sub-book  (P/B 0.63)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (47% insider)</t>
+          <t>·  Insider-aligned  (85% insider)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
+          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -21482,7 +21452,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; first-positive: NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 3.4x); cash 78% of mcap; cash &gt; EV (1.66x, net cash 50% mcap)</t>
+          <t>growth-flip; first-positive: NI; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.6x); cash 99% of mcap; cash &gt; EV (12.54x, net cash 93% mcap)</t>
         </is>
       </c>
     </row>
@@ -21535,7 +21505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -21549,7 +21519,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#44    3798.HK    Homeland Interactive Technology Ltd.</t>
+          <t>#44    7871.T    Fukuvi Chemical Industry Co.,Ltd.</t>
         </is>
       </c>
     </row>
@@ -21578,7 +21548,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.010269682038608</v>
+        <v>1.003220044875006</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -21596,7 +21566,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
     </row>
@@ -21608,7 +21578,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21590,7 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>Interactive Media &amp; Services</t>
+          <t>Building Products</t>
         </is>
       </c>
     </row>
@@ -21632,7 +21602,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -21643,7 +21613,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>224171789.4849358</v>
+        <v>113765049.2331648</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -21653,7 +21623,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>172106635.0032687</v>
+        <v>253081380.5738926</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -21664,7 +21634,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>2025-09-30</t>
         </is>
       </c>
     </row>
@@ -21699,7 +21669,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.6569742743083447</v>
+        <v>0.5606160843709503</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -21707,7 +21677,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.531467836141946</v>
+        <v>0.7412463758519754</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -21717,7 +21687,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.6165931387185373</v>
+        <v>0.4489862772220236</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -21753,7 +21723,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.8495485218474618</v>
+        <v>0.6827490000000001</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -21771,7 +21741,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.4128425191777984</v>
+        <v>0.6262906567788207</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -21779,7 +21749,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -21796,17 +21766,15 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.9352838172307776</v>
+        <v>0.45730183</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
           <t>NCAV / mcap (%)</t>
         </is>
       </c>
-      <c r="E28" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E28" s="32" t="n">
+        <v>104.0366695431652</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -21816,7 +21784,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>2.330035585822138</v>
+        <v>2.052</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -21824,7 +21792,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>-7.225898256848096</v>
+        <v>-3.315803452855246</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -21834,7 +21802,7 @@
         </is>
       </c>
       <c r="C30" s="21" t="n">
-        <v>2.041767239331802</v>
+        <v>6.378690512702079</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -21842,7 +21810,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>33.75755216989689</v>
+        <v>6.31632690273877</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -21852,7 +21820,7 @@
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>23</v>
+        <v>10.857278</v>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -21860,7 +21828,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>13.1301770234321</v>
+        <v>7.743</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -21870,7 +21838,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>1.302516834872044</v>
+        <v>0.44951963</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -21878,7 +21846,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>74.694</v>
+        <v>46.144</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -21888,7 +21856,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>11.29592044426044</v>
+        <v>19.0416985247412</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -21908,7 +21876,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>72.84153319603385</v>
+        <v>68.56641286184274</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -21916,7 +21884,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>-2.6933510331294</v>
+        <v>1.5535486453356</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -21926,7 +21894,7 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>3.142024571801568</v>
+        <v>2.026766710219295</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -21934,7 +21902,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>18.96552025350472</v>
+        <v>18.83017191050615</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -21954,50 +21922,60 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.94)</t>
+          <t>·  Sub-book  (P/B 0.46)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (75% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="34" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="35" t="n"/>
-      <c r="B43" s="35" t="n"/>
-      <c r="C43" s="35" t="n"/>
-      <c r="D43" s="35" t="n"/>
-      <c r="E43" s="35" t="n"/>
-      <c r="F43" s="35" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="23" t="inlineStr">
+          <t>·  Insider-aligned  (46% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>growth-flip; first-positive: FCF; under-priced vs fundamentals; cash 74% of mcap; cash &gt; EV (2.03x, net cash 69% mcap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1"/>
+    <row r="45" ht="18" customHeight="1"/>
+    <row r="48">
+      <c r="A48" s="35" t="n"/>
+      <c r="B48" s="35" t="n"/>
+      <c r="C48" s="35" t="n"/>
+      <c r="D48" s="35" t="n"/>
+      <c r="E48" s="35" t="n"/>
+      <c r="F48" s="35" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 44 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
@@ -22017,7 +21995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -22031,7 +22009,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#45    BENGALT.BO    Bengal Tea &amp; Fabrics Limited</t>
+          <t>#45    0559.HK    DeTai New Energy Group Limited</t>
         </is>
       </c>
     </row>
@@ -22049,9 +22027,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -22060,7 +22038,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.008569295693687</v>
+        <v>1.002930655934327</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -22078,7 +22056,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -22090,7 +22068,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
     </row>
@@ -22100,8 +22078,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v/>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Hotels, Restaurants &amp; Leisure</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -22112,7 +22092,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -22123,7 +22103,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>13176510.8988905</v>
+        <v>8411861.529944658</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -22133,7 +22113,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>5534877.479667775</v>
+        <v>4343410.067886114</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -22144,7 +22124,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>–</t>
         </is>
       </c>
     </row>
@@ -22158,7 +22138,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>BK Birla group offshoot; tea+fabric conglomerate discount real but check promoter cross-holdings and segment EBIT honesty</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -22179,7 +22159,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.6591956181004494</v>
+        <v>0.5865091555171503</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -22187,7 +22167,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.8043732309929412</v>
+        <v>0.8947433522461824</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -22197,7 +22177,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.6207698041754764</v>
+        <v>0.5212014992506679</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -22205,7 +22185,7 @@
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -22215,7 +22195,7 @@
         </is>
       </c>
       <c r="C23" s="21" t="n">
-        <v>0.7</v>
+        <v>0.6599999999999999</v>
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
@@ -22233,7 +22213,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.918984</v>
+        <v>0.614669</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -22241,7 +22221,7 @@
         </is>
       </c>
       <c r="E24" s="21" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -22251,7 +22231,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.4734316608513833</v>
+        <v>0.5535631163043078</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -22259,7 +22239,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -22276,7 +22256,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.6265579999999999</v>
+        <v>0.1392800169025987</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -22284,7 +22264,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>94.33666693235584</v>
+        <v>350.1163327772758</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -22294,7 +22274,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>0.5163259892042282</v>
+        <v>2.042046942853337</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -22302,7 +22282,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>0.3903915671502885</v>
+        <v>0.2857865991741041</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -22311,10 +22291,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>2.311745445771504</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -22322,7 +22300,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>23.06910778751934</v>
+        <v>15.52777868840942</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -22332,7 +22310,7 @@
         </is>
       </c>
       <c r="C31" s="21" t="n">
-        <v>28.11245</v>
+        <v>2.52</v>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -22340,7 +22318,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>38.54704195248318</v>
+        <v>110.2738116223045</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -22350,7 +22328,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>2.3937035</v>
+        <v>1.936695222986074</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -22358,7 +22336,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>84.797996</v>
+        <v>28.063</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -22368,7 +22346,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>12.82322950167912</v>
+        <v>-14.45209640499437</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -22388,7 +22366,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>92.80615316949594</v>
+        <v>394.0657541109062</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -22396,7 +22374,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>32.22922398597871</v>
+        <v>8.865860679332179</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -22406,7 +22384,7 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>12.54245137388083</v>
+        <v>3.604414515392866</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -22414,7 +22392,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>2.40659480742106</v>
+        <v>4.13223364405128</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -22427,70 +22405,45 @@
     <row r="38" ht="16" customHeight="1">
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
+          <t>·  Graham net-net  (mcap &lt; NCAV)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.63)</t>
+          <t>·  Sub-book  (P/B 0.14)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (85% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="34" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; first-positive: NI; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.6x); cash 99% of mcap; cash &gt; EV (12.54x, net cash 93% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="46" ht="18" customHeight="1"/>
-    <row r="49">
-      <c r="A49" s="35" t="n"/>
-      <c r="B49" s="35" t="n"/>
-      <c r="C49" s="35" t="n"/>
-      <c r="D49" s="35" t="n"/>
-      <c r="E49" s="35" t="n"/>
-      <c r="F49" s="35" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="23" t="inlineStr">
+          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="n"/>
+      <c r="B42" s="35" t="n"/>
+      <c r="C42" s="35" t="n"/>
+      <c r="D42" s="35" t="n"/>
+      <c r="E42" s="35" t="n"/>
+      <c r="F42" s="35" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 45 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="15">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
@@ -22499,7 +22452,6 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B44:E46"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -22515,7 +22467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -22529,7 +22481,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#46    0559.HK    DeTai New Energy Group Limited</t>
+          <t>#46    036190.KQ    Geumhwa Plant Service &amp; Construction Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -22547,9 +22499,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="36" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -22558,7 +22510,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.002930655934327</v>
+        <v>1.002562672083327</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -22576,7 +22528,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
@@ -22588,7 +22540,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -22598,10 +22550,8 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Hotels, Restaurants &amp; Leisure</t>
-        </is>
+      <c r="B8" s="27" t="n">
+        <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -22623,7 +22573,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>8411861.529944658</v>
+        <v>120906303.1013031</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -22633,7 +22583,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>4343410.067886114</v>
+        <v>275616874.9640363</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -22644,7 +22594,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
@@ -22658,7 +22608,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>Korean power-plant maintenance/EPC with nuclear exposure into a confirmed SMR upcycle (Feb-2026 SMR Special Act); 3Q25 revenue +43% YoY to 93.8B KRW, 4.5% dividend yield, EPS guidance to KRW5,119</t>
         </is>
       </c>
     </row>
@@ -22679,7 +22629,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.5865091555171503</v>
+        <v>0.5457949381009995</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -22687,7 +22637,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.8947433522461824</v>
+        <v>0.641579735904684</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -22697,7 +22647,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.5212014992506679</v>
+        <v>0.4255601635095342</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -22705,7 +22655,7 @@
         </is>
       </c>
       <c r="E22" s="21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -22715,7 +22665,7 @@
         </is>
       </c>
       <c r="C23" s="21" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
@@ -22733,7 +22683,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.614669</v>
+        <v>0.536955</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -22741,7 +22691,7 @@
         </is>
       </c>
       <c r="E24" s="21" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -22751,7 +22701,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.5535631163043078</v>
+        <v>0.4426237147801244</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -22759,7 +22709,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -22776,7 +22726,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.1392800169025987</v>
+        <v>0.4951807783269601</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -22784,7 +22734,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>350.1163327772758</v>
+        <v>97.13932449961075</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -22794,7 +22744,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>2.042046942853337</v>
+        <v>1.111</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -22802,7 +22752,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>0.2857865991741041</v>
+        <v>-3.141017358294149</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -22811,8 +22761,10 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="21" t="n">
-        <v>2.311745445771504</v>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -22820,7 +22772,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>15.52777868840942</v>
+        <v>14.99143654608343</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -22829,8 +22781,10 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n">
-        <v>2.52</v>
+      <c r="C31" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
@@ -22838,7 +22792,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>110.2738116223045</v>
+        <v>10.20078968125122</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -22848,7 +22802,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>1.936695222986074</v>
+        <v>0.43867525</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -22856,7 +22810,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>28.063</v>
+        <v>44.772997</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -22866,7 +22820,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>-14.45209640499437</v>
+        <v>9.7899333480142</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -22886,7 +22840,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>394.0657541109062</v>
+        <v>72.00482746381182</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -22894,7 +22848,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>8.865860679332179</v>
+        <v>23.85416843924622</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -22904,7 +22858,7 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>3.604414515392866</v>
+        <v>2.737636802392253</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -22912,7 +22866,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>4.13223364405128</v>
+        <v>25.90122655335556</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -22925,41 +22879,57 @@
     <row r="38" ht="16" customHeight="1">
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>·  Graham net-net  (mcap &lt; NCAV)</t>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.14)</t>
+          <t>·  Sub-book  (P/B 0.50)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="35" t="n"/>
-      <c r="B42" s="35" t="n"/>
-      <c r="C42" s="35" t="n"/>
-      <c r="D42" s="35" t="n"/>
-      <c r="E42" s="35" t="n"/>
-      <c r="F42" s="35" t="n"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="23" t="inlineStr">
+          <t>·  Insider-aligned  (45% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>accelerating sales; cheap+grow (EV/EBIT 1.6x); cash 84% of mcap; cash &gt; EV (2.74x, net cash 72% mcap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1"/>
+    <row r="45" ht="18" customHeight="1"/>
+    <row r="48">
+      <c r="A48" s="35" t="n"/>
+      <c r="B48" s="35" t="n"/>
+      <c r="C48" s="35" t="n"/>
+      <c r="D48" s="35" t="n"/>
+      <c r="E48" s="35" t="n"/>
+      <c r="F48" s="35" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 46 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B8:E8"/>
@@ -22968,6 +22938,8 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
@@ -23501,7 +23473,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#47    036190.KQ    Geumhwa Plant Service &amp; Construction Co., Ltd.</t>
+          <t>#47    FPIP.ST    Formpipe Software AB (publ)</t>
         </is>
       </c>
     </row>
@@ -23530,7 +23502,7 @@
         </is>
       </c>
       <c r="E3" s="25" t="n">
-        <v>1.002562672083327</v>
+        <v>0.9979808062005222</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -23548,7 +23520,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SE</t>
         </is>
       </c>
     </row>
@@ -23560,7 +23532,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -23570,8 +23542,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v/>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -23593,7 +23567,7 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>120906303.1013031</v>
+        <v>169011409.3541451</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -23603,7 +23577,7 @@
         </is>
       </c>
       <c r="B11" s="28" t="n">
-        <v>275616874.9640363</v>
+        <v>33948145.22631466</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -23628,7 +23602,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Korean power-plant maintenance/EPC with nuclear exposure into a confirmed SMR upcycle (Feb-2026 SMR Special Act); 3Q25 revenue +43% YoY to 93.8B KRW, 4.5% dividend yield, EPS guidance to KRW5,119</t>
+          <t>Divesting Public Sector for up to SEK 850M; active buyback + redemption program; rebranding to Lasernet Group</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23623,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="n">
-        <v>0.5457949381009995</v>
+        <v>0.5680502503701589</v>
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
@@ -23657,7 +23631,7 @@
         </is>
       </c>
       <c r="E21" s="21" t="n">
-        <v>0.641579735904684</v>
+        <v>0.6571710329652143</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -23667,7 +23641,7 @@
         </is>
       </c>
       <c r="C22" s="21" t="n">
-        <v>0.4255601635095342</v>
+        <v>0.5378018115760004</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -23685,7 +23659,7 @@
         </is>
       </c>
       <c r="C23" s="21" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
@@ -23703,7 +23677,7 @@
         </is>
       </c>
       <c r="C24" s="21" t="n">
-        <v>0.536955</v>
+        <v>0.720162</v>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
@@ -23711,7 +23685,7 @@
         </is>
       </c>
       <c r="E24" s="21" t="n">
-        <v>1.2</v>
+        <v>1.135</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -23721,7 +23695,7 @@
         </is>
       </c>
       <c r="C25" s="21" t="n">
-        <v>0.4426237147801244</v>
+        <v>0.4120506931715937</v>
       </c>
       <c r="D25" s="30" t="inlineStr">
         <is>
@@ -23729,7 +23703,7 @@
         </is>
       </c>
       <c r="E25" s="31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -23746,7 +23720,7 @@
         </is>
       </c>
       <c r="C28" s="21" t="n">
-        <v>0.4951807783269601</v>
+        <v>1.852776</v>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
@@ -23754,7 +23728,7 @@
         </is>
       </c>
       <c r="E28" s="32" t="n">
-        <v>97.13932449961075</v>
+        <v>64.07198066227858</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -23764,7 +23738,7 @@
         </is>
       </c>
       <c r="C29" s="21" t="n">
-        <v>1.111</v>
+        <v>17.728</v>
       </c>
       <c r="D29" s="30" t="inlineStr">
         <is>
@@ -23772,7 +23746,7 @@
         </is>
       </c>
       <c r="E29" s="21" t="n">
-        <v>-3.141017358294149</v>
+        <v>-9.71034096461643</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -23781,10 +23755,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="21" t="n">
+        <v>6.558816042861836</v>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
@@ -23792,7 +23764,7 @@
         </is>
       </c>
       <c r="E30" s="32" t="n">
-        <v>14.99143654608343</v>
+        <v>71.98682846071279</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -23812,7 +23784,7 @@
         </is>
       </c>
       <c r="E31" s="32" t="n">
-        <v>10.20078968125122</v>
+        <v>26.09394679147295</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -23822,7 +23794,7 @@
         </is>
       </c>
       <c r="C32" s="21" t="n">
-        <v>0.43867525</v>
+        <v>6.5829334</v>
       </c>
       <c r="D32" s="30" t="inlineStr">
         <is>
@@ -23830,7 +23802,7 @@
         </is>
       </c>
       <c r="E32" s="32" t="n">
-        <v>44.772997</v>
+        <v>37.955</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -23840,7 +23812,7 @@
         </is>
       </c>
       <c r="C33" s="32" t="n">
-        <v>9.7899333480142</v>
+        <v>2.66406750572596</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -23860,7 +23832,7 @@
         </is>
       </c>
       <c r="C34" s="32" t="n">
-        <v>72.00482746381182</v>
+        <v>76.34235721355236</v>
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
@@ -23868,7 +23840,7 @@
         </is>
       </c>
       <c r="E34" s="32" t="n">
-        <v>23.85416843924622</v>
+        <v>44.44050164399806</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -23878,7 +23850,7 @@
         </is>
       </c>
       <c r="C35" s="21" t="n">
-        <v>2.737636802392253</v>
+        <v>3.145251937040616</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -23886,7 +23858,7 @@
         </is>
       </c>
       <c r="E35" s="32" t="n">
-        <v>25.90122655335556</v>
+        <v>-25.38500650704087</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -23906,14 +23878,14 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.50)</t>
+          <t>·  Insider-aligned  (38% insider)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (45% insider)</t>
+          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -23927,7 +23899,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>accelerating sales; cheap+grow (EV/EBIT 1.6x); cash 84% of mcap; cash &gt; EV (2.74x, net cash 72% mcap)</t>
+          <t>growth-flip; first-positive: ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 6.6x); cash 76% of mcap; cash &gt; EV (3.15x, net cash 76% mcap)</t>
         </is>
       </c>
     </row>
@@ -23979,498 +23951,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>#48    FPIP.ST    Formpipe Software AB (publ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="D3" s="23" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="25" t="n">
-        <v>0.9979808062005222</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>Micro Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="28" t="n">
-        <v>169011409.3541451</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="n">
-        <v>33948145.22631466</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>Divesting Public Sector for up to SEK 850M; active buyback + redemption program; rebranding to Lasernet Group</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="30" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="n">
-        <v>0.5680502503701589</v>
-      </c>
-      <c r="D21" s="30" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="n">
-        <v>0.6571710329652143</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="30" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="n">
-        <v>0.5378018115760004</v>
-      </c>
-      <c r="D22" s="30" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="30" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D23" s="30" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="30" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="n">
-        <v>0.720162</v>
-      </c>
-      <c r="D24" s="30" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>1.135</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="30" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="n">
-        <v>0.4120506931715937</v>
-      </c>
-      <c r="D25" s="30" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="30" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="n">
-        <v>1.852776</v>
-      </c>
-      <c r="D28" s="30" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="32" t="n">
-        <v>64.07198066227858</v>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="n">
-        <v>17.728</v>
-      </c>
-      <c r="D29" s="30" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="n">
-        <v>-9.71034096461643</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="n">
-        <v>6.558816042861836</v>
-      </c>
-      <c r="D30" s="30" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="32" t="n">
-        <v>71.98682846071279</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D31" s="30" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="n">
-        <v>26.09394679147295</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="n">
-        <v>6.5829334</v>
-      </c>
-      <c r="D32" s="30" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="32" t="n">
-        <v>37.955</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="n">
-        <v>2.66406750572596</v>
-      </c>
-      <c r="D33" s="30" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="33" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="30" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="32" t="n">
-        <v>76.34235721355236</v>
-      </c>
-      <c r="D34" s="30" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="32" t="n">
-        <v>44.44050164399806</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="30" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="n">
-        <v>3.145251937040616</v>
-      </c>
-      <c r="D35" s="30" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="n">
-        <v>-25.38500650704087</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="34" t="inlineStr">
-        <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="34" t="inlineStr">
-        <is>
-          <t>·  Insider-aligned  (38% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="34" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; first-positive: ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 6.6x); cash 76% of mcap; cash &gt; EV (3.15x, net cash 76% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="35" t="n"/>
-      <c r="B48" s="35" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="35" t="n"/>
-      <c r="F48" s="35" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 48 of 50</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00707070"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -24485,7 +23965,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#49    1V5.F    Zaklady Azotowe Pulawy S.A.</t>
+          <t>#48    1V5.F    Zaklady Azotowe Pulawy S.A.</t>
         </is>
       </c>
     </row>
@@ -24925,7 +24405,7 @@
     <row r="44">
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 49 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 48 of 50</t>
         </is>
       </c>
     </row>
@@ -24952,7 +24432,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -24973,7 +24453,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#50    IGAR.JK    PT Champion Pacific Indonesia Tbk</t>
+          <t>#49    IGAR.JK    PT Champion Pacific Indonesia Tbk</t>
         </is>
       </c>
     </row>
@@ -25419,7 +24899,7 @@
     <row r="50">
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 50 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 49 of 50</t>
         </is>
       </c>
     </row>
@@ -25440,6 +24920,488 @@
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B44:E46"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00707070"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#50    6912.KL    Pasdec Holdings Bhd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="n">
+        <v>0.9943177685727069</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Nano Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="n">
+        <v>29092297.90078092</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="n">
+        <v>24150204.2426914</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>0.6648017889599034</v>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="n">
+        <v>0.4963837405937419</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>0.6313734551489828</v>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D23" s="30" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="n">
+        <v>0.9176293912656586</v>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="n">
+        <v>0.6155965459970597</v>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="n">
+        <v>0.2821393964440219</v>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="n">
+        <v>0.6596619823684178</v>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="n">
+        <v>-0.8129979924436076</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="n">
+        <v>24.14839043741281</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="n">
+        <v>1.9666665</v>
+      </c>
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="n">
+        <v>81.79611402927227</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>1.20463982865011</v>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="n">
+        <v>90.63200399999999</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n">
+        <v>55.75916743691619</v>
+      </c>
+      <c r="D33" s="30" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="33" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="n">
+        <v>55.20328559118384</v>
+      </c>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="32" t="n">
+        <v>232.5491714541378</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>1.496023508119931</v>
+      </c>
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="32" t="n">
+        <v>2.94824349373655</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (91% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="n"/>
+      <c r="B43" s="35" t="n"/>
+      <c r="C43" s="35" t="n"/>
+      <c r="D43" s="35" t="n"/>
+      <c r="E43" s="35" t="n"/>
+      <c r="F43" s="35" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 50 of 50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -756,7 +756,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>25,466</t>
+          <t>25,849</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>394</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>177</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>25,084</t>
+          <t>25,455</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 25,466 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 25,849 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -26053,22 +26053,22 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>25466</v>
+        <v>25849</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G5" s="31" t="n">
-        <v>25084</v>
+        <v>25455</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.500039268043666</v>
+        <v>1.524236914387404</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -756,7 +756,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>25,849</t>
+          <t>25,862</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>25,455</t>
+          <t>25,467</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 25,849 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 25,862 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -21923,8 +21923,10 @@
           <t>FCF yield (%)</t>
         </is>
       </c>
-      <c r="C33" s="23" t="n">
-        <v>1453.539401863697</v>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -26053,10 +26055,10 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>25849</v>
+        <v>25862</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>177</v>
@@ -26065,10 +26067,10 @@
         <v>96</v>
       </c>
       <c r="G5" s="31" t="n">
-        <v>25455</v>
+        <v>25467</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.524236914387404</v>
+        <v>1.527337406233083</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -756,7 +756,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>25,862</t>
+          <t>25,849</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>394</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>25,467</t>
+          <t>25,455</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 25,862 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 25,849 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -26055,10 +26055,10 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>25862</v>
+        <v>25849</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>177</v>
@@ -26067,10 +26067,10 @@
         <v>96</v>
       </c>
       <c r="G5" s="31" t="n">
-        <v>25467</v>
+        <v>25455</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.527337406233083</v>
+        <v>1.524236914387404</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -756,7 +756,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>25,849</t>
+          <t>25,862</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>395</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>25,455</t>
+          <t>25,467</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 25,849 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 25,862 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -26055,10 +26055,10 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>25849</v>
+        <v>25862</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>177</v>
@@ -26067,10 +26067,10 @@
         <v>96</v>
       </c>
       <c r="G5" s="31" t="n">
-        <v>25455</v>
+        <v>25467</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.524236914387404</v>
+        <v>1.527337406233083</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -756,7 +756,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>25,862</t>
+          <t>25,859</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>25,467</t>
+          <t>25,464</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 25,862 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 25,859 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -26055,7 +26055,7 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>25862</v>
+        <v>25859</v>
       </c>
       <c r="D5" s="31" t="n">
         <v>122</v>
@@ -26067,10 +26067,10 @@
         <v>96</v>
       </c>
       <c r="G5" s="31" t="n">
-        <v>25467</v>
+        <v>25464</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.527337406233083</v>
+        <v>1.52751459839901</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -24,14 +24,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_TPP_BK" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_LSIP_JK" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_120240_KQ" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_035610_KQ" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_3798_HK" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_3798_HK" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_035610_KQ" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_031510_KQ" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_052330_KQ" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_KROS" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_348350_KQ" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_2348_HK" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_METCO_BK" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_348350_KQ" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_2348_HK" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21_METCO_BK" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22_KROS" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23_S23_SI" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_095660_KQ" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_051160_KQ" sheetId="28" state="visible" r:id="rId28"/>
@@ -4815,6 +4815,488 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#15    3798.HK    Homeland Interactive Technology Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>1.146428117925815</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Interactive Media &amp; Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n">
+        <v>193180522.7553062</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n">
+        <v>172106635.0032687</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>0.6573455939461111</v>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>0.5915588255881016</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>0.5617341988444753</v>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>0.8495485218474618</v>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>0.4128425191777984</v>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>0.63482887</v>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>-7.225898256848096</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="n">
+        <v>2.041767239331802</v>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>33.75755216989689</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="n">
+        <v>20.000002</v>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>13.1301770234321</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n">
+        <v>1.2164296</v>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>74.694</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>11.29592044426044</v>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>72.84153319603385</v>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="n">
+        <v>-2.6933510331294</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>3.142024571801568</v>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>-18.09</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.63)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (75% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="n"/>
+      <c r="B43" s="36" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 15 of 50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00707070"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4829,7 +5311,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#15    035610.KQ    Solborn, Inc.</t>
+          <t>#16    035610.KQ    Solborn, Inc.</t>
         </is>
       </c>
     </row>
@@ -4858,7 +5340,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.146648181877715</v>
+        <v>1.137221610175333</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -5039,7 +5521,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.2164</v>
+        <v>1.2064</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -5119,8 +5601,10 @@
           <t>ROCE (%)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="n">
-        <v>197.6613890777809</v>
+      <c r="E30" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -5279,7 +5763,7 @@
     <row r="50">
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 15 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 16 of 50</t>
         </is>
       </c>
     </row>
@@ -5300,488 +5784,6 @@
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B44:E46"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00707070"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>#16    3798.HK    Homeland Interactive Technology Ltd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="n">
-        <v>1.146428117925815</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>Interactive Media &amp; Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>Small Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n">
-        <v>193180522.7553062</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n">
-        <v>172106635.0032687</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>0.6573455939461111</v>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>0.5915588255881016</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>0.5617341988444753</v>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>0.7692307692307692</v>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="n">
-        <v>0.8495485218474618</v>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="n">
-        <v>0.4128425191777984</v>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>0.63482887</v>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>1.119</v>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="n">
-        <v>-7.225898256848096</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="n">
-        <v>2.041767239331802</v>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="n">
-        <v>33.75755216989689</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n">
-        <v>20.000002</v>
-      </c>
-      <c r="D31" s="33" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="n">
-        <v>13.1301770234321</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n">
-        <v>1.2164296</v>
-      </c>
-      <c r="D32" s="33" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="n">
-        <v>74.694</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="n">
-        <v>11.29592044426044</v>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>72.84153319603385</v>
-      </c>
-      <c r="D34" s="33" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="n">
-        <v>-2.6933510331294</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n">
-        <v>3.142024571801568</v>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="n">
-        <v>-18.09</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>·  Sub-book  (P/B 0.63)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>·  Insider-aligned  (75% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="36" t="n"/>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
-      <c r="F43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="26" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 16 of 50</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -6945,7 +6947,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#19    KROS    Keros Therapeutics, Inc.</t>
+          <t>#19    348350.KQ    WITHTECH Co., LTD.</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6976,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.11727586668782</v>
+        <v>1.113650562417347</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -6992,7 +6994,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7006,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -7014,10 +7016,8 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
+      <c r="B8" s="30" t="n">
+        <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>224443760</v>
+        <v>60858057.77970123</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>244061000</v>
+        <v>37014740.95624924</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6305867949791741</v>
+        <v>0.588439175935826</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.67887376</v>
+        <v>0.7650282137291016</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5716070773780287</v>
+        <v>0.5626735786360552</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6153846153846153</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.837901</v>
+        <v>0.694261</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.24</v>
+        <v>1.2617</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.4395225067843441</v>
+        <v>0.467269358229353</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.8556312</v>
+        <v>0.7937623623751395</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>127.0432475398032</v>
+        <v>75.63918384940335</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>0.18</v>
+        <v>1.723</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-3.916326471524943</v>
+        <v>-4.466251897016345</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -7227,10 +7227,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>2.795730826372435</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -7238,7 +7236,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>207.2668711656441</v>
+        <v>6.48271546413415</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -7258,7 +7256,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>28.30357984274423</v>
+        <v>24.38145444513379</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -7268,7 +7266,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>14.948965</v>
+        <v>1.4497193</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -7276,7 +7274,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>3.641</v>
+        <v>57.577</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -7286,7 +7284,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>36.66783771232035</v>
+        <v>9.770428543556529</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -7306,7 +7304,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>135.4560479850007</v>
+        <v>97.41201443595627</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -7314,7 +7312,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>6774.957746478873</v>
+        <v>29.74903547376832</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -7323,10 +7321,8 @@
           <t>Cash / EV (x)</t>
         </is>
       </c>
-      <c r="C35" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C35" s="22" t="n">
+        <v>27.45971875741036</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -7334,7 +7330,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>-25.62</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -7347,21 +7343,21 @@
     <row r="38" ht="16" customHeight="1">
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>·  Negative enterprise value</t>
+          <t>·  Sub-book  (P/B 0.79)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.86)</t>
+          <t>·  Insider-aligned  (58% insider)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7371,7 @@
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; first-positive: FCF/EBITDA/CFO/NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cash 138% of mcap</t>
+          <t>growth-flip; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 2.8x)</t>
         </is>
       </c>
     </row>
@@ -7427,7 +7423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7441,7 +7437,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#20    348350.KQ    WITHTECH Co., LTD.</t>
+          <t>#20    2348.HK    Dawnrays Pharmaceutical (Holdings) Limited</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7466,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.113650562417347</v>
+        <v>1.09772165902702</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -7488,7 +7484,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7496,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
     </row>
@@ -7510,8 +7506,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
-        <v/>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -7522,7 +7520,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7531,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>60858057.77970123</v>
+        <v>189917124.4803295</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -7543,7 +7541,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>37014740.95624924</v>
+        <v>157064460.8974904</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -7554,7 +7552,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7587,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.588439175935826</v>
+        <v>0.6098453661261224</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -7597,7 +7595,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.7650282137291016</v>
+        <v>0.9079045322105156</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -7607,7 +7605,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5626735786360552</v>
+        <v>0.4834847817611555</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -7625,7 +7623,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.6153846153846153</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -7643,7 +7641,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.694261</v>
+        <v>0.761567</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -7651,7 +7649,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.2617</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -7661,7 +7659,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.467269358229353</v>
+        <v>0.4269003334734619</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -7686,7 +7684,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.7937623623751395</v>
+        <v>0.37188843</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -7694,7 +7692,7 @@
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>75.63918384940335</v>
+        <v>104.7508519298697</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -7704,7 +7702,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>1.723</v>
+        <v>0.2541832540201263</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -7712,7 +7710,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-4.466251897016345</v>
+        <v>-4.049683737461582</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -7721,8 +7719,10 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="22" t="n">
-        <v>2.795730826372435</v>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>6.48271546413415</v>
+        <v>13.2643076741945</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -7739,10 +7739,8 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C31" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -7750,7 +7748,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>24.38145444513379</v>
+        <v>30.0813979089536</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -7760,7 +7758,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>1.4497193</v>
+        <v>1.2983886</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -7768,7 +7766,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>57.577</v>
+        <v>67.661005</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -7778,7 +7776,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>9.770428543556529</v>
+        <v>14.81031382345322</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -7798,7 +7796,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>97.41201443595627</v>
+        <v>94.09407273683851</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -7806,7 +7804,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>29.74903547376832</v>
+        <v>16.08568822862014</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -7816,7 +7814,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>27.45971875741036</v>
+        <v>16.75536368504713</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -7824,7 +7822,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>20.77</v>
+        <v>-14.17</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -7837,71 +7835,79 @@
     <row r="38" ht="16" customHeight="1">
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.79)</t>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (58% insider)</t>
+          <t>·  Sub-book  (P/B 0.37)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
+          <t>·  Insider-aligned  (68% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="35" t="inlineStr">
+        <is>
           <t>·  Cluster stack  (4 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 2.8x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>growth-flip; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.4x); cash 99% of mcap; cash &gt; EV (16.76x, net cash 94% mcap)</t>
+        </is>
+      </c>
+    </row>
     <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="36" t="n"/>
-      <c r="B48" s="36" t="n"/>
-      <c r="C48" s="36" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="36" t="n"/>
-    </row>
+    <row r="46" ht="18" customHeight="1"/>
     <row r="49">
-      <c r="B49" s="26" t="inlineStr">
+      <c r="A49" s="36" t="n"/>
+      <c r="B49" s="36" t="n"/>
+      <c r="C49" s="36" t="n"/>
+      <c r="D49" s="36" t="n"/>
+      <c r="E49" s="36" t="n"/>
+      <c r="F49" s="36" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 20 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B44:E46"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -7931,7 +7937,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#21    2348.HK    Dawnrays Pharmaceutical (Holdings) Limited</t>
+          <t>#21    METCO.BK    Muramoto Electron (Thailand) Public Company Limited</t>
         </is>
       </c>
     </row>
@@ -7949,9 +7955,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -7960,7 +7966,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.09772165902702</v>
+        <v>1.095391292032167</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -7978,7 +7984,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7996,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8008,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Electronic Equipment, Instruments &amp; Components</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8020,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8031,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>189917124.4803295</v>
+        <v>189173887.7198486</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -8035,7 +8041,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>157064460.8974904</v>
+        <v>514626167.5263252</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -8046,7 +8052,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8066,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>Japanese parent Muramoto 80%; ~3.6-4.6% yield; 56% payout; 10yr dividend growth; squeeze-out is upside</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8087,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6098453661261224</v>
+        <v>0.7075775903804709</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -8089,7 +8095,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.9079045322105156</v>
+        <v>0.5168569030978339</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -8099,7 +8105,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.4834847817611555</v>
+        <v>0.6508658603312235</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -8107,7 +8113,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -8125,7 +8131,7 @@
         </is>
       </c>
       <c r="E23" s="22" t="n">
-        <v>1</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -8135,7 +8141,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.761567</v>
+        <v>0.7800820000000001</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -8153,7 +8159,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.4269003334734619</v>
+        <v>0.5225695245785115</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -8161,7 +8167,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -8178,7 +8184,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.37188843</v>
+        <v>0.8462543</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -8186,7 +8192,7 @@
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>104.7508519298697</v>
+        <v>84.50518903603952</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -8196,7 +8202,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>0.2541832540201263</v>
+        <v>1.743</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -8204,7 +8210,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-4.049683737461582</v>
+        <v>-1.67116159988576</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -8224,7 +8230,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>13.2643076741945</v>
+        <v>35.31203322577265</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -8234,7 +8240,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>5.5</v>
+        <v>5.7241645</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -8242,7 +8248,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>30.0813979089536</v>
+        <v>10.96313272568954</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -8252,7 +8258,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>1.2983886</v>
+        <v>0.3770226</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -8260,7 +8266,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>67.661005</v>
+        <v>85.438</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -8270,7 +8276,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>14.81031382345322</v>
+        <v>22.68002247505217</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -8290,7 +8296,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>94.09407273683851</v>
+        <v>52.11409371218626</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -8298,7 +8304,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>16.08568822862014</v>
+        <v>7.00038199914789</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -8308,7 +8314,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>16.75536368504713</v>
+        <v>1.143401385189282</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -8316,7 +8322,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>-14.17</v>
+        <v>50.79</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -8336,21 +8342,21 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.37)</t>
+          <t>·  Sub-book  (P/B 0.85)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (68% insider)</t>
+          <t>·  Insider-aligned  (85% insider)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8370,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.4x); cash 99% of mcap; cash &gt; EV (16.76x, net cash 94% mcap)</t>
+          <t>growth-flip; first-positive: FCF; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 2.0x); cash 55% of mcap; cash &gt; EV (1.14x, net cash 52% mcap)</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8431,7 +8437,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#22    METCO.BK    Muramoto Electron (Thailand) Public Company Limited</t>
+          <t>#22    KROS    Keros Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -8449,9 +8455,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -8460,7 +8466,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.095391292032167</v>
+        <v>1.09375163490372</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -8478,7 +8484,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>US</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8496,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8508,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Electronic Equipment, Instruments &amp; Components</t>
+          <t>Biotechnology</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8520,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8531,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>189173887.7198486</v>
+        <v>224443760</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -8535,7 +8541,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>514626167.5263252</v>
+        <v>244061000</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -8546,7 +8552,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
     </row>
@@ -8560,7 +8566,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Japanese parent Muramoto 80%; ~3.6-4.6% yield; 56% payout; 10yr dividend growth; squeeze-out is upside</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8587,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.7075775903804709</v>
+        <v>0.6173097965516875</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -8589,7 +8595,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.5168569030978339</v>
+        <v>0.67887376</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -8599,7 +8605,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.6508658603312235</v>
+        <v>0.5716070773780287</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -8607,7 +8613,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -8617,7 +8623,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.7692307692307692</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -8625,7 +8631,7 @@
         </is>
       </c>
       <c r="E23" s="22" t="n">
-        <v>0.926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -8635,7 +8641,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.7800820000000001</v>
+        <v>0.837901</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -8643,7 +8649,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -8653,7 +8659,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.5225695245785115</v>
+        <v>0.4395225067843441</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -8678,7 +8684,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.8462543</v>
+        <v>0.8556312</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -8686,7 +8692,7 @@
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>84.50518903603952</v>
+        <v>127.0432475398032</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -8696,7 +8702,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>1.743</v>
+        <v>0.18</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -8704,7 +8710,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-1.67116159988576</v>
+        <v>-3.916326471524943</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -8723,8 +8729,10 @@
           <t>ROCE (%)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="n">
-        <v>35.31203322577265</v>
+      <c r="E30" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -8733,8 +8741,10 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n">
-        <v>5.7241645</v>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -8742,7 +8752,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>10.96313272568954</v>
+        <v>28.30357984274423</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -8752,7 +8762,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.3770226</v>
+        <v>14.948965</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -8760,7 +8770,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>85.438</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -8770,7 +8780,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>22.68002247505217</v>
+        <v>36.66783771232035</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -8790,7 +8800,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>52.11409371218626</v>
+        <v>135.4560479850007</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -8798,7 +8808,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>7.00038199914789</v>
+        <v>6774.957746478873</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -8807,8 +8817,10 @@
           <t>Cash / EV (x)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="n">
-        <v>1.143401385189282</v>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -8816,7 +8828,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>50.79</v>
+        <v>-25.62</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -8829,79 +8841,71 @@
     <row r="38" ht="16" customHeight="1">
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
+          <t>·  Negative enterprise value</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.85)</t>
+          <t>·  Sub-book  (P/B 0.86)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (85% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
-        <is>
           <t>·  Cluster stack  (5 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; first-positive: FCF; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 2.0x); cash 55% of mcap; cash &gt; EV (1.14x, net cash 52% mcap)</t>
-        </is>
-      </c>
-    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>growth-flip; first-positive: FCF/EBITDA/CFO/NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cash 138% of mcap</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1"/>
     <row r="45" ht="18" customHeight="1"/>
-    <row r="46" ht="18" customHeight="1"/>
+    <row r="48">
+      <c r="A48" s="36" t="n"/>
+      <c r="B48" s="36" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="36" t="n"/>
+    </row>
     <row r="49">
-      <c r="A49" s="36" t="n"/>
-      <c r="B49" s="36" t="n"/>
-      <c r="C49" s="36" t="n"/>
-      <c r="D49" s="36" t="n"/>
-      <c r="E49" s="36" t="n"/>
-      <c r="F49" s="36" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="26" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 22 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="17">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B44:E46"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -11564,22 +11568,22 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>035610.KQ</t>
+          <t>3798.HK</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Solborn, Inc.</t>
+          <t>Homeland Interactive Technology Ltd.</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
@@ -11588,10 +11592,10 @@
         </is>
       </c>
       <c r="H18" s="22" t="n">
-        <v>1.146648181877715</v>
+        <v>1.146428117925815</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>0.4404573070670534</v>
+        <v>0.63482887</v>
       </c>
       <c r="J18" s="25" t="inlineStr">
         <is>
@@ -11599,7 +11603,7 @@
         </is>
       </c>
       <c r="K18" s="22" t="n">
-        <v>1.0640486</v>
+        <v>1.2164296</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -11608,22 +11612,22 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>3798.HK</t>
+          <t>035610.KQ</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>Homeland Interactive Technology Ltd.</t>
+          <t>Solborn, Inc.</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
@@ -11632,10 +11636,10 @@
         </is>
       </c>
       <c r="H19" s="22" t="n">
-        <v>1.146428117925815</v>
+        <v>1.137221610175333</v>
       </c>
       <c r="I19" s="22" t="n">
-        <v>0.63482887</v>
+        <v>0.4404573070670534</v>
       </c>
       <c r="J19" s="25" t="inlineStr">
         <is>
@@ -11643,7 +11647,7 @@
         </is>
       </c>
       <c r="K19" s="22" t="n">
-        <v>1.2164296</v>
+        <v>1.0640486</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -11736,22 +11740,22 @@
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>KROS</t>
+          <t>348350.KQ</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>Keros Therapeutics, Inc.</t>
+          <t>WITHTECH Co., LTD.</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
@@ -11760,18 +11764,16 @@
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>1.11727586668782</v>
+        <v>1.113650562417347</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>0.8556312</v>
-      </c>
-      <c r="J22" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.7937623623751395</v>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>2.8800001</v>
       </c>
       <c r="K22" s="22" t="n">
-        <v>14.948965</v>
+        <v>1.4497193</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -11780,22 +11782,22 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>348350.KQ</t>
+          <t>2348.HK</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>WITHTECH Co., LTD.</t>
+          <t>Dawnrays Pharmaceutical (Holdings) Limited</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
@@ -11804,16 +11806,16 @@
         </is>
       </c>
       <c r="H23" s="22" t="n">
-        <v>1.113650562417347</v>
+        <v>1.09772165902702</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>0.7937623623751395</v>
+        <v>0.37188843</v>
       </c>
       <c r="J23" s="23" t="n">
-        <v>2.8800001</v>
+        <v>6.3</v>
       </c>
       <c r="K23" s="22" t="n">
-        <v>1.4497193</v>
+        <v>1.2983886</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -11822,40 +11824,40 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>2348.HK</t>
+          <t>METCO.BK</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Dawnrays Pharmaceutical (Holdings) Limited</t>
+          <t>Muramoto Electron (Thailand) Public Company Limited</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="G24" s="24" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H24" s="22" t="n">
-        <v>1.09772165902702</v>
+        <v>1.095391292032167</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>0.37188843</v>
+        <v>0.8462543</v>
       </c>
       <c r="J24" s="23" t="n">
-        <v>6.3</v>
+        <v>10.24</v>
       </c>
       <c r="K24" s="22" t="n">
-        <v>1.2983886</v>
+        <v>0.3770226</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -11864,40 +11866,42 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>METCO.BK</t>
+          <t>KROS</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>Muramoto Electron (Thailand) Public Company Limited</t>
+          <t>Keros Therapeutics, Inc.</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H25" s="22" t="n">
-        <v>1.095391292032167</v>
+        <v>1.09375163490372</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>0.8462543</v>
-      </c>
-      <c r="J25" s="23" t="n">
-        <v>10.24</v>
+        <v>0.8556312</v>
+      </c>
+      <c r="J25" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K25" s="22" t="n">
-        <v>0.3770226</v>
+        <v>14.948965</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -26188,16 +26188,16 @@
         <v>1</v>
       </c>
       <c r="E14" s="34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -11578,7 +11578,7 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -14200,7 +14200,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>MY</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -25524,7 +25524,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E20" s="34" t="n">
         <v>1</v>
@@ -26344,10 +26344,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21">
@@ -27105,7 +27105,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
     </row>

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_AWC_SI" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_042420_KQ" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_2230_HK" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_003650_KS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_3798_HK" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_3798_HK" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_003650_KS" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_IRC_BK" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_054800_KQ" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_ALGEV_PA" sheetId="12" state="visible" r:id="rId12"/>
@@ -36,13 +36,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24_6907_T" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25_SHRIDINE_BO" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="26_7877_T" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_6820_HK" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_095660_KQ" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_014570_KQ" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_TCID_JK" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_348350_KQ" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_IGAR_JK" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_BENGALT_BO" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27_095660_KQ" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28_014570_KQ" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29_TCID_JK" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_348350_KQ" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="31_IGAR_JK" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32_BENGALT_BO" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="33_6820_HK" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="34_051160_KQ" sheetId="37" state="visible" r:id="rId37"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="35_LSIP_JK" sheetId="38" state="visible" r:id="rId38"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="36_7722_T" sheetId="39" state="visible" r:id="rId39"/>
@@ -53,13 +53,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41_053980_KQ" sheetId="44" state="visible" r:id="rId44"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42_088130_KQ" sheetId="45" state="visible" r:id="rId45"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43_4625_T" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44_CAAS" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45_0725_HK" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46_1281_HK" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44_1V5_F" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45_CAAS" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46_0725_HK" sheetId="49" state="visible" r:id="rId49"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="47_131090_KQ" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48_052790_KQ" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49_3954_T" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50_036190_KQ" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48_1281_HK" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49_052790_KQ" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50_3954_T" sheetId="53" state="visible" r:id="rId53"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="54" state="visible" r:id="rId54"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
@@ -756,7 +756,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>26,154</t>
+          <t>26,385</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>401</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>25,755</t>
+          <t>25,984</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 26,154 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 26,385 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>78821510.97271729</v>
+        <v>77653786.95794658</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>136153379.1378207</v>
+        <v>136153379.1378204</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>85944326.25859833</v>
+        <v>86400269.06174681</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>621263383.7902402</v>
+        <v>621263383.7902211</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>14694714.95424652</v>
+        <v>14694714.95424648</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>8311024.856157303</v>
+        <v>8311024.856157282</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>97170111.41296196</v>
+        <v>97649721.25524984</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>77102450.02260983</v>
+        <v>77102450.02260746</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>68969379.53465939</v>
+        <v>69110133.31576708</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>74515427.36626884</v>
+        <v>74515427.36626655</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>101813330.5148983</v>
+        <v>98540142.03049168</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>280815515.3520368</v>
+        <v>280815515.3520282</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>36657145.75909615</v>
+        <v>38413174.78646944</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.7870427008847081</v>
+        <v>0.771852126</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.0647864955764595</v>
+        <v>0.14073937</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.06)</t>
+          <t>·  Sub-book  (P/B 0.14)</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>36465264.94312406</v>
+        <v>36263429.07907232</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>86615249.88943711</v>
+        <v>86615249.88943674</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>18872311.0689466</v>
+        <v>18429222.51684681</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>90551985.4721216</v>
+        <v>90551985.47211882</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>87016812.30957699</v>
+        <v>90146910.85052596</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>85769277.6876678</v>
+        <v>85769277.68766516</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>331100479.5374721</v>
+        <v>331100479.537472</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.101465135344188</v>
+        <v>1.099278313855842</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>49478730.98710728</v>
+        <v>50773986.45186899</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6398208048089544</v>
+        <v>0.6370614891453174</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.2599812216818146</v>
+        <v>0.2737778</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.26)</t>
+          <t>·  Sub-book  (P/B 0.27)</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>189917124.4803295</v>
+        <v>190876303.7740096</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.9301888218670404</v>
+        <v>0.9253510300000001</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.3490558906647981</v>
+        <v>0.37324485</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.35)</t>
+          <t>·  Sub-book  (P/B 0.37)</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>68171702.99383163</v>
+        <v>72336165.70478408</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>216405193.725382</v>
+        <v>216405193.725381</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>23630217.79200745</v>
+        <v>23924676.0523474</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>11671505.63693912</v>
+        <v>11671505.63693877</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>191774490.9876108</v>
+        <v>184192477.3257772</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -9017,7 +9017,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>425102384.579368</v>
+        <v>425102384.5793661</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>39255726.92124725</v>
+        <v>37283078.28963859</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>32923308.73264465</v>
+        <v>32923308.73264452</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>21685160.35478532</v>
+        <v>20660894.65984212</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>7273825.765494257</v>
+        <v>7273825.765494212</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -10493,7 +10493,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>17178057.55831003</v>
+        <v>16725600.29102139</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>55222673.83330967</v>
+        <v>55222673.83330944</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -11136,40 +11136,42 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>003650.KS</t>
+          <t>3798.HK</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>Michang Oil Ind .Co.,Ltd.</t>
+          <t>Homeland Interactive Technology Ltd.</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H8" s="22" t="n">
-        <v>1.196379645329934</v>
+        <v>1.214607294531874</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>0.3814184820374598</v>
-      </c>
-      <c r="J8" s="23" t="n">
-        <v>2.77</v>
+        <v>0.64328694</v>
+      </c>
+      <c r="J8" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K8" s="22" t="n">
-        <v>0.47688493</v>
+        <v>1.06764828969794</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -11178,42 +11180,40 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>3798.HK</t>
+          <t>003650.KS</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Homeland Interactive Technology Ltd.</t>
+          <t>Michang Oil Ind .Co.,Ltd.</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H9" s="22" t="n">
-        <v>1.184048179572399</v>
+        <v>1.196379645329934</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>0.822089473429743</v>
-      </c>
-      <c r="J9" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.3814184820374598</v>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>2.77</v>
       </c>
       <c r="K9" s="22" t="n">
-        <v>1.06764828969794</v>
+        <v>0.47688493</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -11545,7 +11545,7 @@
         <v>1.13653565357367</v>
       </c>
       <c r="I17" s="22" t="n">
-        <v>0.0647864955764595</v>
+        <v>0.14073937</v>
       </c>
       <c r="J17" s="25" t="inlineStr">
         <is>
@@ -11756,10 +11756,10 @@
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>1.101465135344188</v>
+        <v>1.099278313855842</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>0.2599812216818146</v>
+        <v>0.2737778</v>
       </c>
       <c r="J22" s="25" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>1.09772165902702</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>0.3490558906647981</v>
+        <v>0.37324485</v>
       </c>
       <c r="J23" s="23" t="n">
         <v>6.3</v>
@@ -12074,22 +12074,22 @@
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>6820.HK</t>
+          <t>095660.KQ</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
         <is>
-          <t>FriendTimes Inc.</t>
+          <t>NEOWIZ</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
@@ -12098,16 +12098,18 @@
         </is>
       </c>
       <c r="H30" s="22" t="n">
-        <v>1.080518586556192</v>
+        <v>1.077025085586687</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>0.3799833008689863</v>
-      </c>
-      <c r="J30" s="23" t="n">
-        <v>5.63</v>
+        <v>0.6557044396837195</v>
+      </c>
+      <c r="J30" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K30" s="22" t="n">
-        <v>0.3826423671230745</v>
+        <v>0.7902293526088751</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -12116,12 +12118,12 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>095660.KQ</t>
+          <t>014570.KQ</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr">
         <is>
-          <t>NEOWIZ</t>
+          <t>Korean Drug Co., Ltd.</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
@@ -12131,7 +12133,7 @@
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
@@ -12140,18 +12142,16 @@
         </is>
       </c>
       <c r="H31" s="22" t="n">
-        <v>1.077025085586687</v>
+        <v>1.076618108296869</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>0.6557044396837195</v>
-      </c>
-      <c r="J31" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.4577384913211642</v>
+      </c>
+      <c r="J31" s="23" t="n">
+        <v>5.71</v>
       </c>
       <c r="K31" s="22" t="n">
-        <v>0.7902293526088751</v>
+        <v>0.5645629</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -12160,40 +12160,38 @@
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>014570.KQ</t>
+          <t>TCID.JK</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
         <is>
-          <t>Korean Drug Co., Ltd.</t>
+          <t>PT. Mandom Indonesia Tbk</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="G32" s="24" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="n">
+        <v/>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H32" s="22" t="n">
-        <v>1.076618108296869</v>
+        <v>1.073817836048235</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>0.4577384913211642</v>
+        <v>0.5712140999999999</v>
       </c>
       <c r="J32" s="23" t="n">
-        <v>5.71</v>
+        <v>1.39</v>
       </c>
       <c r="K32" s="22" t="n">
-        <v>0.5645629</v>
+        <v>0.5015371</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -12202,38 +12200,40 @@
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>TCID.JK</t>
+          <t>348350.KQ</t>
         </is>
       </c>
       <c r="D33" s="18" t="inlineStr">
         <is>
-          <t>PT. Mandom Indonesia Tbk</t>
+          <t>WITHTECH Co., LTD.</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="F33" s="20" t="n">
-        <v/>
-      </c>
-      <c r="G33" s="21" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H33" s="22" t="n">
-        <v>1.073817836048235</v>
+        <v>1.07027397463544</v>
       </c>
       <c r="I33" s="22" t="n">
-        <v>0.5712140999999999</v>
+        <v>0.7937623623751395</v>
       </c>
       <c r="J33" s="23" t="n">
-        <v>1.39</v>
+        <v>2.8800001</v>
       </c>
       <c r="K33" s="22" t="n">
-        <v>0.5015371</v>
+        <v>1.4025122</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -12242,23 +12242,21 @@
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>348350.KQ</t>
+          <t>IGAR.JK</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>WITHTECH Co., LTD.</t>
+          <t>PT Champion Pacific Indonesia Tbk</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v/>
       </c>
       <c r="G34" s="24" t="inlineStr">
         <is>
@@ -12266,16 +12264,16 @@
         </is>
       </c>
       <c r="H34" s="22" t="n">
-        <v>1.07027397463544</v>
+        <v>1.069061043495279</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>0.7937623623751395</v>
+        <v>0.60156065</v>
       </c>
       <c r="J34" s="23" t="n">
-        <v>2.8800001</v>
+        <v>1.23000005</v>
       </c>
       <c r="K34" s="22" t="n">
-        <v>1.4025122</v>
+        <v>0.44866917</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -12284,38 +12282,40 @@
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>IGAR.JK</t>
+          <t>BENGALT.BO</t>
         </is>
       </c>
       <c r="D35" s="18" t="inlineStr">
         <is>
-          <t>PT Champion Pacific Indonesia Tbk</t>
+          <t>Bengal Tea &amp; Fabrics Limited</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="F35" s="20" t="n">
-        <v/>
-      </c>
-      <c r="G35" s="24" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="H35" s="22" t="n">
-        <v>1.069061043495279</v>
+        <v>1.066842547335759</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>0.60156065</v>
+        <v>0.6536218499999999</v>
       </c>
       <c r="J35" s="23" t="n">
-        <v>1.23000005</v>
+        <v>1.07</v>
       </c>
       <c r="K35" s="22" t="n">
-        <v>0.44866917</v>
+        <v>2.4318655</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -12324,40 +12324,40 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>BENGALT.BO</t>
+          <t>6820.HK</t>
         </is>
       </c>
       <c r="D36" s="18" t="inlineStr">
         <is>
-          <t>Bengal Tea &amp; Fabrics Limited</t>
+          <t>FriendTimes Inc.</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="G36" s="19" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H36" s="22" t="n">
-        <v>1.066842547335759</v>
+        <v>1.063309537487694</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>0.6536218499999999</v>
+        <v>0.49736303</v>
       </c>
       <c r="J36" s="23" t="n">
-        <v>1.07</v>
+        <v>5.63</v>
       </c>
       <c r="K36" s="22" t="n">
-        <v>2.4318655</v>
+        <v>0.3826423671230745</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -12788,22 +12788,22 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>CAAS</t>
+          <t>1V5.F</t>
         </is>
       </c>
       <c r="D47" s="18" t="inlineStr">
         <is>
-          <t>China Automotive Systems, Inc.</t>
+          <t>Zaklady Azotowe Pulawy S.A.</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
@@ -12812,10 +12812,10 @@
         </is>
       </c>
       <c r="H47" s="22" t="n">
-        <v>1.026328294118021</v>
+        <v>1.026905265433991</v>
       </c>
       <c r="I47" s="22" t="n">
-        <v>0.3576042</v>
+        <v>0.07192945000000001</v>
       </c>
       <c r="J47" s="25" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         </is>
       </c>
       <c r="K47" s="22" t="n">
-        <v>0.19008878</v>
+        <v>3.837890044653707</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -12832,40 +12832,42 @@
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>0725.HK</t>
+          <t>CAAS</t>
         </is>
       </c>
       <c r="D48" s="18" t="inlineStr">
         <is>
-          <t>Perennial International Limited</t>
+          <t>China Automotive Systems, Inc.</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="G48" s="21" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H48" s="22" t="n">
-        <v>1.019908786675609</v>
+        <v>1.026328294118021</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>0.40812057</v>
-      </c>
-      <c r="J48" s="23" t="n">
-        <v>9</v>
+        <v>0.3576042</v>
+      </c>
+      <c r="J48" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K48" s="22" t="n">
-        <v>0.47891504</v>
+        <v>0.19008878</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -12874,12 +12876,12 @@
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>1281.HK</t>
+          <t>0725.HK</t>
         </is>
       </c>
       <c r="D49" s="18" t="inlineStr">
         <is>
-          <t>LongiTech Smart Energy Holding Limited</t>
+          <t>Perennial International Limited</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
@@ -12889,27 +12891,25 @@
       </c>
       <c r="F49" s="20" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="G49" s="21" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H49" s="22" t="n">
-        <v>1.019495580900564</v>
+        <v>1.019908786675609</v>
       </c>
       <c r="I49" s="22" t="n">
-        <v>0.1178803625717161</v>
-      </c>
-      <c r="J49" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.40812057</v>
+      </c>
+      <c r="J49" s="23" t="n">
+        <v>9</v>
       </c>
       <c r="K49" s="22" t="n">
-        <v>0.8947578844443459</v>
+        <v>0.47891504</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -12960,22 +12960,22 @@
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>052790.KQ</t>
+          <t>1281.HK</t>
         </is>
       </c>
       <c r="D51" s="18" t="inlineStr">
         <is>
-          <t>Actoz Soft Co.,Ltd.</t>
+          <t>LongiTech Smart Energy Holding Limited</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="F51" s="20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
@@ -12984,10 +12984,10 @@
         </is>
       </c>
       <c r="H51" s="22" t="n">
-        <v>1.015941915770137</v>
+        <v>1.016413963344826</v>
       </c>
       <c r="I51" s="22" t="n">
-        <v>0.183928423362757</v>
+        <v>0.13929923</v>
       </c>
       <c r="J51" s="25" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         </is>
       </c>
       <c r="K51" s="22" t="n">
-        <v>0.6022702</v>
+        <v>0.8947578844443459</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -13004,40 +13004,42 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>3954.T</t>
+          <t>052790.KQ</t>
         </is>
       </c>
       <c r="D52" s="18" t="inlineStr">
         <is>
-          <t>Showa Paxxs Corporation</t>
+          <t>Actoz Soft Co.,Ltd.</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="G52" s="21" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H52" s="22" t="n">
-        <v>1.015602077566072</v>
+        <v>1.015941915770137</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>0.4591028</v>
-      </c>
-      <c r="J52" s="23" t="n">
-        <v>1.72</v>
+        <v>0.183928423362757</v>
+      </c>
+      <c r="J52" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K52" s="22" t="n">
-        <v>0.5316604</v>
+        <v>0.6022702</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -13046,22 +13048,22 @@
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>036190.KQ</t>
+          <t>3954.T</t>
         </is>
       </c>
       <c r="D53" s="18" t="inlineStr">
         <is>
-          <t>Geumhwa Plant Service &amp; Construction Co., Ltd.</t>
+          <t>Showa Paxxs Corporation</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="G53" s="21" t="inlineStr">
@@ -13070,16 +13072,16 @@
         </is>
       </c>
       <c r="H53" s="22" t="n">
-        <v>1.012591896435186</v>
+        <v>1.015602077566072</v>
       </c>
       <c r="I53" s="22" t="n">
-        <v>0.4951807783269601</v>
+        <v>0.4591028</v>
       </c>
       <c r="J53" s="23" t="n">
-        <v>5.11</v>
+        <v>1.72</v>
       </c>
       <c r="K53" s="22" t="n">
-        <v>0.45693028</v>
+        <v>0.5316604</v>
       </c>
     </row>
   </sheetData>
@@ -13149,7 +13151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -13163,7 +13165,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#27    6820.HK    FriendTimes Inc.</t>
+          <t>#27    095660.KQ    NEOWIZ</t>
         </is>
       </c>
     </row>
@@ -13192,7 +13194,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.080518586556192</v>
+        <v>1.077025085586687</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -13210,7 +13212,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
@@ -13222,7 +13224,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13232,10 +13234,8 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>Interactive Media &amp; Services</t>
-        </is>
+      <c r="B8" s="30" t="n">
+        <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>94713120.1414652</v>
+        <v>227119088.1089789</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>247523871.5816361</v>
+        <v>291135327.5719145</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6194442262558337</v>
+        <v>0.5993466395318613</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.7240033398262028</v>
+        <v>0.6323066326254765</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -13331,7 +13331,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.4988244942741952</v>
+        <v>0.5094341592148095</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.7692307692307692</v>
+        <v>0.7051282051282051</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.9622899316797732</v>
+        <v>0.8890977446263806</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.1834</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.4610561285853196</v>
+        <v>0.5028326152844377</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -13393,7 +13393,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.3799833008689863</v>
+        <v>0.6557044396837195</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>-10.65094536225466</v>
+        <v>0.61390554610102</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-38.72885037333177</v>
+        <v>-4.424649065325728</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -13458,7 +13458,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>11.48953160906113</v>
+        <v>24.89423161683539</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -13467,8 +13467,10 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n">
-        <v>3.798693210791965</v>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -13476,7 +13478,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>1.36278816732272</v>
+        <v>15.68365163328275</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -13486,15 +13488,17 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.3826423671230745</v>
+        <v>0.7902293526088751</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
           <t>Insider ownership (%)</t>
         </is>
       </c>
-      <c r="E32" s="23" t="n">
-        <v>59.489</v>
+      <c r="E32" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -13504,7 +13508,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>20.77303497364105</v>
+        <v>18.08190313269434</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -13524,7 +13528,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>119.0793944904485</v>
+        <v>87.81584018740679</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -13532,7 +13536,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>7.337291642658229</v>
+        <v>21.34561440959939</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -13542,7 +13546,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>3.934709164861952</v>
+        <v>7.27833749507558</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -13550,7 +13554,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>-32.55</v>
+        <v>-25.99</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -13570,44 +13574,36 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.38)</t>
+          <t>·  Sub-book  (P/B 0.66)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (59% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
-        </is>
-      </c>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="36" t="n"/>
+      <c r="B42" s="36" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
+      <c r="F42" s="36" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="36" t="n"/>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
-      <c r="F43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="26" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 27 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="B12:E12"/>
@@ -13633,7 +13629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -13647,7 +13643,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#28    095660.KQ    NEOWIZ</t>
+          <t>#28    014570.KQ    Korean Drug Co., Ltd.</t>
         </is>
       </c>
     </row>
@@ -13676,7 +13672,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.077025085586687</v>
+        <v>1.076618108296869</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -13706,7 +13702,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13724,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Small Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -13739,7 +13735,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>227631179.1809044</v>
+        <v>24146193.53754446</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -13749,7 +13745,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>291135327.5719234</v>
+        <v>41049810.50742549</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -13760,7 +13756,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
@@ -13795,7 +13791,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.5993466395318613</v>
+        <v>0.5981211712760384</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -13803,7 +13799,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6323066326254765</v>
+        <v>0.8752685323343624</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -13813,7 +13809,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5094341592148095</v>
+        <v>0.4044118401627878</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -13831,7 +13827,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.7051282051282051</v>
+        <v>0.8846153846153845</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -13849,7 +13845,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.8890977446263806</v>
+        <v>0.919059</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -13857,7 +13853,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -13867,7 +13863,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.5028326152844377</v>
+        <v>0.4079380416059407</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -13875,7 +13871,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -13892,17 +13888,15 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.6557044396837195</v>
+        <v>0.4577384913211642</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
           <t>NCAV / mcap (%)</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E28" s="23" t="n">
+        <v>153.849275908906</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -13912,7 +13906,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>0.61390554610102</v>
+        <v>0.093</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -13920,7 +13914,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-4.424649065325728</v>
+        <v>-3.341676594417583</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -13929,10 +13923,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>0.0915064559526798</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -13940,7 +13932,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>24.89423161683539</v>
+        <v>17.44103613951987</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -13949,10 +13941,8 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C31" s="22" t="n">
+        <v>25.13370454679728</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -13960,7 +13950,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>15.68365163328275</v>
+        <v>16.4298547876868</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -13970,17 +13960,15 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.7902293526088751</v>
+        <v>0.5645629</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
           <t>Insider ownership (%)</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E32" s="23" t="n">
+        <v>50.193</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -13990,7 +13978,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>18.08190313269434</v>
+        <v>28.5107551365251</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -14010,7 +13998,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>87.81584018740679</v>
+        <v>91.460965287107</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -14018,7 +14006,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>21.34561440959939</v>
+        <v>-14.02875104746569</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -14028,7 +14016,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>7.27833749507558</v>
+        <v>9.813565006941566</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -14036,7 +14024,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>-25.99</v>
+        <v>-13.08</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -14056,38 +14044,63 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.66)</t>
+          <t>·  Graham net-net  (mcap &lt; NCAV)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="36" t="n"/>
-      <c r="B42" s="36" t="n"/>
-      <c r="C42" s="36" t="n"/>
-      <c r="D42" s="36" t="n"/>
-      <c r="E42" s="36" t="n"/>
-      <c r="F42" s="36" t="n"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="26" t="inlineStr">
+          <t>·  Sub-book  (P/B 0.46)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (50% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.4x); Graham net-net (mcap 0.65x NCAV); cash 92% of mcap; cash &gt; EV (9.81x, net cash 91% mcap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1"/>
+    <row r="46" ht="18" customHeight="1"/>
+    <row r="49">
+      <c r="A49" s="36" t="n"/>
+      <c r="B49" s="36" t="n"/>
+      <c r="C49" s="36" t="n"/>
+      <c r="D49" s="36" t="n"/>
+      <c r="E49" s="36" t="n"/>
+      <c r="F49" s="36" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 28 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
@@ -14096,6 +14109,7 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B44:E46"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -14125,7 +14139,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#29    014570.KQ    Korean Drug Co., Ltd.</t>
+          <t>#29    TCID.JK    PT. Mandom Indonesia Tbk</t>
         </is>
       </c>
     </row>
@@ -14143,9 +14157,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -14154,7 +14168,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.076618108296869</v>
+        <v>1.073817836048235</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -14172,7 +14186,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ID</t>
         </is>
       </c>
     </row>
@@ -14182,10 +14196,8 @@
           <t>Sector</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
+      <c r="B7" s="30" t="n">
+        <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
@@ -14206,7 +14218,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Mega Cap</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14229,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>24818887.73322535</v>
+        <v>56815040.56741953</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -14227,7 +14239,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>41049810.50742675</v>
+        <v>118256574.242592</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -14252,7 +14264,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>Japanese parent Mandom Corp 60%; 99.93% payout culture; Gatsby/Pixy brands real category leadership; 3-5% yield</t>
         </is>
       </c>
     </row>
@@ -14273,7 +14285,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.5981211712760384</v>
+        <v>0.5775986210044186</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -14281,7 +14293,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.8752685323343624</v>
+        <v>0.6487400331688689</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -14291,7 +14303,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.4044118401627878</v>
+        <v>0.5204474604984813</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -14299,7 +14311,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -14309,7 +14321,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.8846153846153845</v>
+        <v>0.641025641025641</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -14327,7 +14339,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.919059</v>
+        <v>0.612465</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -14335,7 +14347,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.2</v>
+        <v>1.2083</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -14345,7 +14357,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.4079380416059407</v>
+        <v>0.4304861925012495</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -14353,7 +14365,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -14370,7 +14382,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.4577384913211642</v>
+        <v>0.5712140999999999</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -14378,7 +14390,7 @@
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>153.849275908906</v>
+        <v>103.5602755711481</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -14388,7 +14400,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>0.093</v>
+        <v>9.26</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -14396,7 +14408,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-3.341676594417583</v>
+        <v>-17.22501908711128</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -14405,8 +14417,10 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="22" t="n">
-        <v>0.0915064559526798</v>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -14414,7 +14428,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>17.44103613951987</v>
+        <v>6.397833869051651</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -14424,7 +14438,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>25.13370454679728</v>
+        <v>98.032196</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -14432,7 +14446,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>16.4298547876868</v>
+        <v>1.78694331523505</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -14442,7 +14456,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.5645629</v>
+        <v>0.5015371</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -14450,7 +14464,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>50.193</v>
+        <v>78.369004</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -14460,7 +14474,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>28.5107551365251</v>
+        <v>8.56843258100065</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -14480,7 +14494,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>91.460965287107</v>
+        <v>59.22714347477071</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -14488,7 +14502,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>-14.02875104746569</v>
+        <v>15.69105868985647</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -14498,7 +14512,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>9.813565006941566</v>
+        <v>1.47068563659409</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -14506,7 +14520,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>-13.08</v>
+        <v>-15.81</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -14526,21 +14540,21 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Graham net-net  (mcap &lt; NCAV)</t>
+          <t>·  Sub-book  (P/B 0.57)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.46)</t>
+          <t>·  Insider-aligned  (78% insider)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (50% insider)</t>
+          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14568,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.4x); Graham net-net (mcap 0.65x NCAV); cash 92% of mcap; cash &gt; EV (9.81x, net cash 91% mcap)</t>
+          <t>growth-flip; first-positive: FCF/EBITDA/NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 6.1x); cash 60% of mcap; cash &gt; EV (1.47x, net cash 59% mcap)</t>
         </is>
       </c>
     </row>
@@ -14607,6 +14621,496 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#30    348350.KQ    WITHTECH Co., LTD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>1.07027397463544</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Large Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n">
+        <v>58876338.41682063</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n">
+        <v>37014740.9562481</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>0.588439175935826</v>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>0.6915751368798955</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>0.5626735786360552</v>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>0.6153846153846153</v>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>0.694261</v>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>1.2617</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>0.467269358229353</v>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>0.7937623623751395</v>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="n">
+        <v>75.63918384940335</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>1.517</v>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>-8.698986782148422</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>6.48271546413415</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="n">
+        <v>6.361932033025235</v>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>13.42176912304436</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n">
+        <v>1.4025122</v>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>57.577</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>18.71203545054837</v>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>72.92765548622091</v>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="n">
+        <v>29.74903547376832</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>27.45971875741036</v>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>20.77</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.79)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (58% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>growth-flip; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 2.8x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1"/>
+    <row r="45" ht="18" customHeight="1"/>
+    <row r="48">
+      <c r="A48" s="36" t="n"/>
+      <c r="B48" s="36" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="36" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="26" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 30 of 50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B43:E45"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00707070"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14621,7 +15125,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#30    TCID.JK    PT. Mandom Indonesia Tbk</t>
+          <t>#31    IGAR.JK    PT Champion Pacific Indonesia Tbk</t>
         </is>
       </c>
     </row>
@@ -14639,9 +15143,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -14650,7 +15154,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.073817836048235</v>
+        <v>1.069061043495279</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -14711,7 +15215,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>56372901.44959808</v>
+        <v>23665919.52022672</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -14721,7 +15225,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>118256574.242592</v>
+        <v>49743837.46728887</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -14746,7 +15250,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Japanese parent Mandom Corp 60%; 99.93% payout culture; Gatsby/Pixy brands real category leadership; 3-5% yield</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -14767,7 +15271,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.5775986210044186</v>
+        <v>0.5842598879828441</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -14775,7 +15279,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6487400331688689</v>
+        <v>0.7138157648456206</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -14785,7 +15289,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5204474604984813</v>
+        <v>0.3858847841021246</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -14793,7 +15297,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -14803,7 +15307,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.641025641025641</v>
+        <v>0.8846153846153845</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -14821,7 +15325,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.612465</v>
+        <v>0.779851</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -14829,7 +15333,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.2083</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -14839,7 +15343,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.4304861925012495</v>
+        <v>0.308765309669861</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -14847,7 +15351,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -14864,7 +15368,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.5712140999999999</v>
+        <v>0.60156065</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -14872,7 +15376,7 @@
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>103.5602755711481</v>
+        <v>164.6861139955122</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -14882,7 +15386,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>9.26</v>
+        <v>2.152790690800193</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -14890,7 +15394,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-17.22501908711128</v>
+        <v>-4.415208898821855</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -14910,7 +15414,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>6.397833869051651</v>
+        <v>43.62067588625837</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -14920,7 +15424,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>98.032196</v>
+        <v>6.309491</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -14928,7 +15432,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>1.78694331523505</v>
+        <v>11.49414998827318</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -14938,7 +15442,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.5015371</v>
+        <v>0.44866917</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -14946,7 +15450,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>78.369004</v>
+        <v>88.881</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -14956,7 +15460,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>8.56843258100065</v>
+        <v>14.9728231439858</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -14976,7 +15480,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>59.22714347477071</v>
+        <v>110.4800825407801</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -14984,7 +15488,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>15.69105868985647</v>
+        <v>4.10990513790382</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -14994,7 +15498,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>1.47068563659409</v>
+        <v>2.324572062843816</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -15002,7 +15506,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>-15.81</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -15022,21 +15526,21 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.57)</t>
+          <t>·  Graham net-net  (mcap &lt; NCAV)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (78% insider)</t>
+          <t>·  Sub-book  (P/B 0.60)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
+          <t>·  Insider-aligned  (89% insider)</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15554,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; first-positive: FCF/EBITDA/NI/ROCE; ROCE improving from &lt;=0; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 6.1x); cash 60% of mcap; cash &gt; EV (1.47x, net cash 59% mcap)</t>
+          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.9x); Graham net-net (mcap 0.61x NCAV); cash 111% of mcap; cash &gt; EV (2.32x, net cash 110% mcap)</t>
         </is>
       </c>
     </row>
@@ -15067,7 +15571,7 @@
     <row r="50">
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 30 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 31 of 50</t>
         </is>
       </c>
     </row>
@@ -15088,496 +15592,6 @@
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B44:E46"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00707070"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>#31    348350.KQ    WITHTECH Co., LTD.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="n">
-        <v>1.07027397463544</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>Large Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n">
-        <v>60858057.77970123</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n">
-        <v>37014740.95624924</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>0.588439175935826</v>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>0.6915751368798955</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>0.5626735786360552</v>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>0.6153846153846153</v>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="n">
-        <v>0.694261</v>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="n">
-        <v>1.2617</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="n">
-        <v>0.467269358229353</v>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>0.7937623623751395</v>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="n">
-        <v>75.63918384940335</v>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>1.517</v>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="n">
-        <v>-8.698986782148422</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="n">
-        <v>6.48271546413415</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n">
-        <v>6.361932033025235</v>
-      </c>
-      <c r="D31" s="33" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="n">
-        <v>13.42176912304436</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n">
-        <v>1.4025122</v>
-      </c>
-      <c r="D32" s="33" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="n">
-        <v>57.577</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="n">
-        <v>18.71203545054837</v>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>72.92765548622091</v>
-      </c>
-      <c r="D34" s="33" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="n">
-        <v>29.74903547376832</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n">
-        <v>27.45971875741036</v>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="n">
-        <v>20.77</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>·  Sub-book  (P/B 0.79)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>·  Insider-aligned  (58% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 2.8x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="36" t="n"/>
-      <c r="B48" s="36" t="n"/>
-      <c r="C48" s="36" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="36" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="26" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 31 of 50</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -15607,7 +15621,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#32    IGAR.JK    PT Champion Pacific Indonesia Tbk</t>
+          <t>#32    BENGALT.BO    Bengal Tea &amp; Fabrics Limited</t>
         </is>
       </c>
     </row>
@@ -15625,9 +15639,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="38" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -15636,7 +15650,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.069061043495279</v>
+        <v>1.066842547335759</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -15654,7 +15668,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
@@ -15664,8 +15678,10 @@
           <t>Sector</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
-        <v/>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
@@ -15686,7 +15702,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Mega Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -15697,7 +15713,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>24175962.39553988</v>
+        <v>13364747.41860322</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -15707,7 +15723,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>49743837.46728887</v>
+        <v>5534877.479667741</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -15718,7 +15734,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-09-30</t>
         </is>
       </c>
     </row>
@@ -15732,7 +15748,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>BK Birla group offshoot; tea+fabric conglomerate discount real but check promoter cross-holdings and segment EBIT honesty</t>
         </is>
       </c>
     </row>
@@ -15753,7 +15769,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.5842598879828441</v>
+        <v>0.6972827106769669</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -15761,7 +15777,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.7138157648456206</v>
+        <v>0.7989604609929413</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -15771,7 +15787,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.3858847841021246</v>
+        <v>0.6320641321917244</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -15779,7 +15795,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -15789,7 +15805,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.8846153846153845</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -15807,7 +15823,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.779851</v>
+        <v>0.918984</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -15815,7 +15831,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -15825,7 +15841,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.308765309669861</v>
+        <v>0.4734316608513833</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -15833,7 +15849,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -15850,7 +15866,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.60156065</v>
+        <v>0.6536218499999999</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -15858,7 +15874,7 @@
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>164.6861139955122</v>
+        <v>94.33666693235584</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -15868,7 +15884,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>2.152790690800193</v>
+        <v>0.148</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -15876,7 +15892,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-4.415208898821855</v>
+        <v>-49.22599432906736</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -15896,7 +15912,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>43.62067588625837</v>
+        <v>23.06910778751934</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -15906,7 +15922,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>6.309491</v>
+        <v>19.346048</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -15914,7 +15930,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>11.49414998827318</v>
+        <v>4.92765608744333</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -15924,7 +15940,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.44866917</v>
+        <v>2.4318655</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -15932,7 +15948,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>88.881</v>
+        <v>84.797996</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -15942,7 +15958,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>14.9728231439858</v>
+        <v>12.82322950167912</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -15962,7 +15978,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>110.4800825407801</v>
+        <v>92.80615316949594</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -15970,7 +15986,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>4.10990513790382</v>
+        <v>32.22922398597871</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -15980,7 +15996,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>2.324572062843816</v>
+        <v>12.54245137388083</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -15988,7 +16004,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>-5.53</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -16008,21 +16024,21 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Graham net-net  (mcap &lt; NCAV)</t>
+          <t>·  Sub-book  (P/B 0.65)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.60)</t>
+          <t>·  Insider-aligned  (85% insider)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (89% insider)</t>
+          <t>·  Cluster stack  (5 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
@@ -16036,7 +16052,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.9x); Graham net-net (mcap 0.61x NCAV); cash 111% of mcap; cash &gt; EV (2.32x, net cash 110% mcap)</t>
+          <t>growth-flip; first-positive: NI; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.6x); cash 99% of mcap; cash &gt; EV (12.54x, net cash 93% mcap)</t>
         </is>
       </c>
     </row>
@@ -16089,7 +16105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -16103,7 +16119,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#33    BENGALT.BO    Bengal Tea &amp; Fabrics Limited</t>
+          <t>#33    6820.HK    FriendTimes Inc.</t>
         </is>
       </c>
     </row>
@@ -16121,9 +16137,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="38" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -16132,7 +16148,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.066842547335759</v>
+        <v>1.063309537487694</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -16150,7 +16166,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>HK</t>
         </is>
       </c>
     </row>
@@ -16162,7 +16178,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
     </row>
@@ -16172,8 +16188,10 @@
           <t>Industry</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
-        <v/>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Interactive Media &amp; Services</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
@@ -16184,7 +16202,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
     </row>
@@ -16195,7 +16213,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>13105923.0400461</v>
+        <v>94713120.14146514</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -16205,7 +16223,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>5534877.479667775</v>
+        <v>247523871.5816361</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -16216,7 +16234,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>–</t>
         </is>
       </c>
     </row>
@@ -16230,7 +16248,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>BK Birla group offshoot; tea+fabric conglomerate discount real but check promoter cross-holdings and segment EBIT honesty</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -16251,7 +16269,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6972827106769669</v>
+        <v>0.6194442262558337</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -16259,7 +16277,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.7989604609929413</v>
+        <v>0.700527394</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -16269,7 +16287,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.6320641321917244</v>
+        <v>0.4988244942741952</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -16277,7 +16295,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -16305,7 +16323,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.918984</v>
+        <v>0.9622899316797732</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -16313,7 +16331,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.2</v>
+        <v>1.1834</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -16323,7 +16341,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.4734316608513833</v>
+        <v>0.4610561285853196</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -16348,15 +16366,17 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.6536218499999999</v>
+        <v>0.49736303</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
           <t>NCAV / mcap (%)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="n">
-        <v>94.33666693235584</v>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -16366,7 +16386,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>0.148</v>
+        <v>-10.65094536225466</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -16374,7 +16394,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-49.22599432906736</v>
+        <v>-38.72885037333177</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -16394,7 +16414,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>23.06910778751934</v>
+        <v>11.48953160906113</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -16404,7 +16424,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>19.346048</v>
+        <v>3.798693210791965</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -16412,7 +16432,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>4.92765608744333</v>
+        <v>1.36278816732272</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -16422,7 +16442,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>2.4318655</v>
+        <v>0.3826423671230745</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -16430,7 +16450,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>84.797996</v>
+        <v>59.489</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -16440,7 +16460,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>12.82322950167912</v>
+        <v>20.77303497364105</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -16460,7 +16480,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>92.80615316949594</v>
+        <v>119.0793944904485</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -16468,7 +16488,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>32.22922398597871</v>
+        <v>7.337291642658229</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -16478,7 +16498,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>12.54245137388083</v>
+        <v>3.934709164861952</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -16486,7 +16506,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>8.369999999999999</v>
+        <v>-32.55</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -16506,14 +16526,14 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.65)</t>
+          <t>·  Sub-book  (P/B 0.50)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (85% insider)</t>
+          <t>·  Insider-aligned  (59% insider)</t>
         </is>
       </c>
     </row>
@@ -16524,45 +16544,28 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; first-positive: NI; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.6x); cash 99% of mcap; cash &gt; EV (12.54x, net cash 93% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="46" ht="18" customHeight="1"/>
-    <row r="49">
-      <c r="A49" s="36" t="n"/>
-      <c r="B49" s="36" t="n"/>
-      <c r="C49" s="36" t="n"/>
-      <c r="D49" s="36" t="n"/>
-      <c r="E49" s="36" t="n"/>
-      <c r="F49" s="36" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="26" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="36" t="n"/>
+      <c r="B43" s="36" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 33 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
@@ -16571,7 +16574,6 @@
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B44:E46"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -16693,7 +16695,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>87192185.23034763</v>
+        <v>88338287.18595138</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -16703,7 +16705,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>387812025.290559</v>
+        <v>387812025.2905471</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -17173,7 +17175,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>624246983.235302</v>
+        <v>646742342.4944687</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -17663,7 +17665,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>65859172.35604763</v>
+        <v>64263095.03524991</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -17673,7 +17675,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>82321438.99549031</v>
+        <v>82321438.99548995</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -18159,7 +18161,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>35330243.9018116</v>
+        <v>34909646.27042425</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -18169,7 +18171,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>216015408.892177</v>
+        <v>216015408.8921704</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -18665,7 +18667,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>127855413.6385498</v>
+        <v>125759425.1632687</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -18675,7 +18677,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>71113427.56021285</v>
+        <v>71113427.56021267</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -19147,7 +19149,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>29092297.90078092</v>
+        <v>28599209.57540799</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -19629,7 +19631,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>50909684.39264202</v>
+        <v>50524003.66617677</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -19639,7 +19641,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>89795964.46359158</v>
+        <v>89795964.46359153</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -20129,7 +20131,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>87952045.37611961</v>
+        <v>87952045.37611957</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -20139,7 +20141,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>461430088.9879614</v>
+        <v>461430088.9879612</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -20619,7 +20621,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>30341326.35495377</v>
+        <v>29658799.91638808</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -20629,7 +20631,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>89068535.34864391</v>
+        <v>89068535.34864119</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -21109,7 +21111,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>62558644.65229607</v>
+        <v>64731618.55333321</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -21119,7 +21121,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>390351789.1708</v>
+        <v>390351789.170788</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -21599,7 +21601,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>27787918.80877018</v>
+        <v>28617906.59480798</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -21609,7 +21611,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>76986125.38898829</v>
+        <v>76986125.38898796</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -21989,7 +21991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -22003,7 +22005,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#44    CAAS    China Automotive Systems, Inc.</t>
+          <t>#44    1V5.F    Zaklady Azotowe Pulawy S.A.</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22034,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.026328294118021</v>
+        <v>1.026905265433991</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -22050,7 +22052,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>PL</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22064,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
     </row>
@@ -22074,7 +22076,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -22086,7 +22088,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Small Cap</t>
         </is>
       </c>
     </row>
@@ -22097,7 +22099,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>162921792</v>
+        <v>228294787.022644</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -22107,7 +22109,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>765736000</v>
+        <v>59484452.22933506</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -22118,7 +22120,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>–</t>
         </is>
       </c>
     </row>
@@ -22153,7 +22155,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.5793782759030126</v>
+        <v>0.5905868479636597</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -22161,7 +22163,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6126387733251275</v>
+        <v>0.7014089319704393</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -22171,7 +22173,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5155073222606764</v>
+        <v>0.5869928030279979</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -22189,7 +22191,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.6511627906976745</v>
+        <v>0.5942028985507245</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -22207,7 +22209,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.7110674193484872</v>
+        <v>0.8433652825604028</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -22215,7 +22217,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.3</v>
+        <v>1.198</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -22225,7 +22227,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.6177871059013622</v>
+        <v>0.6549592322937731</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -22250,15 +22252,17 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.3576042</v>
+        <v>0.07192945000000001</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
           <t>NCAV / mcap (%)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="n">
-        <v>117.9530386236229</v>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -22268,7 +22272,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>2.777771335984681</v>
+        <v>18.81984303849444</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -22276,7 +22280,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-0.8935041979673001</v>
+        <v>-1.270812315309707</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -22285,8 +22289,10 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="22" t="n">
-        <v>2.890987168635948</v>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -22294,7 +22300,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>15.74238506042344</v>
+        <v>-5.85163945049248</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -22303,8 +22309,10 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="C31" s="22" t="n">
-        <v>2.7684212</v>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -22312,7 +22320,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>8.865979919972409</v>
+        <v>20.39278455619219</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -22322,7 +22330,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.19008878</v>
+        <v>3.837890044653707</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -22330,7 +22338,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>64.765</v>
+        <v>95.975995</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -22339,8 +22347,10 @@
           <t>FCF yield (%)</t>
         </is>
       </c>
-      <c r="C33" s="23" t="n">
-        <v>45.69247556520861</v>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -22360,7 +22370,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>45.2828768914895</v>
+        <v>87.2456000630648</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -22368,7 +22378,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>17.63632313518247</v>
+        <v>13.00334076107754</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -22378,7 +22388,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>1.536442869830014</v>
+        <v>21.94434020049347</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -22386,7 +22396,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>26.46</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -22399,43 +22409,51 @@
     <row r="38" ht="16" customHeight="1">
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.36)</t>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (65% insider)</t>
+          <t>·  Sub-book  (P/B 0.07)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
+          <t>·  Insider-aligned  (96% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="35" t="inlineStr">
+        <is>
           <t>·  Cluster stack  (4 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="36" t="n"/>
-      <c r="B42" s="36" t="n"/>
-      <c r="C42" s="36" t="n"/>
-      <c r="D42" s="36" t="n"/>
-      <c r="E42" s="36" t="n"/>
-      <c r="F42" s="36" t="n"/>
-    </row>
     <row r="43">
-      <c r="B43" s="26" t="inlineStr">
+      <c r="A43" s="36" t="n"/>
+      <c r="B43" s="36" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 44 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="B12:E12"/>
@@ -22461,7 +22479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -22475,7 +22493,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#45    0725.HK    Perennial International Limited</t>
+          <t>#45    CAAS    China Automotive Systems, Inc.</t>
         </is>
       </c>
     </row>
@@ -22493,9 +22511,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -22504,7 +22522,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.019908786675609</v>
+        <v>1.026328294118021</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -22522,7 +22540,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22552,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
     </row>
@@ -22546,7 +22564,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Auto Components</t>
         </is>
       </c>
     </row>
@@ -22558,7 +22576,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -22569,7 +22587,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>25007163.94232941</v>
+        <v>158697904</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -22579,7 +22597,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>50498298.96777868</v>
+        <v>765736000</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -22604,7 +22622,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Perennial International - electric cable family business; ~6% TTM dividend yield with intact payouts; P/B 0.46</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -22625,7 +22643,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6381708462961632</v>
+        <v>0.5793782759030126</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -22633,7 +22651,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.4716463047139654</v>
+        <v>0.6126387733251275</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -22643,7 +22661,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5294406377810695</v>
+        <v>0.5155073222606764</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -22651,7 +22669,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -22661,7 +22679,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.7692307692307692</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -22669,7 +22687,7 @@
         </is>
       </c>
       <c r="E23" s="22" t="n">
-        <v>0.991</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -22679,7 +22697,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.820348</v>
+        <v>0.7110674193484872</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -22687,7 +22705,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -22697,7 +22715,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.5524636352202518</v>
+        <v>0.6177871059013622</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -22705,7 +22723,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -22722,7 +22740,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.40812057</v>
+        <v>0.3576042</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -22730,7 +22748,7 @@
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>119.585308118896</v>
+        <v>117.9530386236229</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -22740,7 +22758,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>1.985515932474278</v>
+        <v>2.777771335984681</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -22748,7 +22766,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-2.129477574667865</v>
+        <v>-0.8935041979673001</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -22757,10 +22775,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>2.890987168635948</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -22768,7 +22784,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>11.90882409257052</v>
+        <v>15.74238506042344</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -22778,7 +22794,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>6.5</v>
+        <v>2.7684212</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -22786,7 +22802,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>12.64845605700712</v>
+        <v>8.865979919972409</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -22796,7 +22812,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.47891504</v>
+        <v>0.19008878</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -22804,7 +22820,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>74.361</v>
+        <v>64.765</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -22814,7 +22830,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>24.22527118078666</v>
+        <v>45.69247556520861</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -22834,7 +22850,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>50.5420998322809</v>
+        <v>45.2828768914895</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -22842,7 +22858,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>20.44019989165434</v>
+        <v>17.63632313518247</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -22852,7 +22868,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>1.021921589561637</v>
+        <v>1.536442869830014</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -22860,7 +22876,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>32.5</v>
+        <v>26.46</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -22873,57 +22889,41 @@
     <row r="38" ht="16" customHeight="1">
       <c r="B38" s="35" t="inlineStr">
         <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
+          <t>·  Sub-book  (P/B 0.36)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.41)</t>
+          <t>·  Insider-aligned  (65% insider)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (74% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; accelerating sales; cheap+grow (EV/EBIT 2.5x); cash 51% of mcap; cash &gt; EV (1.02x, net cash 51% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="36" t="n"/>
-      <c r="B48" s="36" t="n"/>
-      <c r="C48" s="36" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="36" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="26" t="inlineStr">
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="36" t="n"/>
+      <c r="B42" s="36" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
+      <c r="F42" s="36" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 45 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="15">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B8:E8"/>
@@ -22932,8 +22932,6 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
@@ -22953,7 +22951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -22967,7 +22965,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#46    1281.HK    LongiTech Smart Energy Holding Limited</t>
+          <t>#46    0725.HK    Perennial International Limited</t>
         </is>
       </c>
     </row>
@@ -22985,9 +22983,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -22996,7 +22994,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.019495580900564</v>
+        <v>1.019908786675609</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -23026,7 +23024,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -23038,7 +23036,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Independent Power and Renewable Electricity Producers</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
     </row>
@@ -23061,7 +23059,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>17239267.37836957</v>
+        <v>24753283.59752344</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -23071,7 +23069,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>19266963.3630279</v>
+        <v>50498298.96777866</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -23082,7 +23080,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>2025-12-31</t>
         </is>
       </c>
     </row>
@@ -23096,7 +23094,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>Perennial International - electric cable family business; ~6% TTM dividend yield with intact payouts; P/B 0.46</t>
         </is>
       </c>
     </row>
@@ -23117,7 +23115,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6291497860677019</v>
+        <v>0.6381708462961632</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -23125,7 +23123,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6672064051475415</v>
+        <v>0.4716463047139654</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -23135,7 +23133,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5145782893017455</v>
+        <v>0.5294406377810695</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -23143,7 +23141,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -23161,7 +23159,7 @@
         </is>
       </c>
       <c r="E23" s="22" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -23171,7 +23169,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.8794749681014746</v>
+        <v>0.820348</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -23179,7 +23177,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.1434</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -23189,7 +23187,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.4655292998699878</v>
+        <v>0.5524636352202518</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -23197,7 +23195,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -23214,17 +23212,15 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.1178803625717161</v>
+        <v>0.40812057</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
           <t>NCAV / mcap (%)</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E28" s="23" t="n">
+        <v>119.585308118896</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -23234,7 +23230,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>-3.355922619636716</v>
+        <v>1.985515932474278</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -23242,7 +23238,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-7.396120066301267</v>
+        <v>-2.129477574667865</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -23262,7 +23258,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>2.15667527759927</v>
+        <v>11.90882409257052</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -23272,7 +23268,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>7.50352403384571</v>
+        <v>6.5</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -23280,7 +23276,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>31.31714285714285</v>
+        <v>12.64845605700712</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -23290,7 +23286,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.8947578844443459</v>
+        <v>0.47891504</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -23298,7 +23294,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>65.373003</v>
+        <v>74.361</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -23307,10 +23303,8 @@
           <t>FCF yield (%)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C33" s="23" t="n">
+        <v>24.22527118078666</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -23330,7 +23324,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>181.9727797636792</v>
+        <v>50.5420998322809</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -23338,7 +23332,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>22.5586749656398</v>
+        <v>20.44019989165434</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -23348,7 +23342,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>1.54376636882513</v>
+        <v>1.021921589561637</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -23356,7 +23350,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>-24.14</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -23376,50 +23370,60 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.12)</t>
+          <t>·  Sub-book  (P/B 0.41)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (65% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="36" t="n"/>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
-      <c r="F43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="26" t="inlineStr">
+          <t>·  Insider-aligned  (74% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>growth-flip; accelerating sales; cheap+grow (EV/EBIT 2.5x); cash 51% of mcap; cash &gt; EV (1.02x, net cash 51% mcap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1"/>
+    <row r="45" ht="18" customHeight="1"/>
+    <row r="48">
+      <c r="A48" s="36" t="n"/>
+      <c r="B48" s="36" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="36" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 46 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
@@ -24045,7 +24049,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>21238329.13709617</v>
+        <v>20459466.81140074</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -24055,7 +24059,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>8563148.622397322</v>
+        <v>8563148.62239706</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -24431,6 +24435,492 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#48    1281.HK    LongiTech Smart Energy Holding Limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>1.016413963344826</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Independent Power and Renewable Electricity Producers</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Nano Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n">
+        <v>17239267.37836956</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n">
+        <v>19266963.3630279</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>0.6291497860677019</v>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>0.6629226316618847</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>0.5145782893017455</v>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>0.8794749681014746</v>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>1.1434</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>0.4655292998699878</v>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>0.13929923</v>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>-3.355922619636716</v>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>-7.396120066301267</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>2.15667527759927</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="n">
+        <v>7.50352403384571</v>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>31.31714285714285</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n">
+        <v>0.8947578844443459</v>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>65.373003</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>181.9727797636792</v>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="n">
+        <v>22.5586749656398</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>1.54376636882513</v>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>-24.14</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (65% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="n"/>
+      <c r="B43" s="36" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 48 of 50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00707070"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -24445,7 +24935,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#48    052790.KQ    Actoz Soft Co.,Ltd.</t>
+          <t>#49    052790.KQ    Actoz Soft Co.,Ltd.</t>
         </is>
       </c>
     </row>
@@ -24537,7 +25027,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>29189193.77843904</v>
+        <v>29224919.38030916</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -24547,7 +25037,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>43532230.22913835</v>
+        <v>43532230.22913702</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -24888,7 +25378,7 @@
     <row r="49">
       <c r="B49" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 48 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 49 of 50</t>
         </is>
       </c>
     </row>
@@ -24916,7 +25406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00707070"/>
@@ -24937,7 +25427,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#49    3954.T    Showa Paxxs Corporation</t>
+          <t>#50    3954.T    Showa Paxxs Corporation</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25521,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>84707937.1239996</v>
+        <v>80246742.39991631</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -25041,7 +25531,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>145366592.7187284</v>
+        <v>145366592.7187277</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -25385,7 +25875,7 @@
     <row r="50">
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 49 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 50 of 50</t>
         </is>
       </c>
     </row>
@@ -25406,496 +25896,6 @@
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="B44:E46"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00707070"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>#50    036190.KQ    Geumhwa Plant Service &amp; Construction Co., Ltd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="n">
-        <v>1.012591896435186</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>Micro Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n">
-        <v>130563355.2429657</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n">
-        <v>275616874.9640363</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>Korean power-plant maintenance/EPC with nuclear exposure into a confirmed SMR upcycle (Feb-2026 SMR Special Act); 3Q25 revenue +43% YoY to 93.8B KRW, 4.5% dividend yield, EPS guidance to KRW5,119</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>0.5512548460316921</v>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>0.641579735904684</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>0.3950464768554518</v>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>0.7692307692307692</v>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="n">
-        <v>0.536955</v>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="n">
-        <v>0.4426237147801244</v>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>0.4951807783269601</v>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="n">
-        <v>97.13932449961075</v>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>1.498</v>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="n">
-        <v>-3.141017358294149</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="n">
-        <v>14.99143654608343</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n">
-        <v>6.755750320078609</v>
-      </c>
-      <c r="D31" s="33" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="n">
-        <v>10.20078968125122</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n">
-        <v>0.45693028</v>
-      </c>
-      <c r="D32" s="33" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="n">
-        <v>44.772997</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="n">
-        <v>14.74511619750453</v>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>72.00482746381182</v>
-      </c>
-      <c r="D34" s="33" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="n">
-        <v>23.85416843924622</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n">
-        <v>2.737636802392253</v>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="n">
-        <v>9.790000000000001</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>·  Sub-book  (P/B 0.50)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>·  Insider-aligned  (45% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>accelerating sales; cheap+grow (EV/EBIT 1.6x); cash 84% of mcap; cash &gt; EV (2.74x, net cash 72% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="36" t="n"/>
-      <c r="B48" s="36" t="n"/>
-      <c r="C48" s="36" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="36" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="26" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 50 of 50</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -25987,7 +25987,7 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>26154</v>
+        <v>26385</v>
       </c>
       <c r="D5" s="31" t="n">
         <v>122</v>
@@ -25996,13 +25996,13 @@
         <v>180</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G5" s="31" t="n">
-        <v>25755</v>
+        <v>25984</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.525579261298463</v>
+        <v>1.519802918324806</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
@@ -26055,7 +26055,7 @@
         <v>50</v>
       </c>
       <c r="D9" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="31" t="n">
         <v>3</v>
@@ -26064,10 +26064,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" s="42" t="n">
-        <v>56.00000000000001</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -26252,16 +26252,16 @@
         <v>1</v>
       </c>
       <c r="E18" s="34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" s="23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>96578076.43704414</v>
+        <v>96779704.39330758</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -26626,7 +26626,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>293732750.4359149</v>
+        <v>293732750.4359059</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -27100,7 +27100,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>49566784.38127041</v>
+        <v>50583538.93268106</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -27110,7 +27110,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>82663114.82569575</v>
+        <v>82663114.82569572</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -27490,6 +27490,488 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#05    3798.HK    Homeland Interactive Technology Ltd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Entry-today score</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="n">
+        <v>1.214607294531874</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SNAPSHOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Interactive Media &amp; Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Small Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>Market cap (USD)</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="n">
+        <v>196398350.8262919</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Revenue TTM (USD)</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n">
+        <v>183954166.1063843</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>As-of</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>SCORE DECOMPOSITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Asymmetry (raw)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>0.6573455939461111</v>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>Intrinsic discount</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="n">
+        <v>0.671342612</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>Upside leg</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>0.5617341988444753</v>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>Qual multiplier (x)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>Downside floor</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>0.7692307692307692</v>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>Post-rally factor (x)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>Yartseva composite</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>0.8495485218474618</v>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>Confirmation (x)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>Berezin growth</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>0.4128425191777984</v>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>Cluster signals (of 7)</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>VALUATION &amp; BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>0.64328694</v>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>NCAV / mcap (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="n">
+        <v>-1.47356998523237</v>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA (x)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>-7.225898256848096</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>EV / EBIT</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="n">
+        <v>0.9912811803599012</v>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>ROCE (%)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>33.75755216989689</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="n">
+        <v>21.73689776387475</v>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>EBITDA margin (%)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>19.092307888602</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="n">
+        <v>1.06764828969794</v>
+      </c>
+      <c r="D32" s="33" t="inlineStr">
+        <is>
+          <t>Insider ownership (%)</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>74.694</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>FCF yield (%)</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>17.29941120876121</v>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
+        <is>
+          <t>Rev 3y CAGR (%)</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Net cash / mcap (%)</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>126.3512358188845</v>
+      </c>
+      <c r="D34" s="33" t="inlineStr">
+        <is>
+          <t>Rev YoY (TTM, %)</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="n">
+        <v>-2.6933510331294</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>Cash / EV (x)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>3.142024571801568</v>
+      </c>
+      <c r="D35" s="33" t="inlineStr">
+        <is>
+          <t>12m price momentum (%)</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>-18.09</v>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>SIGNALS FIRING</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>·  Cash &gt; EV  (downside floor in place)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="B39" s="35" t="inlineStr">
+        <is>
+          <t>·  Sub-book  (P/B 0.64)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>·  Insider-aligned  (75% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="n"/>
+      <c r="B43" s="36" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>Asymmetry Workbook  ·  Sheet 05 of 50</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B15:E18"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00707070"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -27504,7 +27986,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#05    003650.KS    Michang Oil Ind .Co.,Ltd.</t>
+          <t>#06    003650.KS    Michang Oil Ind .Co.,Ltd.</t>
         </is>
       </c>
     </row>
@@ -27598,7 +28080,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>129835458.4956131</v>
+        <v>129835458.4956091</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -27608,7 +28090,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>265260383.0321121</v>
+        <v>265260383.032104</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -27952,7 +28434,7 @@
     <row r="50">
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>Asymmetry Workbook  ·  Sheet 05 of 50</t>
+          <t>Asymmetry Workbook  ·  Sheet 06 of 50</t>
         </is>
       </c>
     </row>
@@ -27979,486 +28461,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00707070"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>#06    3798.HK    Homeland Interactive Technology Ltd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4" customHeight="1">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="inlineStr">
-        <is>
-          <t>Entry-today score</t>
-        </is>
-      </c>
-      <c r="E3" s="28" t="n">
-        <v>1.184048179572399</v>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>SNAPSHOT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>HK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>Interactive Media &amp; Services</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>Small Cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>Market cap (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="n">
-        <v>193180522.7553062</v>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>Revenue TTM (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="n">
-        <v>183954166.1063843</v>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
-        <is>
-          <t>As-of</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>INVESTMENT THESIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>SCORE DECOMPOSITION</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t>Asymmetry (raw)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>0.6573455939461111</v>
-      </c>
-      <c r="D21" s="33" t="inlineStr">
-        <is>
-          <t>Intrinsic discount</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>0.6355821053140513</v>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t>Upside leg</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="n">
-        <v>0.5617341988444753</v>
-      </c>
-      <c r="D22" s="33" t="inlineStr">
-        <is>
-          <t>Qual multiplier (x)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="33" t="inlineStr">
-        <is>
-          <t>Downside floor</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>0.7692307692307692</v>
-      </c>
-      <c r="D23" s="33" t="inlineStr">
-        <is>
-          <t>Post-rally factor (x)</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>Yartseva composite</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="n">
-        <v>0.8495485218474618</v>
-      </c>
-      <c r="D24" s="33" t="inlineStr">
-        <is>
-          <t>Confirmation (x)</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>Berezin growth</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="n">
-        <v>0.4128425191777984</v>
-      </c>
-      <c r="D25" s="33" t="inlineStr">
-        <is>
-          <t>Cluster signals (of 7)</t>
-        </is>
-      </c>
-      <c r="E25" s="34" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>VALUATION &amp; BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>P/B</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>0.822089473429743</v>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>NCAV / mcap (%)</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>-1.47356998523237</v>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>Net debt / EBITDA (x)</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="n">
-        <v>-7.225898256848096</v>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>EV / EBIT</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="n">
-        <v>0.9912811803599012</v>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>ROCE (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="23" t="n">
-        <v>33.75755216989689</v>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="n">
-        <v>21.73689776387475</v>
-      </c>
-      <c r="D31" s="33" t="inlineStr">
-        <is>
-          <t>EBITDA margin (%)</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="n">
-        <v>19.092307888602</v>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C32" s="22" t="n">
-        <v>1.06764828969794</v>
-      </c>
-      <c r="D32" s="33" t="inlineStr">
-        <is>
-          <t>Insider ownership (%)</t>
-        </is>
-      </c>
-      <c r="E32" s="23" t="n">
-        <v>74.694</v>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t>FCF yield (%)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="n">
-        <v>17.29941120876121</v>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
-        <is>
-          <t>Rev 3y CAGR (%)</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="B34" s="33" t="inlineStr">
-        <is>
-          <t>Net cash / mcap (%)</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="n">
-        <v>126.3512358188845</v>
-      </c>
-      <c r="D34" s="33" t="inlineStr">
-        <is>
-          <t>Rev YoY (TTM, %)</t>
-        </is>
-      </c>
-      <c r="E34" s="23" t="n">
-        <v>-2.6933510331294</v>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>Cash / EV (x)</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="n">
-        <v>3.142024571801568</v>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
-        <is>
-          <t>12m price momentum (%)</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="n">
-        <v>-18.09</v>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>SIGNALS FIRING</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>·  Cash &gt; EV  (downside floor in place)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>·  Sub-book  (P/B 0.82)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>·  Insider-aligned  (75% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (6 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="36" t="n"/>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
-      <c r="F43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="26" t="inlineStr">
-        <is>
-          <t>Asymmetry Workbook  ·  Sheet 06 of 50</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B15:E18"/>
-    <mergeCell ref="A27:E27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -55,9 +55,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="43_4625_T" sheetId="46" state="visible" r:id="rId46"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="44_1V5_F" sheetId="47" state="visible" r:id="rId47"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="45_CAAS" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46_0725_HK" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="46_1281_HK" sheetId="49" state="visible" r:id="rId49"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="47_131090_KQ" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48_1281_HK" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="48_0725_HK" sheetId="51" state="visible" r:id="rId51"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="49_052790_KQ" sheetId="52" state="visible" r:id="rId52"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50_3954_T" sheetId="53" state="visible" r:id="rId53"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="54" state="visible" r:id="rId54"/>
@@ -756,7 +756,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>26,385</t>
+          <t>26,389</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>25,984</t>
+          <t>25,988</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>This workbook documents the top 50 names from a global universe of 26,385 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
+          <t>This workbook documents the top 50 names from a global universe of 26,389 equities ranked by an entry-today asymmetry score. The upside leg weights factors Anna Yartseva (CAFE WP 33, 2025) finds predictive of 10-bagger outcomes — FCF yield, book-to-market, small size, profitability level, asset-growth gate, contra-momentum. The downside floor leg combines Graham net-net, cash &gt; EV, sub-book and negative-EV signals. Each candidate has been qualitatively reviewed and assigned a verdict of GREEN (high-conviction), YELLOW (risk-flagged), RED (avoid) or UNRESEARCHED. Sheets sequence as Cover, Methodology, Index, per-name pages, Coverage, References.</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.173223187173692</v>
+        <v>1.172504383176419</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>77653786.95794658</v>
+        <v>78237641.18890361</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.725824299626438</v>
+        <v>0.7249200996264381</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.601293</v>
+        <v>0.605814</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>10.23077</v>
+        <v>10.307693</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.5709076</v>
+        <v>0.5752</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.60)</t>
+          <t>·  Sub-book  (P/B 0.61)</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>97649721.25524984</v>
+        <v>97745653.94004904</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>1.225791</v>
+        <v>1.2269952</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>69110133.31576708</v>
+        <v>69063217.17478731</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>98540142.03049168</v>
+        <v>98798555.87781604</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.3509070426787583</v>
+        <v>0.3518272690665361</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>18429222.51684681</v>
+        <v>18347168.83320943</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.20313144</v>
+        <v>0.20222703</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.099278313855842</v>
+        <v>1.101049539651115</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>50773986.45186899</v>
+        <v>48701579.34159086</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6370614891453174</v>
+        <v>0.6392964091453174</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.2737778</v>
+        <v>0.2626032</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>-4.083374947411143</v>
+        <v>-4.345596984910629</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="C30" s="22" t="n">
-        <v>-2.817688644880061</v>
+        <v>-2.998632121052401</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>16.98113681911677</v>
+        <v>16.28802936107025</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>1.200266309500878</v>
+        <v>1.151275859708347</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.27)</t>
+          <t>·  Sub-book  (P/B 0.26)</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>72336165.70478408</v>
+        <v>71024071.39044254</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.762087879864858</v>
+        <v>0.764433611864858</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.6466033</v>
+        <v>0.63487464</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>8.007805236580204</v>
+        <v>7.862552918892367</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.3068591</v>
+        <v>0.30129302</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.65)</t>
+          <t>·  Sub-book  (P/B 0.63)</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>23924676.0523474</v>
+        <v>24329555.49054453</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>1.858148</v>
+        <v>1.8895935</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.095466595284029</v>
+        <v>1.094907872286137</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>184192477.3257772</v>
+        <v>185001225.2794639</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -9071,7 +9071,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.670534450302693</v>
+        <v>0.669809932302693</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.82505226</v>
+        <v>0.82867485</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>61.84160092575997</v>
+        <v>62.11313355796926</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.45700946</v>
+        <v>0.45901608</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.092825899825435</v>
+        <v>1.092706777931071</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>37283078.28963859</v>
+        <v>37332395.30343874</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6290377506939995</v>
+        <v>0.6288874306939994</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.5681878</v>
+        <v>0.5689394</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>260.1177048004683</v>
+        <v>260.4617812293953</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.9468284</v>
+        <v>0.9480809</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.084630529981028</v>
+        <v>1.082675977629569</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -9993,7 +9993,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>20660894.65984212</v>
+        <v>21714424.70673309</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6837826681597364</v>
+        <v>0.6811989281597365</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.9870813000000001</v>
+        <v>1.0374141</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>17.57093</v>
+        <v>18.476095</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>2.8326097</v>
+        <v>2.9770486</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -10304,72 +10304,64 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.99)</t>
+          <t>·  Insider-aligned  (67% insider)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (67% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
-        <is>
           <t>·  Cluster stack  (5 of 7 inflection signals)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="12" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>growth-flip; first-positive: FCF; accelerating sales; under-priced vs fundamentals; cheap+grow (EV/EBIT 1.0x); cash 93% of mcap; cash &gt; EV (9.08x, net cash 91% mcap)</t>
         </is>
       </c>
     </row>
+    <row r="44" ht="18" customHeight="1"/>
     <row r="45" ht="18" customHeight="1"/>
-    <row r="46" ht="18" customHeight="1"/>
+    <row r="48">
+      <c r="A48" s="36" t="n"/>
+      <c r="B48" s="36" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="36" t="n"/>
+    </row>
     <row r="49">
-      <c r="A49" s="36" t="n"/>
-      <c r="B49" s="36" t="n"/>
-      <c r="C49" s="36" t="n"/>
-      <c r="D49" s="36" t="n"/>
-      <c r="E49" s="36" t="n"/>
-      <c r="F49" s="36" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="26" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 25 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="17">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A43:E43"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B44:E46"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="B15:E18"/>
     <mergeCell ref="A27:E27"/>
@@ -11001,7 +10993,7 @@
         <v>2.42</v>
       </c>
       <c r="K4" s="22" t="n">
-        <v>0.19837561</v>
+        <v>0.19885361</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -11160,10 +11152,10 @@
         </is>
       </c>
       <c r="H8" s="22" t="n">
-        <v>1.214607294531874</v>
+        <v>1.213706119342358</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>0.64328694</v>
+        <v>0.64855975</v>
       </c>
       <c r="J8" s="25" t="inlineStr">
         <is>
@@ -11171,7 +11163,7 @@
         </is>
       </c>
       <c r="K8" s="22" t="n">
-        <v>1.06764828969794</v>
+        <v>1.076399494270387</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -11213,7 +11205,7 @@
         <v>2.77</v>
       </c>
       <c r="K9" s="22" t="n">
-        <v>0.47688493</v>
+        <v>0.47579452</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -11246,16 +11238,16 @@
         </is>
       </c>
       <c r="H10" s="22" t="n">
-        <v>1.173223187173692</v>
+        <v>1.172504383176419</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>0.601293</v>
+        <v>0.605814</v>
       </c>
       <c r="J10" s="23" t="n">
         <v>4.21</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>0.5709076</v>
+        <v>0.5752</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -11423,7 +11415,7 @@
         <v>4.9200002</v>
       </c>
       <c r="K14" s="22" t="n">
-        <v>1.225791</v>
+        <v>1.2269952</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -11509,7 +11501,7 @@
         <v>2.79</v>
       </c>
       <c r="K16" s="22" t="n">
-        <v>0.3509070426787583</v>
+        <v>0.3518272690665361</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -11637,7 +11629,7 @@
         <v>2.0299999</v>
       </c>
       <c r="K19" s="22" t="n">
-        <v>0.20313144</v>
+        <v>0.20222703</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -11756,10 +11748,10 @@
         </is>
       </c>
       <c r="H22" s="22" t="n">
-        <v>1.099278313855842</v>
+        <v>1.101049539651115</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>0.2737778</v>
+        <v>0.2626032</v>
       </c>
       <c r="J22" s="25" t="inlineStr">
         <is>
@@ -11767,7 +11759,7 @@
         </is>
       </c>
       <c r="K22" s="22" t="n">
-        <v>1.200266309500878</v>
+        <v>1.151275859708347</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -11845,13 +11837,13 @@
         <v>1.097238104899035</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>0.6466033</v>
+        <v>0.63487464</v>
       </c>
       <c r="J24" s="23" t="n">
         <v>2.4300002</v>
       </c>
       <c r="K24" s="22" t="n">
-        <v>0.3068591</v>
+        <v>0.30129302</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -11895,7 +11887,7 @@
         </is>
       </c>
       <c r="K25" s="22" t="n">
-        <v>1.858148</v>
+        <v>1.8895935</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -11928,16 +11920,16 @@
         </is>
       </c>
       <c r="H26" s="22" t="n">
-        <v>1.095466595284029</v>
+        <v>1.094907872286137</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>0.82505226</v>
+        <v>0.82867485</v>
       </c>
       <c r="J26" s="23" t="n">
         <v>3.55</v>
       </c>
       <c r="K26" s="22" t="n">
-        <v>0.45700946</v>
+        <v>0.45901608</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -11970,10 +11962,10 @@
         </is>
       </c>
       <c r="H27" s="22" t="n">
-        <v>1.092825899825435</v>
+        <v>1.092706777931071</v>
       </c>
       <c r="I27" s="22" t="n">
-        <v>0.5681878</v>
+        <v>0.5689394</v>
       </c>
       <c r="J27" s="25" t="inlineStr">
         <is>
@@ -11981,7 +11973,7 @@
         </is>
       </c>
       <c r="K27" s="22" t="n">
-        <v>0.9468284</v>
+        <v>0.9480809</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -12014,16 +12006,16 @@
         </is>
       </c>
       <c r="H28" s="22" t="n">
-        <v>1.084630529981028</v>
+        <v>1.082675977629569</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>0.9870813000000001</v>
+        <v>1.0374141</v>
       </c>
       <c r="J28" s="23" t="n">
         <v>0.5599999999999999</v>
       </c>
       <c r="K28" s="22" t="n">
-        <v>2.8326097</v>
+        <v>2.9770486</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -12151,7 +12143,7 @@
         <v>5.71</v>
       </c>
       <c r="K31" s="22" t="n">
-        <v>0.5645629</v>
+        <v>0.5612516400000001</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -12182,16 +12174,16 @@
         </is>
       </c>
       <c r="H32" s="22" t="n">
-        <v>1.073817836048235</v>
+        <v>1.072794052555671</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>0.5712140999999999</v>
+        <v>0.57788193</v>
       </c>
       <c r="J32" s="23" t="n">
         <v>1.39</v>
       </c>
       <c r="K32" s="22" t="n">
-        <v>0.5015371</v>
+        <v>0.50739163</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -12233,7 +12225,7 @@
         <v>2.8800001</v>
       </c>
       <c r="K33" s="22" t="n">
-        <v>1.4025122</v>
+        <v>1.4009893</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -12264,16 +12256,16 @@
         </is>
       </c>
       <c r="H34" s="22" t="n">
-        <v>1.069061043495279</v>
+        <v>1.068682304326143</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>0.60156065</v>
+        <v>0.6041536</v>
       </c>
       <c r="J34" s="23" t="n">
         <v>1.23000005</v>
       </c>
       <c r="K34" s="22" t="n">
-        <v>0.44866917</v>
+        <v>0.45060313</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -12309,13 +12301,13 @@
         <v>1.066842547335759</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>0.6536218499999999</v>
+        <v>0.6513203400000001</v>
       </c>
       <c r="J35" s="23" t="n">
         <v>1.07</v>
       </c>
       <c r="K35" s="22" t="n">
-        <v>2.4318655</v>
+        <v>2.4233024</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -12401,7 +12393,7 @@
         </is>
       </c>
       <c r="K37" s="22" t="n">
-        <v>0.23204216</v>
+        <v>0.23250532</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -12432,16 +12424,16 @@
         </is>
       </c>
       <c r="H38" s="22" t="n">
-        <v>1.058431562072892</v>
+        <v>1.060366004632101</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>0.8213800999999999</v>
+        <v>0.809476</v>
       </c>
       <c r="J38" s="23" t="n">
         <v>4.9200002</v>
       </c>
       <c r="K38" s="22" t="n">
-        <v>2.000695</v>
+        <v>1.9716996</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -12474,16 +12466,16 @@
         </is>
       </c>
       <c r="H39" s="22" t="n">
-        <v>1.052608565093393</v>
+        <v>1.052813435988574</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>0.830867</v>
+        <v>0.8297809</v>
       </c>
       <c r="J39" s="23" t="n">
         <v>5.35</v>
       </c>
       <c r="K39" s="22" t="n">
-        <v>0.7343785</v>
+        <v>0.7334186</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -12770,16 +12762,16 @@
         </is>
       </c>
       <c r="H46" s="22" t="n">
-        <v>1.027618535300892</v>
+        <v>1.027683931197308</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>0.40647167</v>
+        <v>0.40600014</v>
       </c>
       <c r="J46" s="23" t="n">
         <v>2.77</v>
       </c>
       <c r="K46" s="22" t="n">
-        <v>0.34490073</v>
+        <v>0.3445006</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -12856,10 +12848,10 @@
         </is>
       </c>
       <c r="H48" s="22" t="n">
-        <v>1.026328294118021</v>
+        <v>1.026123465125633</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>0.3576042</v>
+        <v>0.35896394</v>
       </c>
       <c r="J48" s="25" t="inlineStr">
         <is>
@@ -12867,7 +12859,7 @@
         </is>
       </c>
       <c r="K48" s="22" t="n">
-        <v>0.19008878</v>
+        <v>0.19081154</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -12876,12 +12868,12 @@
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>0725.HK</t>
+          <t>1281.HK</t>
         </is>
       </c>
       <c r="D49" s="18" t="inlineStr">
         <is>
-          <t>Perennial International Limited</t>
+          <t>LongiTech Smart Energy Holding Limited</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
@@ -12891,25 +12883,27 @@
       </c>
       <c r="F49" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="G49" s="21" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="H49" s="22" t="n">
-        <v>1.019908786675609</v>
+        <v>1.024547950517395</v>
       </c>
       <c r="I49" s="22" t="n">
-        <v>0.40812057</v>
-      </c>
-      <c r="J49" s="23" t="n">
-        <v>9</v>
+        <v>0.14083</v>
+      </c>
+      <c r="J49" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
       <c r="K49" s="22" t="n">
-        <v>0.47891504</v>
+        <v>0.9045904154520544</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -12951,7 +12945,7 @@
         <v>4.3</v>
       </c>
       <c r="K50" s="22" t="n">
-        <v>2.2538886</v>
+        <v>2.2647114</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -12960,12 +12954,12 @@
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>1281.HK</t>
+          <t>0725.HK</t>
         </is>
       </c>
       <c r="D51" s="18" t="inlineStr">
         <is>
-          <t>LongiTech Smart Energy Holding Limited</t>
+          <t>Perennial International Limited</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
@@ -12975,27 +12969,25 @@
       </c>
       <c r="F51" s="20" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="G51" s="21" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="H51" s="22" t="n">
-        <v>1.016413963344826</v>
+        <v>1.019209861728622</v>
       </c>
       <c r="I51" s="22" t="n">
-        <v>0.13929923</v>
-      </c>
-      <c r="J51" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+        <v>0.41230643</v>
+      </c>
+      <c r="J51" s="23" t="n">
+        <v>9</v>
       </c>
       <c r="K51" s="22" t="n">
-        <v>0.8947578844443459</v>
+        <v>0.483827</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -13039,7 +13031,7 @@
         </is>
       </c>
       <c r="K52" s="22" t="n">
-        <v>0.6022702</v>
+        <v>0.6088967</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -13257,7 +13249,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>227119088.1089789</v>
+        <v>229039477.8522077</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -13735,7 +13727,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>24146193.53754446</v>
+        <v>24004571.73281214</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -13960,7 +13952,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.5645629</v>
+        <v>0.5612516400000001</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -14168,7 +14160,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.073817836048235</v>
+        <v>1.072794052555671</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -14229,7 +14221,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>56815040.56741953</v>
+        <v>57478251.0455513</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -14293,7 +14285,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6487400331688689</v>
+        <v>0.6474064671688688</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -14382,7 +14374,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.5712140999999999</v>
+        <v>0.57788193</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -14456,7 +14448,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.5015371</v>
+        <v>0.50739163</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -14540,7 +14532,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.57)</t>
+          <t>·  Sub-book  (P/B 0.58)</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14719,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>58876338.41682063</v>
+        <v>58812410.08447371</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -14954,7 +14946,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>1.4025122</v>
+        <v>1.4009893</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -15154,7 +15146,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.069061043495279</v>
+        <v>1.068682304326143</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -15215,7 +15207,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>23665919.52022672</v>
+        <v>23767929.1761291</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -15279,7 +15271,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.7138157648456206</v>
+        <v>0.7132971748456206</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -15368,7 +15360,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.60156065</v>
+        <v>0.6041536</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -15424,7 +15416,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>6.309491</v>
+        <v>6.3366876</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -15442,7 +15434,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.44866917</v>
+        <v>0.45060313</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -15713,7 +15705,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>13364747.41860322</v>
+        <v>13317687.95425586</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -15777,7 +15769,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.7989604609929413</v>
+        <v>0.7994207629929412</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -15866,7 +15858,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.6536218499999999</v>
+        <v>0.6513203400000001</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -15922,7 +15914,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>19.346048</v>
+        <v>19.27793</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -15940,7 +15932,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>2.4318655</v>
+        <v>2.4233024</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -16695,7 +16687,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>88338287.18595138</v>
+        <v>88514613.86107269</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -16922,7 +16914,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.23204216</v>
+        <v>0.23250532</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -17114,7 +17106,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.058431562072892</v>
+        <v>1.060366004632101</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -17175,7 +17167,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>646742342.4944687</v>
+        <v>637369300.1551437</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -17239,7 +17231,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.5526672824261241</v>
+        <v>0.555048102426124</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -17328,7 +17320,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.8213800999999999</v>
+        <v>0.809476</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -17382,7 +17374,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>5.693821</v>
+        <v>5.611302</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -17400,7 +17392,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>2.000695</v>
+        <v>1.9716996</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -17484,7 +17476,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.82)</t>
+          <t>·  Sub-book  (P/B 0.81)</t>
         </is>
       </c>
     </row>
@@ -17600,7 +17592,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.052608565093393</v>
+        <v>1.052813435988574</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -17665,7 +17657,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>64263095.03524991</v>
+        <v>64179093.31776353</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -17729,7 +17721,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.3660571749715599</v>
+        <v>0.3662743949715599</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -17818,7 +17810,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.830867</v>
+        <v>0.8297809</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -17872,7 +17864,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>6.8931336</v>
+        <v>6.884123</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -17890,7 +17882,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.7343785</v>
+        <v>0.7334186</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -18161,7 +18153,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>34909646.27042425</v>
+        <v>34993764.18925035</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -18386,7 +18378,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.19837561</v>
+        <v>0.19885361</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -21111,7 +21103,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>64731618.55333321</v>
+        <v>64845983.34468452</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -21536,7 +21528,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.027618535300892</v>
+        <v>1.027683931197308</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -21601,7 +21593,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>28617906.59480798</v>
+        <v>28584706.18959533</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -21665,7 +21657,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.7319063412389546</v>
+        <v>0.7320006472389546</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -21754,7 +21746,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.40647167</v>
+        <v>0.40600014</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -21808,7 +21800,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>4.8549705</v>
+        <v>4.849338</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -21826,7 +21818,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.34490073</v>
+        <v>0.3445006</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -22522,7 +22514,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.026328294118021</v>
+        <v>1.026123465125633</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -22587,7 +22579,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>158697904</v>
+        <v>159301312</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -22651,7 +22643,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6126387733251275</v>
+        <v>0.6123668253251274</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -22740,7 +22732,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.3576042</v>
+        <v>0.35896394</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -22794,7 +22786,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>2.7684212</v>
+        <v>2.7789476</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -22812,7 +22804,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.19008878</v>
+        <v>0.19081154</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -22951,7 +22943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -22965,7 +22957,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#46    0725.HK    Perennial International Limited</t>
+          <t>#46    1281.HK    LongiTech Smart Energy Holding Limited</t>
         </is>
       </c>
     </row>
@@ -22983,9 +22975,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -22994,7 +22986,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.019908786675609</v>
+        <v>1.024547950517395</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -23024,7 +23016,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
     </row>
@@ -23036,7 +23028,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Independent Power and Renewable Electricity Producers</t>
         </is>
       </c>
     </row>
@@ -23059,7 +23051,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>24753283.59752344</v>
+        <v>17428710.39306092</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -23069,7 +23061,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>50498298.96777866</v>
+        <v>19266963.3630279</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -23080,7 +23072,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>–</t>
         </is>
       </c>
     </row>
@@ -23094,7 +23086,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Perennial International - electric cable family business; ~6% TTM dividend yield with intact payouts; P/B 0.46</t>
+          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
         </is>
       </c>
     </row>
@@ -23115,7 +23107,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6381708462961632</v>
+        <v>0.6291497860677019</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -23123,7 +23115,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.4716463047139654</v>
+        <v>0.6626164776618847</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -23133,7 +23125,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5294406377810695</v>
+        <v>0.5145782893017455</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -23141,7 +23133,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -23159,7 +23151,7 @@
         </is>
       </c>
       <c r="E23" s="22" t="n">
-        <v>0.991</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -23169,7 +23161,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.820348</v>
+        <v>0.8794749681014746</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -23177,7 +23169,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.2</v>
+        <v>1.1528</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -23187,7 +23179,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.5524636352202518</v>
+        <v>0.4655292998699878</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -23195,7 +23187,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -23212,15 +23204,17 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.40812057</v>
+        <v>0.14083</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
           <t>NCAV / mcap (%)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="n">
-        <v>119.585308118896</v>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -23230,7 +23224,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>1.985515932474278</v>
+        <v>-3.322634386904862</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -23238,7 +23232,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-2.129477574667865</v>
+        <v>-7.396120066301267</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -23258,7 +23252,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>11.90882409257052</v>
+        <v>2.15667527759927</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -23268,7 +23262,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>6.5</v>
+        <v>7.585980566515093</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -23276,7 +23270,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>12.64845605700712</v>
+        <v>31.31714285714285</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -23286,7 +23280,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.47891504</v>
+        <v>0.9045904154520544</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -23294,7 +23288,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>74.361</v>
+        <v>65.373003</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -23304,7 +23298,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>24.22527118078666</v>
+        <v>99.15826792971392</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -23324,7 +23318,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>50.5420998322809</v>
+        <v>181.9727797636792</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -23332,7 +23326,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>20.44019989165434</v>
+        <v>22.5586749656398</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -23342,7 +23336,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>1.021921589561637</v>
+        <v>1.54376636882513</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -23350,7 +23344,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>32.5</v>
+        <v>-24.14</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -23370,60 +23364,50 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.41)</t>
+          <t>·  Sub-book  (P/B 0.14)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (74% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>growth-flip; accelerating sales; cheap+grow (EV/EBIT 2.5x); cash 51% of mcap; cash &gt; EV (1.02x, net cash 51% mcap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1"/>
-    <row r="45" ht="18" customHeight="1"/>
-    <row r="48">
-      <c r="A48" s="36" t="n"/>
-      <c r="B48" s="36" t="n"/>
-      <c r="C48" s="36" t="n"/>
-      <c r="D48" s="36" t="n"/>
-      <c r="E48" s="36" t="n"/>
-      <c r="F48" s="36" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="26" t="inlineStr">
+          <t>·  Insider-aligned  (65% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="B41" s="35" t="inlineStr">
+        <is>
+          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="n"/>
+      <c r="B43" s="36" t="n"/>
+      <c r="C43" s="36" t="n"/>
+      <c r="D43" s="36" t="n"/>
+      <c r="E43" s="36" t="n"/>
+      <c r="F43" s="36" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 46 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
@@ -24049,7 +24033,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>20459466.81140074</v>
+        <v>20557711.54677471</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -24276,7 +24260,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>2.2538886</v>
+        <v>2.2647114</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -24435,7 +24419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -24449,7 +24433,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#48    1281.HK    LongiTech Smart Energy Holding Limited</t>
+          <t>#48    0725.HK    Perennial International Limited</t>
         </is>
       </c>
     </row>
@@ -24467,9 +24451,9 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="D3" s="26" t="inlineStr">
@@ -24478,7 +24462,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.016413963344826</v>
+        <v>1.019209861728622</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -24508,7 +24492,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -24520,7 +24504,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Independent Power and Renewable Electricity Producers</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
     </row>
@@ -24543,7 +24527,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>17239267.37836956</v>
+        <v>25007163.9423294</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -24553,7 +24537,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>19266963.3630279</v>
+        <v>50498298.96777866</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -24564,7 +24548,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>2025-12-31</t>
         </is>
       </c>
     </row>
@@ -24578,7 +24562,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Unresearched. No qualitative thesis on file; ranking driven entirely by quantitative signals (see Score decomposition below).</t>
+          <t>Perennial International - electric cable family business; ~6% TTM dividend yield with intact payouts; P/B 0.46</t>
         </is>
       </c>
     </row>
@@ -24599,7 +24583,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6291497860677019</v>
+        <v>0.6381708462961632</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -24607,7 +24591,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.6629226316618847</v>
+        <v>0.4708091327139654</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -24617,7 +24601,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5145782893017455</v>
+        <v>0.5294406377810695</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -24625,7 +24609,7 @@
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -24643,7 +24627,7 @@
         </is>
       </c>
       <c r="E23" s="22" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
@@ -24653,7 +24637,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.8794749681014746</v>
+        <v>0.820348</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -24661,7 +24645,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.1434</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -24671,7 +24655,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.4655292998699878</v>
+        <v>0.5524636352202518</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -24679,7 +24663,7 @@
         </is>
       </c>
       <c r="E25" s="34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
@@ -24696,17 +24680,15 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.13929923</v>
+        <v>0.41230643</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
           <t>NCAV / mcap (%)</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="E28" s="23" t="n">
+        <v>119.585308118896</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -24716,7 +24698,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>-3.355922619636716</v>
+        <v>1.985515932474278</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -24724,7 +24706,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-7.396120066301267</v>
+        <v>-2.129477574667865</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -24744,7 +24726,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>2.15667527759927</v>
+        <v>11.90882409257052</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -24754,7 +24736,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>7.50352403384571</v>
+        <v>6.5666666</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -24762,7 +24744,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>31.31714285714285</v>
+        <v>12.64845605700712</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -24772,7 +24754,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.8947578844443459</v>
+        <v>0.483827</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -24780,7 +24762,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>65.373003</v>
+        <v>74.361</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -24789,10 +24771,8 @@
           <t>FCF yield (%)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C33" s="23" t="n">
+        <v>24.22527118078666</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -24812,7 +24792,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>181.9727797636792</v>
+        <v>50.5420998322809</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -24820,7 +24800,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>22.5586749656398</v>
+        <v>20.44019989165434</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -24830,7 +24810,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>1.54376636882513</v>
+        <v>1.021921589561637</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -24838,7 +24818,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>-24.14</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -24858,50 +24838,60 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.14)</t>
+          <t>·  Sub-book  (P/B 0.41)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (65% insider)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>·  Cluster stack  (4 of 7 inflection signals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="36" t="n"/>
-      <c r="B43" s="36" t="n"/>
-      <c r="C43" s="36" t="n"/>
-      <c r="D43" s="36" t="n"/>
-      <c r="E43" s="36" t="n"/>
-      <c r="F43" s="36" t="n"/>
-    </row>
-    <row r="44">
-      <c r="B44" s="26" t="inlineStr">
+          <t>·  Insider-aligned  (74% insider)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>growth-flip; accelerating sales; cheap+grow (EV/EBIT 2.5x); cash 51% of mcap; cash &gt; EV (1.02x, net cash 51% mcap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1"/>
+    <row r="45" ht="18" customHeight="1"/>
+    <row r="48">
+      <c r="A48" s="36" t="n"/>
+      <c r="B48" s="36" t="n"/>
+      <c r="C48" s="36" t="n"/>
+      <c r="D48" s="36" t="n"/>
+      <c r="E48" s="36" t="n"/>
+      <c r="F48" s="36" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>Asymmetry Workbook  ·  Sheet 48 of 50</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B43:E45"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A37:E37"/>
@@ -25027,7 +25017,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>29224919.38030916</v>
+        <v>29546465.8716598</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -25254,7 +25244,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.6022702</v>
+        <v>0.6088967</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -25987,7 +25977,7 @@
         </is>
       </c>
       <c r="C5" s="41" t="n">
-        <v>26385</v>
+        <v>26389</v>
       </c>
       <c r="D5" s="31" t="n">
         <v>122</v>
@@ -25999,10 +25989,10 @@
         <v>99</v>
       </c>
       <c r="G5" s="31" t="n">
-        <v>25984</v>
+        <v>25988</v>
       </c>
       <c r="H5" s="42" t="n">
-        <v>1.519802918324806</v>
+        <v>1.519572549168214</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
@@ -26202,16 +26192,16 @@
         <v>2</v>
       </c>
       <c r="E16" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="34" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
@@ -27533,7 +27523,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.214607294531874</v>
+        <v>1.213706119342358</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -27598,7 +27588,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>196398350.8262919</v>
+        <v>198008171.3658428</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -27662,7 +27652,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.671342612</v>
+        <v>0.67028805</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -27751,7 +27741,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.64328694</v>
+        <v>0.64855975</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -27771,7 +27761,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>-1.47356998523237</v>
+        <v>-1.427733700674697</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -27807,7 +27797,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>21.73689776387475</v>
+        <v>21.91506883475788</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -27825,7 +27815,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>1.06764828969794</v>
+        <v>1.076399494270387</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -27909,7 +27899,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="B39" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.64)</t>
+          <t>·  Sub-book  (P/B 0.65)</t>
         </is>
       </c>
     </row>
@@ -28080,7 +28070,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>129835458.4956091</v>
+        <v>129538583.7003687</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -28305,7 +28295,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.47688493</v>
+        <v>0.47579452</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>

--- a/asymmetry_harvard_workbook.xlsx
+++ b/asymmetry_harvard_workbook.xlsx
@@ -15,8 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_2230_HK" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_3798_HK" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_4629_T" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_AWC_SI" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_003650_KS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_003650_KS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_AWC_SI" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_4301_T" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_IRC_BK" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_054800_KQ" sheetId="13" state="visible" r:id="rId13"/>
@@ -893,7 +893,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#07    003650.KS    Michang Oil Ind .Co.,Ltd.</t>
+          <t>#07    AWC.SI    Brook Crompton Holdings Ltd.</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.190631767830064</v>
+        <v>1.19387677304337</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Oil, Gas &amp; Consumable Fuels</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Micro Cap</t>
+          <t>Nano Cap</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>129538583.7003727</v>
+        <v>15698515.16605616</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>265260383.0321121</v>
+        <v>47767733.03747177</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Profitable Busan lubricants/white-oils maker (FY23 net income 47.6B KRW +104% YoY); 2.5% yield with only 6.6% payout signals net-cash hoard, classic Korean sub-book niche-leader setup</t>
+          <t>Brook Crompton - net-net + cash&gt;EV; Wolong as parent could squeeze out at low multiple = double-edged catalyst</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6220646644880169</v>
+        <v>0.6161324761871702</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.7813682137134539</v>
+        <v>0.7365323562033702</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.4374380703008398</v>
+        <v>0.5018694881453837</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.8846153846153845</v>
+        <v>0.7564102564102564</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.763853</v>
+        <v>0.81277</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.16</v>
+        <v>1.185</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.4460390065168427</v>
+        <v>0.578894638589458</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.3814184820374598</v>
+        <v>0.4305136</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>195.4228046268257</v>
+        <v>186.2185523184757</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>0.502</v>
+        <v>1.614</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-3.532483495983913</v>
+        <v>-13.95633802816901</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>48.19489607961939</v>
+        <v>13.92004707439961</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>3.257832481702135</v>
+        <v>8.142856999999999</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>12.06697403251717</v>
+        <v>2.30894308943089</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.47579452</v>
+        <v>0.3348663</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>50.244</v>
+        <v>66.086</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>3.22106752958146</v>
+        <v>4.09667276945568</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>86.88917215306873</v>
+        <v>90.87835873445673</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>-6.109694716853889</v>
+        <v>-0.22712524334847</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>17.52230716826635</v>
+        <v>6.08519742575637</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>26.1</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -1305,14 +1305,14 @@
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.38)</t>
+          <t>·  Sub-book  (P/B 0.43)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (50% insider)</t>
+          <t>·  Insider-aligned  (66% insider)</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.1x); Graham net-net (mcap 0.51x NCAV); cash 150% of mcap; cash &gt; EV (17.52x, net cash 143% mcap)</t>
+          <t>growth-flip; accelerating sales; cheap+grow (EV/EBIT 1.0x); Graham net-net (mcap 0.54x NCAV); cash 108% of mcap; cash &gt; EV (6.09x, net cash 91% mcap)</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>185001225.2794647</v>
+        <v>185001225.2794639</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>425102384.579368</v>
+        <v>425102384.5793661</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>78237641.18890381</v>
+        <v>78237641.18890361</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>136153379.1378207</v>
+        <v>136153379.1378204</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -2173,10 +2173,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>0.4595209433628192</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -2475,7 +2473,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>86400269.06174946</v>
+        <v>86400269.06174681</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -2485,7 +2483,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>621263383.7902402</v>
+        <v>621263383.7902211</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -3463,7 +3461,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>14694714.95424652</v>
+        <v>14694714.95424648</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -3473,7 +3471,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>8311024.856157303</v>
+        <v>8311024.856157282</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -3888,7 +3886,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.161336639699278</v>
+        <v>1.163897066936411</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -3951,7 +3949,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>97745653.94005205</v>
+        <v>97745653.94004904</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -3961,7 +3959,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>77102450.02260983</v>
+        <v>77102450.02260746</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -4069,7 +4067,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.27</v>
+        <v>1.2728</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -4139,10 +4137,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>0.7374453048913777</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -4441,7 +4437,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>69063217.17478943</v>
+        <v>69063217.17478731</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -4451,7 +4447,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>74515427.36626884</v>
+        <v>74515427.36626655</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -4935,7 +4931,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>98798555.87781906</v>
+        <v>98798555.87781604</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -4945,7 +4941,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>280815515.3520368</v>
+        <v>280815515.3520282</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -5123,10 +5119,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>1.926120339523525</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -6059,7 +6053,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>36263429.07907248</v>
+        <v>36263429.07907232</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -6069,7 +6063,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>86615249.88943711</v>
+        <v>86615249.88943674</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -6555,7 +6549,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>18347168.83320999</v>
+        <v>18347168.83320943</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -6565,7 +6559,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>90551985.4721216</v>
+        <v>90551985.47211882</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -6743,10 +6737,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>0.9806606675872322</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -7053,7 +7045,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>90146910.85052872</v>
+        <v>90146910.85052596</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -7063,7 +7055,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>85769277.6876678</v>
+        <v>85769277.68766516</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -7555,7 +7547,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>38413174.78646946</v>
+        <v>38413174.78646944</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -7565,7 +7557,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>184011076.5883501</v>
+        <v>184011076.58835</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -8041,7 +8033,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>48701579.34159088</v>
+        <v>48701579.34159086</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -8051,7 +8043,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>42302267.46344568</v>
+        <v>42302267.46344566</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -8231,10 +8223,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>-2.998632121052401</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -8525,7 +8515,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>190876303.7740097</v>
+        <v>190876303.7740096</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -8535,7 +8525,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>169430939.0357057</v>
+        <v>169430939.0357056</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -8713,10 +8703,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>-4.937585342446557</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -9023,7 +9011,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>24329555.49054528</v>
+        <v>24329555.49054453</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -9033,7 +9021,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>11671505.63693912</v>
+        <v>11671505.63693877</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -9211,10 +9199,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>1.742800322776044</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -9517,7 +9503,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>331100479.5374721</v>
+        <v>331100479.537472</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -10005,7 +9991,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>21714424.70673323</v>
+        <v>21714424.70673309</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -10015,7 +10001,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>7273825.765494257</v>
+        <v>7273825.765494212</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -10497,7 +10483,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>37332395.3034389</v>
+        <v>37332395.30343874</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -10507,7 +10493,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>32923308.73264465</v>
+        <v>32923308.73264452</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -11080,7 +11066,7 @@
         </is>
       </c>
       <c r="H6" s="22" t="n">
-        <v>1.218387032001579</v>
+        <v>1.224320047113935</v>
       </c>
       <c r="I6" s="22" t="n">
         <v>0.5975976</v>
@@ -11184,22 +11170,22 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>AWC.SI</t>
+          <t>003650.KS</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Brook Crompton Holdings Ltd.</t>
+          <t>Michang Oil Ind .Co.,Ltd.</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -11208,16 +11194,16 @@
         </is>
       </c>
       <c r="H9" s="22" t="n">
-        <v>1.19387677304337</v>
+        <v>1.196379645329934</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>0.4305136</v>
+        <v>0.3814184820374598</v>
       </c>
       <c r="J9" s="23" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="K9" s="22" t="n">
-        <v>0.3348663</v>
+        <v>0.47579452</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -11226,22 +11212,22 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>003650.KS</t>
+          <t>AWC.SI</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>Michang Oil Ind .Co.,Ltd.</t>
+          <t>Brook Crompton Holdings Ltd.</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -11250,16 +11236,16 @@
         </is>
       </c>
       <c r="H10" s="22" t="n">
-        <v>1.190631767830064</v>
+        <v>1.19387677304337</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>0.3814184820374598</v>
+        <v>0.4305136</v>
       </c>
       <c r="J10" s="23" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>0.47579452</v>
+        <v>0.3348663</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -11502,7 +11488,7 @@
         </is>
       </c>
       <c r="H16" s="22" t="n">
-        <v>1.161336639699278</v>
+        <v>1.163897066936411</v>
       </c>
       <c r="I16" s="22" t="n">
         <v>0.9925171574056828</v>
@@ -13263,7 +13249,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>16725600.29102147</v>
+        <v>16725600.29102139</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -13273,7 +13259,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>55222673.83330967</v>
+        <v>55222673.83330944</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -13451,10 +13437,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>1.98262538471883</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -13753,7 +13737,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>229039477.8522148</v>
+        <v>229039477.8522077</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -13763,7 +13747,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>291135327.5719234</v>
+        <v>291135327.5719145</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -14231,7 +14215,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>24004571.73281288</v>
+        <v>24004571.73281214</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -14241,7 +14225,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>41049810.50742675</v>
+        <v>41049810.50742549</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -14419,10 +14403,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>0.0915064559526798</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -15225,7 +15207,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>58812410.08447552</v>
+        <v>58812410.08447371</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -15235,7 +15217,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>37014740.95624924</v>
+        <v>37014740.9562481</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -16211,7 +16193,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>88514613.8610754</v>
+        <v>88514613.86107269</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -16221,7 +16203,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>387812025.290559</v>
+        <v>387812025.2905471</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -16399,10 +16381,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>1.753430692904798</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -16881,10 +16861,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>1.614595351131961</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -17185,7 +17163,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>125759425.163269</v>
+        <v>125759425.1632687</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -17195,7 +17173,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>71113427.56021285</v>
+        <v>71113427.56021267</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -17669,7 +17647,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>50524003.6661768</v>
+        <v>50524003.66617677</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -17679,7 +17657,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>89795964.46359158</v>
+        <v>89795964.46359153</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -18167,7 +18145,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>34993764.18925142</v>
+        <v>34993764.18925035</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -18177,7 +18155,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>216015408.892177</v>
+        <v>216015408.8921704</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -18673,7 +18651,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>87952045.37611961</v>
+        <v>87952045.37611957</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -18683,7 +18661,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>461430088.9879614</v>
+        <v>461430088.9879612</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -19163,7 +19141,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>29658799.91638899</v>
+        <v>29658799.91638808</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -19173,7 +19151,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>89068535.34864391</v>
+        <v>89068535.34864119</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -19653,7 +19631,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>64845983.34468651</v>
+        <v>64845983.34468452</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -19663,7 +19641,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>390351789.1708</v>
+        <v>390351789.170788</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -20627,7 +20605,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>64179093.31776381</v>
+        <v>64179093.31776353</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -20637,7 +20615,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>82321438.99549031</v>
+        <v>82321438.99548995</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -21123,7 +21101,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>20557711.54677534</v>
+        <v>20557711.54677471</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -21133,7 +21111,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>8563148.622397322</v>
+        <v>8563148.62239706</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -21617,7 +21595,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>25007163.94232941</v>
+        <v>25007163.9423294</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -21627,7 +21605,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>50498298.96777868</v>
+        <v>50498298.96777866</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -22107,7 +22085,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>29546465.87166071</v>
+        <v>29546465.8716598</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -22117,7 +22095,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>43532230.22913835</v>
+        <v>43532230.22913702</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -22601,7 +22579,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>80246742.39991665</v>
+        <v>80246742.39991631</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -22611,7 +22589,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>145366592.7187284</v>
+        <v>145366592.7187277</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -23097,7 +23075,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>134233026.9123783</v>
+        <v>134233026.9123742</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -23107,7 +23085,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>275616874.9640363</v>
+        <v>275616874.9640279</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -23589,7 +23567,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>96779704.39331056</v>
+        <v>96779704.39330758</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -23599,7 +23577,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>293732750.4359149</v>
+        <v>293732750.4359059</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -24073,7 +24051,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>60319815.14114141</v>
+        <v>60319815.14114115</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -24083,7 +24061,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>147863210.4322873</v>
+        <v>147863210.4322867</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -24563,7 +24541,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>45157985.92321968</v>
+        <v>45157985.92321829</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -24573,7 +24551,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>201923506.9211402</v>
+        <v>201923506.921134</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -25057,7 +25035,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>268537192.4160213</v>
+        <v>268537192.4160212</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -25067,7 +25045,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>735679467.6824063</v>
+        <v>735679467.6824059</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -26559,7 +26537,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.218387032001579</v>
+        <v>1.224320047113935</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -26624,7 +26602,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>50583538.93268108</v>
+        <v>50583538.93268106</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -26634,7 +26612,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>82663114.82569575</v>
+        <v>82663114.82569572</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -26742,7 +26720,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.15</v>
+        <v>1.1556</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -26812,10 +26790,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>1.244281797914842</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -27134,7 +27110,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>183954166.1063844</v>
+        <v>183954166.1063843</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -27314,10 +27290,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>0.9912811803599012</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -27608,7 +27582,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>71024071.39044285</v>
+        <v>71024071.39044254</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -27618,7 +27592,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>216405193.725382</v>
+        <v>216405193.725381</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -28014,7 +27988,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>#06    AWC.SI    Brook Crompton Holdings Ltd.</t>
+          <t>#06    003650.KS    Michang Oil Ind .Co.,Ltd.</t>
         </is>
       </c>
     </row>
@@ -28043,7 +28017,7 @@
         </is>
       </c>
       <c r="E3" s="28" t="n">
-        <v>1.19387677304337</v>
+        <v>1.196379645329934</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
@@ -28061,7 +28035,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
     </row>
@@ -28073,7 +28047,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
     </row>
@@ -28085,7 +28059,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Oil, Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -28097,7 +28071,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>Nano Cap</t>
+          <t>Micro Cap</t>
         </is>
       </c>
     </row>
@@ -28108,7 +28082,7 @@
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>15698515.16605616</v>
+        <v>129538583.7003687</v>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
@@ -28118,7 +28092,7 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>47767733.03747177</v>
+        <v>265260383.032104</v>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
@@ -28129,7 +28103,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
@@ -28143,7 +28117,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Brook Crompton - net-net + cash&gt;EV; Wolong as parent could squeeze out at low multiple = double-edged catalyst</t>
+          <t>Profitable Busan lubricants/white-oils maker (FY23 net income 47.6B KRW +104% YoY); 2.5% yield with only 6.6% payout signals net-cash hoard, classic Korean sub-book niche-leader setup</t>
         </is>
       </c>
     </row>
@@ -28164,7 +28138,7 @@
         </is>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0.6161324761871702</v>
+        <v>0.6220646644880169</v>
       </c>
       <c r="D21" s="33" t="inlineStr">
         <is>
@@ -28172,7 +28146,7 @@
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0.7365323562033702</v>
+        <v>0.7813682137134539</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
@@ -28182,7 +28156,7 @@
         </is>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0.5018694881453837</v>
+        <v>0.4374380703008398</v>
       </c>
       <c r="D22" s="33" t="inlineStr">
         <is>
@@ -28200,7 +28174,7 @@
         </is>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0.7564102564102564</v>
+        <v>0.8846153846153845</v>
       </c>
       <c r="D23" s="33" t="inlineStr">
         <is>
@@ -28218,7 +28192,7 @@
         </is>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0.81277</v>
+        <v>0.763853</v>
       </c>
       <c r="D24" s="33" t="inlineStr">
         <is>
@@ -28226,7 +28200,7 @@
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>1.185</v>
+        <v>1.1656</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
@@ -28236,7 +28210,7 @@
         </is>
       </c>
       <c r="C25" s="22" t="n">
-        <v>0.578894638589458</v>
+        <v>0.4460390065168427</v>
       </c>
       <c r="D25" s="33" t="inlineStr">
         <is>
@@ -28261,7 +28235,7 @@
         </is>
       </c>
       <c r="C28" s="22" t="n">
-        <v>0.4305136</v>
+        <v>0.3814184820374598</v>
       </c>
       <c r="D28" s="33" t="inlineStr">
         <is>
@@ -28269,7 +28243,7 @@
         </is>
       </c>
       <c r="E28" s="23" t="n">
-        <v>186.2185523184757</v>
+        <v>195.4228046268257</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
@@ -28279,7 +28253,7 @@
         </is>
       </c>
       <c r="C29" s="22" t="n">
-        <v>1.614</v>
+        <v>0.502</v>
       </c>
       <c r="D29" s="33" t="inlineStr">
         <is>
@@ -28287,7 +28261,7 @@
         </is>
       </c>
       <c r="E29" s="22" t="n">
-        <v>-13.95633802816901</v>
+        <v>-3.532483495983913</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
@@ -28296,10 +28270,8 @@
           <t>EV / EBIT</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C30" s="22" t="n">
+        <v>0.5830299613427031</v>
       </c>
       <c r="D30" s="33" t="inlineStr">
         <is>
@@ -28307,7 +28279,7 @@
         </is>
       </c>
       <c r="E30" s="23" t="n">
-        <v>13.92004707439961</v>
+        <v>48.19489607961939</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
@@ -28317,7 +28289,7 @@
         </is>
       </c>
       <c r="C31" s="22" t="n">
-        <v>8.142856999999999</v>
+        <v>3.257832481702135</v>
       </c>
       <c r="D31" s="33" t="inlineStr">
         <is>
@@ -28325,7 +28297,7 @@
         </is>
       </c>
       <c r="E31" s="23" t="n">
-        <v>2.30894308943089</v>
+        <v>12.06697403251717</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
@@ -28335,7 +28307,7 @@
         </is>
       </c>
       <c r="C32" s="22" t="n">
-        <v>0.3348663</v>
+        <v>0.47579452</v>
       </c>
       <c r="D32" s="33" t="inlineStr">
         <is>
@@ -28343,7 +28315,7 @@
         </is>
       </c>
       <c r="E32" s="23" t="n">
-        <v>66.086</v>
+        <v>50.244</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
@@ -28353,7 +28325,7 @@
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>4.09667276945568</v>
+        <v>3.22106752958146</v>
       </c>
       <c r="D33" s="33" t="inlineStr">
         <is>
@@ -28373,7 +28345,7 @@
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>90.87835873445673</v>
+        <v>86.88917215306873</v>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
@@ -28381,7 +28353,7 @@
         </is>
       </c>
       <c r="E34" s="23" t="n">
-        <v>-0.22712524334847</v>
+        <v>-6.109694716853889</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
@@ -28391,7 +28363,7 @@
         </is>
       </c>
       <c r="C35" s="22" t="n">
-        <v>6.08519742575637</v>
+        <v>17.52230716826635</v>
       </c>
       <c r="D35" s="33" t="inlineStr">
         <is>
@@ -28399,7 +28371,7 @@
         </is>
       </c>
       <c r="E35" s="23" t="n">
-        <v>14.1</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
@@ -28426,14 +28398,14 @@
     <row r="40" ht="16" customHeight="1">
       <c r="B40" s="35" t="inlineStr">
         <is>
-          <t>·  Sub-book  (P/B 0.43)</t>
+          <t>·  Sub-book  (P/B 0.38)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="B41" s="35" t="inlineStr">
         <is>
-          <t>·  Insider-aligned  (66% insider)</t>
+          <t>·  Insider-aligned  (50% insider)</t>
         </is>
       </c>
     </row>
@@ -28447,7 +28419,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>growth-flip; accelerating sales; cheap+grow (EV/EBIT 1.0x); Graham net-net (mcap 0.54x NCAV); cash 108% of mcap; cash &gt; EV (6.09x, net cash 91% mcap)</t>
+          <t>growth-flip; under-priced vs fundamentals; cheap+grow (EV/EBIT 0.1x); Graham net-net (mcap 0.51x NCAV); cash 150% of mcap; cash &gt; EV (17.52x, net cash 143% mcap)</t>
         </is>
       </c>
     </row>
